--- a/VFC.xlsx
+++ b/VFC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4D8E787-575E-4D3E-987D-B7DD50DC8793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49B54D7F-CE21-44E3-9D07-422DEA8345E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{FD9221D3-9194-474F-AA6F-D3A3CA930557}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{FD9221D3-9194-474F-AA6F-D3A3CA930557}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="65">
   <si>
     <t>VF Corporation</t>
   </si>
@@ -195,9 +195,6 @@
     <t>Tax Rate</t>
   </si>
   <si>
-    <t>FQ426</t>
-  </si>
-  <si>
     <t>The North Face, Timberland, Vans, Kipling</t>
   </si>
   <si>
@@ -219,7 +216,22 @@
     <t>Outdoor Revenue</t>
   </si>
   <si>
-    <t>Actuve Revenue</t>
+    <t>Active Revenue</t>
+  </si>
+  <si>
+    <t>Q127</t>
+  </si>
+  <si>
+    <t>Q227</t>
+  </si>
+  <si>
+    <t>Q327</t>
+  </si>
+  <si>
+    <t>Q427</t>
+  </si>
+  <si>
+    <t>FQ127</t>
   </si>
 </sst>
 </file>
@@ -231,13 +243,19 @@
     <numFmt numFmtId="165" formatCode="#,##0.0;\(#,##0.0\)"/>
     <numFmt numFmtId="166" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -314,32 +332,36 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -696,7 +718,7 @@
         <v>4</v>
       </c>
       <c r="H2" s="2">
-        <v>16.72</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -704,10 +726,10 @@
         <v>5</v>
       </c>
       <c r="H3" s="3">
-        <v>391.76970499999999</v>
+        <v>393.13457</v>
       </c>
-      <c r="I3" s="14" t="s">
-        <v>52</v>
+      <c r="I3" s="17" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -719,7 +741,7 @@
       </c>
       <c r="H4" s="3">
         <f>+H2*H3</f>
-        <v>6550.3894675999991</v>
+        <v>5700.4512649999997</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -730,10 +752,10 @@
         <v>7</v>
       </c>
       <c r="H5" s="3">
-        <v>823.94299999999998</v>
+        <v>670.06299999999999</v>
       </c>
-      <c r="I5" s="14" t="s">
-        <v>52</v>
+      <c r="I5" s="17" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -741,11 +763,11 @@
         <v>8</v>
       </c>
       <c r="H6" s="3">
-        <f>10.139+3519.87</f>
-        <v>3530.009</v>
+        <f>9.688+3003.417</f>
+        <v>3013.105</v>
       </c>
-      <c r="I6" s="14" t="s">
-        <v>52</v>
+      <c r="I6" s="17" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -754,7 +776,7 @@
       </c>
       <c r="H7" s="3">
         <f>+H4-H5+H6</f>
-        <v>9256.4554675999989</v>
+        <v>8043.4932649999992</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
@@ -769,17 +791,17 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B12" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B13" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B14" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -792,7 +814,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC6FD6D1-E9FA-4061-9239-71EF4FDE7FAB}">
-  <dimension ref="A1:GY252"/>
+  <dimension ref="A1:HC252"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -800,12 +822,12 @@
     <col min="3" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:207" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:211" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:207" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:211" x14ac:dyDescent="0.2">
       <c r="C2" s="4" t="s">
         <v>11</v>
       </c>
@@ -842,17 +864,29 @@
       <c r="N2" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="P2" s="14" t="s">
-        <v>58</v>
+      <c r="O2" s="17" t="s">
+        <v>60</v>
       </c>
-      <c r="Q2" s="14" t="s">
+      <c r="P2" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q2" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="R2" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="T2" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="U2" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="V2" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="R2" s="14" t="s">
-        <v>57</v>
-      </c>
     </row>
-    <row r="3" spans="1:207" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:211" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>37</v>
       </c>
@@ -885,21 +919,26 @@
       <c r="M3" s="7">
         <v>1538.6579999999999</v>
       </c>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7">
+      <c r="N3" s="7">
+        <f>+V3-SUM(K3:M3)</f>
+        <v>1010.346</v>
+      </c>
+      <c r="O3" s="7">
+        <v>895.50099999999998</v>
+      </c>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="7">
         <v>5152.7579999999998</v>
       </c>
-      <c r="Q3" s="7">
+      <c r="U3" s="7">
         <v>4833.5249999999996</v>
       </c>
-      <c r="R3" s="7">
+      <c r="V3" s="7">
         <v>4830.0940000000001</v>
       </c>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="7"/>
-      <c r="V3" s="7"/>
       <c r="W3" s="7"/>
       <c r="X3" s="7"/>
       <c r="Y3" s="7"/>
@@ -965,8 +1004,12 @@
       <c r="CG3" s="7"/>
       <c r="CH3" s="7"/>
       <c r="CI3" s="7"/>
+      <c r="CJ3" s="7"/>
+      <c r="CK3" s="7"/>
+      <c r="CL3" s="7"/>
+      <c r="CM3" s="7"/>
     </row>
-    <row r="4" spans="1:207" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:211" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
         <v>38</v>
       </c>
@@ -999,21 +1042,26 @@
       <c r="M4" s="7">
         <v>928.74</v>
       </c>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7">
+      <c r="N4" s="7">
+        <f>+V4-SUM(K4:M4)</f>
+        <v>819.26199999999972</v>
+      </c>
+      <c r="O4" s="7">
+        <v>511.14600000000002</v>
+      </c>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="7">
         <v>3339.6559999999999</v>
       </c>
-      <c r="Q4" s="7">
+      <c r="U4" s="7">
         <v>3248.4609999999998</v>
       </c>
-      <c r="R4" s="7">
+      <c r="V4" s="7">
         <v>3371.92</v>
       </c>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="7"/>
       <c r="W4" s="7"/>
       <c r="X4" s="7"/>
       <c r="Y4" s="7"/>
@@ -1079,8 +1127,12 @@
       <c r="CG4" s="7"/>
       <c r="CH4" s="7"/>
       <c r="CI4" s="7"/>
+      <c r="CJ4" s="7"/>
+      <c r="CK4" s="7"/>
+      <c r="CL4" s="7"/>
+      <c r="CM4" s="7"/>
     </row>
-    <row r="5" spans="1:207" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:211" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>39</v>
       </c>
@@ -1113,21 +1165,26 @@
       <c r="M5" s="7">
         <v>408.40300000000002</v>
       </c>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7">
+      <c r="N5" s="7">
+        <f>+V5-SUM(K5:M5)</f>
+        <v>336.42599999999993</v>
+      </c>
+      <c r="O5" s="7">
+        <v>262.73200000000003</v>
+      </c>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7">
         <v>1403.2639999999999</v>
       </c>
-      <c r="Q5" s="7">
+      <c r="U5" s="7">
         <v>1422.7049999999999</v>
       </c>
-      <c r="R5" s="7">
+      <c r="V5" s="7">
         <v>1403.193</v>
       </c>
-      <c r="S5" s="7"/>
-      <c r="T5" s="7"/>
-      <c r="U5" s="7"/>
-      <c r="V5" s="7"/>
       <c r="W5" s="7"/>
       <c r="X5" s="7"/>
       <c r="Y5" s="7"/>
@@ -1193,10 +1250,14 @@
       <c r="CG5" s="7"/>
       <c r="CH5" s="7"/>
       <c r="CI5" s="7"/>
+      <c r="CJ5" s="7"/>
+      <c r="CK5" s="7"/>
+      <c r="CL5" s="7"/>
+      <c r="CM5" s="7"/>
     </row>
-    <row r="6" spans="1:207" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:211" x14ac:dyDescent="0.2">
       <c r="B6" s="15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
@@ -1206,24 +1267,28 @@
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
+      <c r="K6" s="7">
+        <v>812.46600000000001</v>
+      </c>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
       <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7">
+      <c r="O6" s="7">
+        <v>856.97900000000004</v>
+      </c>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7">
         <v>5230.2870000000003</v>
       </c>
-      <c r="Q6" s="7">
+      <c r="U6" s="7">
         <v>5311.0609999999997</v>
       </c>
-      <c r="R6" s="7">
+      <c r="V6" s="7">
         <v>5741.7920000000004</v>
       </c>
-      <c r="S6" s="7"/>
-      <c r="T6" s="7"/>
-      <c r="U6" s="7"/>
-      <c r="V6" s="7"/>
       <c r="W6" s="7"/>
       <c r="X6" s="7"/>
       <c r="Y6" s="7"/>
@@ -1289,10 +1354,14 @@
       <c r="CG6" s="7"/>
       <c r="CH6" s="7"/>
       <c r="CI6" s="7"/>
+      <c r="CJ6" s="7"/>
+      <c r="CK6" s="7"/>
+      <c r="CL6" s="7"/>
+      <c r="CM6" s="7"/>
     </row>
-    <row r="7" spans="1:207" x14ac:dyDescent="0.2">
-      <c r="B7" s="15" t="s">
-        <v>60</v>
+    <row r="7" spans="1:211" x14ac:dyDescent="0.2">
+      <c r="B7" s="16" t="s">
+        <v>59</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
@@ -1302,24 +1371,28 @@
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
+      <c r="K7" s="7">
+        <v>699.68700000000001</v>
+      </c>
       <c r="L7" s="7"/>
       <c r="M7" s="7"/>
       <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7">
+      <c r="O7" s="7">
+        <v>667.303</v>
+      </c>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7">
         <v>3327.6120000000001</v>
       </c>
-      <c r="Q7" s="7">
+      <c r="U7" s="7">
         <v>2914.3069999999998</v>
       </c>
-      <c r="R7" s="7">
+      <c r="V7" s="7">
         <v>2720.9670000000001</v>
       </c>
-      <c r="S7" s="7"/>
-      <c r="T7" s="7"/>
-      <c r="U7" s="7"/>
-      <c r="V7" s="7"/>
       <c r="W7" s="7"/>
       <c r="X7" s="7"/>
       <c r="Y7" s="7"/>
@@ -1385,8 +1458,12 @@
       <c r="CG7" s="7"/>
       <c r="CH7" s="7"/>
       <c r="CI7" s="7"/>
+      <c r="CJ7" s="7"/>
+      <c r="CK7" s="7"/>
+      <c r="CL7" s="7"/>
+      <c r="CM7" s="7"/>
     </row>
-    <row r="8" spans="1:207" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:211" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
         <v>42</v>
       </c>
@@ -1404,8 +1481,8 @@
       <c r="J8" s="7">
         <v>301.5</v>
       </c>
-      <c r="K8" s="10" t="s">
-        <v>47</v>
+      <c r="K8" s="10">
+        <v>238.51300000000001</v>
       </c>
       <c r="L8" s="10" t="s">
         <v>47</v>
@@ -1413,21 +1490,26 @@
       <c r="M8" s="7">
         <v>392.2</v>
       </c>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
-      <c r="P8" s="7">
+      <c r="N8" s="7">
+        <f>+V8-SUM(K8:M8)</f>
+        <v>511.73500000000013</v>
+      </c>
+      <c r="O8" s="7">
+        <v>145.09700000000001</v>
+      </c>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7">
         <v>1357.779</v>
       </c>
-      <c r="Q8" s="7">
+      <c r="U8" s="7">
         <v>1279.3230000000001</v>
       </c>
-      <c r="R8" s="7">
+      <c r="V8" s="7">
         <v>1142.4480000000001</v>
       </c>
-      <c r="S8" s="7"/>
-      <c r="T8" s="7"/>
-      <c r="U8" s="7"/>
-      <c r="V8" s="7"/>
       <c r="W8" s="7"/>
       <c r="X8" s="7"/>
       <c r="Y8" s="7"/>
@@ -1493,8 +1575,12 @@
       <c r="CG8" s="7"/>
       <c r="CH8" s="7"/>
       <c r="CI8" s="7"/>
+      <c r="CJ8" s="7"/>
+      <c r="CK8" s="7"/>
+      <c r="CL8" s="7"/>
+      <c r="CM8" s="7"/>
     </row>
-    <row r="9" spans="1:207" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:211" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>34</v>
       </c>
@@ -1527,21 +1613,26 @@
       <c r="M9" s="7">
         <v>1237.443</v>
       </c>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
-      <c r="P9" s="7">
+      <c r="N9" s="7">
+        <f>+V9-SUM(K9:M9)</f>
+        <v>1204.7470000000003</v>
+      </c>
+      <c r="O9" s="7">
+        <v>924.75199999999995</v>
+      </c>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="7"/>
+      <c r="S9" s="7"/>
+      <c r="T9" s="7">
         <v>5422.0169999999998</v>
       </c>
-      <c r="Q9" s="7">
+      <c r="U9" s="7">
         <v>5300.0940000000001</v>
       </c>
-      <c r="R9" s="7">
+      <c r="V9" s="7">
         <v>5343.643</v>
       </c>
-      <c r="S9" s="7"/>
-      <c r="T9" s="7"/>
-      <c r="U9" s="7"/>
-      <c r="V9" s="7"/>
       <c r="W9" s="7"/>
       <c r="X9" s="7"/>
       <c r="Y9" s="7"/>
@@ -1607,8 +1698,12 @@
       <c r="CG9" s="7"/>
       <c r="CH9" s="7"/>
       <c r="CI9" s="7"/>
+      <c r="CJ9" s="7"/>
+      <c r="CK9" s="7"/>
+      <c r="CL9" s="7"/>
+      <c r="CM9" s="7"/>
     </row>
-    <row r="10" spans="1:207" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:211" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>35</v>
       </c>
@@ -1641,21 +1736,26 @@
       <c r="M10" s="7">
         <v>1626.002</v>
       </c>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7"/>
-      <c r="P10" s="7">
+      <c r="N10" s="7">
+        <f>+V10-SUM(K10:M10)</f>
+        <v>955.34299999999985</v>
+      </c>
+      <c r="O10" s="7">
+        <v>738.39099999999996</v>
+      </c>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7"/>
+      <c r="S10" s="7"/>
+      <c r="T10" s="7">
         <v>4426.5879999999997</v>
       </c>
-      <c r="Q10" s="7">
+      <c r="U10" s="7">
         <v>4142.2749999999996</v>
       </c>
-      <c r="R10" s="7">
+      <c r="V10" s="7">
         <v>4211.8689999999997</v>
       </c>
-      <c r="S10" s="7"/>
-      <c r="T10" s="7"/>
-      <c r="U10" s="7"/>
-      <c r="V10" s="7"/>
       <c r="W10" s="7"/>
       <c r="X10" s="7"/>
       <c r="Y10" s="7"/>
@@ -1721,8 +1821,12 @@
       <c r="CG10" s="7"/>
       <c r="CH10" s="7"/>
       <c r="CI10" s="7"/>
+      <c r="CJ10" s="7"/>
+      <c r="CK10" s="7"/>
+      <c r="CL10" s="7"/>
+      <c r="CM10" s="7"/>
     </row>
-    <row r="11" spans="1:207" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:211" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>36</v>
       </c>
@@ -1755,21 +1859,26 @@
       <c r="M11" s="7">
         <v>12.356</v>
       </c>
-      <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
-      <c r="P11" s="7">
+      <c r="N11" s="7">
+        <f>+V11-SUM(K11:M11)</f>
+        <v>5.9440000000000026</v>
+      </c>
+      <c r="O11" s="7">
+        <v>6.2359999999999998</v>
+      </c>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7">
         <v>67.072999999999993</v>
       </c>
-      <c r="Q11" s="7">
+      <c r="U11" s="7">
         <v>62.322000000000003</v>
       </c>
-      <c r="R11" s="7">
+      <c r="V11" s="7">
         <v>49.695</v>
       </c>
-      <c r="S11" s="7"/>
-      <c r="T11" s="7"/>
-      <c r="U11" s="7"/>
-      <c r="V11" s="7"/>
       <c r="W11" s="7"/>
       <c r="X11" s="7"/>
       <c r="Y11" s="7"/>
@@ -1835,8 +1944,12 @@
       <c r="CG11" s="7"/>
       <c r="CH11" s="7"/>
       <c r="CI11" s="7"/>
+      <c r="CJ11" s="7"/>
+      <c r="CK11" s="7"/>
+      <c r="CL11" s="7"/>
+      <c r="CM11" s="7"/>
     </row>
-    <row r="12" spans="1:207" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:211" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
         <v>19</v>
       </c>
@@ -1869,21 +1982,26 @@
       <c r="M12" s="8">
         <v>2875.8009999999999</v>
       </c>
-      <c r="N12" s="7"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8">
+      <c r="N12" s="8">
+        <f>+V12-SUM(K12:M12)</f>
+        <v>2166.0339999999997</v>
+      </c>
+      <c r="O12" s="8">
+        <v>1669.3789999999999</v>
+      </c>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="7"/>
+      <c r="R12" s="7"/>
+      <c r="S12" s="8"/>
+      <c r="T12" s="8">
         <v>9915.6779999999999</v>
       </c>
-      <c r="Q12" s="8">
+      <c r="U12" s="8">
         <v>9504.6910000000007</v>
       </c>
-      <c r="R12" s="8">
+      <c r="V12" s="8">
         <v>9605.2070000000003</v>
       </c>
-      <c r="S12" s="7"/>
-      <c r="T12" s="7"/>
-      <c r="U12" s="7"/>
-      <c r="V12" s="7"/>
       <c r="W12" s="7"/>
       <c r="X12" s="7"/>
       <c r="Y12" s="7"/>
@@ -1949,10 +2067,10 @@
       <c r="CG12" s="7"/>
       <c r="CH12" s="7"/>
       <c r="CI12" s="7"/>
-      <c r="CJ12" s="3"/>
-      <c r="CK12" s="3"/>
-      <c r="CL12" s="3"/>
-      <c r="CM12" s="3"/>
+      <c r="CJ12" s="7"/>
+      <c r="CK12" s="7"/>
+      <c r="CL12" s="7"/>
+      <c r="CM12" s="7"/>
       <c r="CN12" s="3"/>
       <c r="CO12" s="3"/>
       <c r="CP12" s="3"/>
@@ -2069,8 +2187,12 @@
       <c r="GW12" s="3"/>
       <c r="GX12" s="3"/>
       <c r="GY12" s="3"/>
+      <c r="GZ12" s="3"/>
+      <c r="HA12" s="3"/>
+      <c r="HB12" s="3"/>
+      <c r="HC12" s="3"/>
     </row>
-    <row r="13" spans="1:207" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:211" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>20</v>
       </c>
@@ -2103,21 +2225,26 @@
       <c r="M13" s="7">
         <v>1247.46</v>
       </c>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="7">
+      <c r="N13" s="7">
+        <f>+V13-SUM(K13:M13)</f>
+        <v>944.10600000000022</v>
+      </c>
+      <c r="O13" s="7">
+        <v>752.33500000000004</v>
+      </c>
+      <c r="P13" s="7"/>
+      <c r="Q13" s="7"/>
+      <c r="R13" s="7"/>
+      <c r="S13" s="7"/>
+      <c r="T13" s="7">
         <v>4803.3779999999997</v>
       </c>
-      <c r="Q13" s="7">
+      <c r="U13" s="7">
         <v>4420.826</v>
       </c>
-      <c r="R13" s="7">
+      <c r="V13" s="7">
         <v>4343.4920000000002</v>
       </c>
-      <c r="S13" s="7"/>
-      <c r="T13" s="7"/>
-      <c r="U13" s="7"/>
-      <c r="V13" s="7"/>
       <c r="W13" s="7"/>
       <c r="X13" s="7"/>
       <c r="Y13" s="7"/>
@@ -2183,10 +2310,10 @@
       <c r="CG13" s="7"/>
       <c r="CH13" s="7"/>
       <c r="CI13" s="7"/>
-      <c r="CJ13" s="3"/>
-      <c r="CK13" s="3"/>
-      <c r="CL13" s="3"/>
-      <c r="CM13" s="3"/>
+      <c r="CJ13" s="7"/>
+      <c r="CK13" s="7"/>
+      <c r="CL13" s="7"/>
+      <c r="CM13" s="7"/>
       <c r="CN13" s="3"/>
       <c r="CO13" s="3"/>
       <c r="CP13" s="3"/>
@@ -2303,8 +2430,12 @@
       <c r="GW13" s="3"/>
       <c r="GX13" s="3"/>
       <c r="GY13" s="3"/>
+      <c r="GZ13" s="3"/>
+      <c r="HA13" s="3"/>
+      <c r="HB13" s="3"/>
+      <c r="HC13" s="3"/>
     </row>
-    <row r="14" spans="1:207" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:211" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>21</v>
       </c>
@@ -2337,7 +2468,7 @@
         <v>1595.1739999999998</v>
       </c>
       <c r="J14" s="7">
-        <f t="shared" ref="J14:M14" si="1">+J12-J13</f>
+        <f t="shared" ref="J14:O14" si="1">+J12-J13</f>
         <v>1142.4560000000001</v>
       </c>
       <c r="K14" s="7">
@@ -2352,24 +2483,30 @@
         <f t="shared" si="1"/>
         <v>1628.3409999999999</v>
       </c>
-      <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
-      <c r="P14" s="7">
-        <f>+P12-P13</f>
+      <c r="N14" s="7">
+        <f t="shared" si="1"/>
+        <v>1221.9279999999994</v>
+      </c>
+      <c r="O14" s="7">
+        <f t="shared" si="1"/>
+        <v>917.04399999999987</v>
+      </c>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="7"/>
+      <c r="R14" s="7"/>
+      <c r="S14" s="7"/>
+      <c r="T14" s="7">
+        <f>+T12-T13</f>
         <v>5112.3</v>
       </c>
-      <c r="Q14" s="7">
-        <f>+Q12-Q13</f>
+      <c r="U14" s="7">
+        <f>+U12-U13</f>
         <v>5083.8650000000007</v>
       </c>
-      <c r="R14" s="7">
-        <f>+R12-R13</f>
+      <c r="V14" s="7">
+        <f>+V12-V13</f>
         <v>5261.7150000000001</v>
       </c>
-      <c r="S14" s="7"/>
-      <c r="T14" s="7"/>
-      <c r="U14" s="7"/>
-      <c r="V14" s="7"/>
       <c r="W14" s="7"/>
       <c r="X14" s="7"/>
       <c r="Y14" s="7"/>
@@ -2435,10 +2572,10 @@
       <c r="CG14" s="7"/>
       <c r="CH14" s="7"/>
       <c r="CI14" s="7"/>
-      <c r="CJ14" s="3"/>
-      <c r="CK14" s="3"/>
-      <c r="CL14" s="3"/>
-      <c r="CM14" s="3"/>
+      <c r="CJ14" s="7"/>
+      <c r="CK14" s="7"/>
+      <c r="CL14" s="7"/>
+      <c r="CM14" s="7"/>
       <c r="CN14" s="3"/>
       <c r="CO14" s="3"/>
       <c r="CP14" s="3"/>
@@ -2555,8 +2692,12 @@
       <c r="GW14" s="3"/>
       <c r="GX14" s="3"/>
       <c r="GY14" s="3"/>
+      <c r="GZ14" s="3"/>
+      <c r="HA14" s="3"/>
+      <c r="HB14" s="3"/>
+      <c r="HC14" s="3"/>
     </row>
-    <row r="15" spans="1:207" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:211" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>22</v>
       </c>
@@ -2589,21 +2730,26 @@
       <c r="M15" s="7">
         <v>1308.5709999999999</v>
       </c>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="7">
+      <c r="N15" s="7">
+        <f>+V15-SUM(K15:M15)</f>
+        <v>1160.424</v>
+      </c>
+      <c r="O15" s="7">
+        <v>1000.116</v>
+      </c>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="7"/>
+      <c r="T15" s="7">
         <v>4748.6689999999999</v>
       </c>
-      <c r="Q15" s="7">
+      <c r="U15" s="7">
         <v>4690.8500000000004</v>
       </c>
-      <c r="R15" s="7">
+      <c r="V15" s="7">
         <v>4654.43</v>
       </c>
-      <c r="S15" s="7"/>
-      <c r="T15" s="7"/>
-      <c r="U15" s="7"/>
-      <c r="V15" s="7"/>
       <c r="W15" s="7"/>
       <c r="X15" s="7"/>
       <c r="Y15" s="7"/>
@@ -2669,10 +2815,10 @@
       <c r="CG15" s="7"/>
       <c r="CH15" s="7"/>
       <c r="CI15" s="7"/>
-      <c r="CJ15" s="3"/>
-      <c r="CK15" s="3"/>
-      <c r="CL15" s="3"/>
-      <c r="CM15" s="3"/>
+      <c r="CJ15" s="7"/>
+      <c r="CK15" s="7"/>
+      <c r="CL15" s="7"/>
+      <c r="CM15" s="7"/>
       <c r="CN15" s="3"/>
       <c r="CO15" s="3"/>
       <c r="CP15" s="3"/>
@@ -2789,8 +2935,12 @@
       <c r="GW15" s="3"/>
       <c r="GX15" s="3"/>
       <c r="GY15" s="3"/>
+      <c r="GZ15" s="3"/>
+      <c r="HA15" s="3"/>
+      <c r="HB15" s="3"/>
+      <c r="HC15" s="3"/>
     </row>
-    <row r="16" spans="1:207" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:211" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>23</v>
       </c>
@@ -2823,21 +2973,26 @@
       <c r="M16" s="7">
         <v>30.716000000000001</v>
       </c>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="7">
+      <c r="N16" s="7">
+        <f>+V16-SUM(K16:M16)</f>
+        <v>0</v>
+      </c>
+      <c r="O16" s="7">
+        <v>0</v>
+      </c>
+      <c r="P16" s="7"/>
+      <c r="Q16" s="7"/>
+      <c r="R16" s="7"/>
+      <c r="S16" s="7"/>
+      <c r="T16" s="7">
         <v>507.56599999999997</v>
       </c>
-      <c r="Q16" s="7">
+      <c r="U16" s="7">
         <v>89.242000000000004</v>
       </c>
-      <c r="R16" s="7">
+      <c r="V16" s="7">
         <v>30.716000000000001</v>
       </c>
-      <c r="S16" s="7"/>
-      <c r="T16" s="7"/>
-      <c r="U16" s="7"/>
-      <c r="V16" s="7"/>
       <c r="W16" s="7"/>
       <c r="X16" s="7"/>
       <c r="Y16" s="7"/>
@@ -2903,10 +3058,10 @@
       <c r="CG16" s="7"/>
       <c r="CH16" s="7"/>
       <c r="CI16" s="7"/>
-      <c r="CJ16" s="3"/>
-      <c r="CK16" s="3"/>
-      <c r="CL16" s="3"/>
-      <c r="CM16" s="3"/>
+      <c r="CJ16" s="7"/>
+      <c r="CK16" s="7"/>
+      <c r="CL16" s="7"/>
+      <c r="CM16" s="7"/>
       <c r="CN16" s="3"/>
       <c r="CO16" s="3"/>
       <c r="CP16" s="3"/>
@@ -3023,8 +3178,12 @@
       <c r="GW16" s="3"/>
       <c r="GX16" s="3"/>
       <c r="GY16" s="3"/>
+      <c r="GZ16" s="3"/>
+      <c r="HA16" s="3"/>
+      <c r="HB16" s="3"/>
+      <c r="HC16" s="3"/>
     </row>
-    <row r="17" spans="2:207" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:211" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>24</v>
       </c>
@@ -3057,7 +3216,7 @@
         <v>225.77699999999982</v>
       </c>
       <c r="J17" s="7">
-        <f t="shared" ref="J17:M17" si="5">+J14-J15-J16</f>
+        <f t="shared" ref="J17:O17" si="5">+J14-J15-J16</f>
         <v>-72.886999999999972</v>
       </c>
       <c r="K17" s="7">
@@ -3072,24 +3231,30 @@
         <f t="shared" si="5"/>
         <v>289.05399999999997</v>
       </c>
-      <c r="N17" s="7"/>
-      <c r="O17" s="7"/>
-      <c r="P17" s="7">
-        <f t="shared" ref="P17:R17" si="6">+P14-P15-P16</f>
+      <c r="N17" s="7">
+        <f t="shared" si="5"/>
+        <v>61.503999999999451</v>
+      </c>
+      <c r="O17" s="7">
+        <f t="shared" si="5"/>
+        <v>-83.072000000000116</v>
+      </c>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="7"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7">
+        <f t="shared" ref="T17:V17" si="6">+T14-T15-T16</f>
         <v>-143.93499999999966</v>
       </c>
-      <c r="Q17" s="7">
+      <c r="U17" s="7">
         <f t="shared" si="6"/>
         <v>303.77300000000031</v>
       </c>
-      <c r="R17" s="7">
+      <c r="V17" s="7">
         <f t="shared" si="6"/>
         <v>576.56899999999985</v>
       </c>
-      <c r="S17" s="7"/>
-      <c r="T17" s="7"/>
-      <c r="U17" s="7"/>
-      <c r="V17" s="7"/>
       <c r="W17" s="7"/>
       <c r="X17" s="7"/>
       <c r="Y17" s="7"/>
@@ -3155,10 +3320,10 @@
       <c r="CG17" s="7"/>
       <c r="CH17" s="7"/>
       <c r="CI17" s="7"/>
-      <c r="CJ17" s="3"/>
-      <c r="CK17" s="3"/>
-      <c r="CL17" s="3"/>
-      <c r="CM17" s="3"/>
+      <c r="CJ17" s="7"/>
+      <c r="CK17" s="7"/>
+      <c r="CL17" s="7"/>
+      <c r="CM17" s="7"/>
       <c r="CN17" s="3"/>
       <c r="CO17" s="3"/>
       <c r="CP17" s="3"/>
@@ -3275,8 +3440,12 @@
       <c r="GW17" s="3"/>
       <c r="GX17" s="3"/>
       <c r="GY17" s="3"/>
+      <c r="GZ17" s="3"/>
+      <c r="HA17" s="3"/>
+      <c r="HB17" s="3"/>
+      <c r="HC17" s="3"/>
     </row>
-    <row r="18" spans="2:207" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:211" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>25</v>
       </c>
@@ -3309,21 +3478,26 @@
       <c r="M18" s="7">
         <v>5.1360000000000001</v>
       </c>
-      <c r="N18" s="7"/>
-      <c r="O18" s="7"/>
-      <c r="P18" s="7">
+      <c r="N18" s="7">
+        <f>+V18-SUM(K18:M18)</f>
+        <v>6.9659999999999975</v>
+      </c>
+      <c r="O18" s="7">
+        <v>5.8070000000000004</v>
+      </c>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="7"/>
+      <c r="R18" s="7"/>
+      <c r="S18" s="7"/>
+      <c r="T18" s="7">
         <v>20.245999999999999</v>
       </c>
-      <c r="Q18" s="7">
+      <c r="U18" s="7">
         <v>24.783000000000001</v>
       </c>
-      <c r="R18" s="7">
+      <c r="V18" s="7">
         <v>18.027999999999999</v>
       </c>
-      <c r="S18" s="7"/>
-      <c r="T18" s="7"/>
-      <c r="U18" s="7"/>
-      <c r="V18" s="7"/>
       <c r="W18" s="7"/>
       <c r="X18" s="7"/>
       <c r="Y18" s="7"/>
@@ -3389,10 +3563,10 @@
       <c r="CG18" s="7"/>
       <c r="CH18" s="7"/>
       <c r="CI18" s="7"/>
-      <c r="CJ18" s="3"/>
-      <c r="CK18" s="3"/>
-      <c r="CL18" s="3"/>
-      <c r="CM18" s="3"/>
+      <c r="CJ18" s="7"/>
+      <c r="CK18" s="7"/>
+      <c r="CL18" s="7"/>
+      <c r="CM18" s="7"/>
       <c r="CN18" s="3"/>
       <c r="CO18" s="3"/>
       <c r="CP18" s="3"/>
@@ -3509,8 +3683,12 @@
       <c r="GW18" s="3"/>
       <c r="GX18" s="3"/>
       <c r="GY18" s="3"/>
+      <c r="GZ18" s="3"/>
+      <c r="HA18" s="3"/>
+      <c r="HB18" s="3"/>
+      <c r="HC18" s="3"/>
     </row>
-    <row r="19" spans="2:207" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:211" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>26</v>
       </c>
@@ -3543,21 +3721,26 @@
       <c r="M19" s="7">
         <v>39.747</v>
       </c>
-      <c r="N19" s="7"/>
-      <c r="O19" s="7"/>
-      <c r="P19" s="7">
+      <c r="N19" s="7">
+        <f>+V19-SUM(K19:M19)</f>
+        <v>33.768999999999977</v>
+      </c>
+      <c r="O19" s="7">
+        <v>30.417999999999999</v>
+      </c>
+      <c r="P19" s="7"/>
+      <c r="Q19" s="7"/>
+      <c r="R19" s="7"/>
+      <c r="S19" s="7"/>
+      <c r="T19" s="7">
         <v>185.92500000000001</v>
       </c>
-      <c r="Q19" s="7">
+      <c r="U19" s="7">
         <v>174.136</v>
       </c>
-      <c r="R19" s="7">
+      <c r="V19" s="7">
         <v>166.77099999999999</v>
       </c>
-      <c r="S19" s="7"/>
-      <c r="T19" s="7"/>
-      <c r="U19" s="7"/>
-      <c r="V19" s="7"/>
       <c r="W19" s="7"/>
       <c r="X19" s="7"/>
       <c r="Y19" s="7"/>
@@ -3623,10 +3806,10 @@
       <c r="CG19" s="7"/>
       <c r="CH19" s="7"/>
       <c r="CI19" s="7"/>
-      <c r="CJ19" s="3"/>
-      <c r="CK19" s="3"/>
-      <c r="CL19" s="3"/>
-      <c r="CM19" s="3"/>
+      <c r="CJ19" s="7"/>
+      <c r="CK19" s="7"/>
+      <c r="CL19" s="7"/>
+      <c r="CM19" s="7"/>
       <c r="CN19" s="3"/>
       <c r="CO19" s="3"/>
       <c r="CP19" s="3"/>
@@ -3743,8 +3926,12 @@
       <c r="GW19" s="3"/>
       <c r="GX19" s="3"/>
       <c r="GY19" s="3"/>
+      <c r="GZ19" s="3"/>
+      <c r="HA19" s="3"/>
+      <c r="HB19" s="3"/>
+      <c r="HC19" s="3"/>
     </row>
-    <row r="20" spans="2:207" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:211" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
         <v>27</v>
       </c>
@@ -3777,21 +3964,26 @@
       <c r="M20" s="7">
         <v>108.416</v>
       </c>
-      <c r="N20" s="7"/>
-      <c r="O20" s="7"/>
-      <c r="P20" s="7">
+      <c r="N20" s="7">
+        <f>+V20-SUM(K20:M20)</f>
+        <v>-198.03</v>
+      </c>
+      <c r="O20" s="7">
+        <v>0.79100000000000004</v>
+      </c>
+      <c r="P20" s="7"/>
+      <c r="Q20" s="7"/>
+      <c r="R20" s="7"/>
+      <c r="S20" s="7"/>
+      <c r="T20" s="7">
         <v>24.693000000000001</v>
       </c>
-      <c r="Q20" s="7">
+      <c r="U20" s="7">
         <v>-9.3689999999999998</v>
       </c>
-      <c r="R20" s="7">
+      <c r="V20" s="7">
         <v>-86.608000000000004</v>
       </c>
-      <c r="S20" s="7"/>
-      <c r="T20" s="7"/>
-      <c r="U20" s="7"/>
-      <c r="V20" s="7"/>
       <c r="W20" s="7"/>
       <c r="X20" s="7"/>
       <c r="Y20" s="7"/>
@@ -3857,10 +4049,10 @@
       <c r="CG20" s="7"/>
       <c r="CH20" s="7"/>
       <c r="CI20" s="7"/>
-      <c r="CJ20" s="3"/>
-      <c r="CK20" s="3"/>
-      <c r="CL20" s="3"/>
-      <c r="CM20" s="3"/>
+      <c r="CJ20" s="7"/>
+      <c r="CK20" s="7"/>
+      <c r="CL20" s="7"/>
+      <c r="CM20" s="7"/>
       <c r="CN20" s="3"/>
       <c r="CO20" s="3"/>
       <c r="CP20" s="3"/>
@@ -3977,8 +4169,12 @@
       <c r="GW20" s="3"/>
       <c r="GX20" s="3"/>
       <c r="GY20" s="3"/>
+      <c r="GZ20" s="3"/>
+      <c r="HA20" s="3"/>
+      <c r="HB20" s="3"/>
+      <c r="HC20" s="3"/>
     </row>
-    <row r="21" spans="2:207" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:211" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
         <v>28</v>
       </c>
@@ -4011,7 +4207,7 @@
         <v>196.66899999999978</v>
       </c>
       <c r="J21" s="7">
-        <f t="shared" ref="J21:M21" si="8">+J17+J18-J19+J20</f>
+        <f t="shared" ref="J21:O21" si="8">+J17+J18-J19+J20</f>
         <v>-116.60999999999997</v>
       </c>
       <c r="K21" s="7">
@@ -4026,24 +4222,30 @@
         <f t="shared" si="8"/>
         <v>362.85899999999998</v>
       </c>
-      <c r="N21" s="7"/>
-      <c r="O21" s="7"/>
-      <c r="P21" s="7">
-        <f t="shared" ref="P21:R21" si="9">+P17+P18-P19+P20</f>
+      <c r="N21" s="7">
+        <f t="shared" si="8"/>
+        <v>-163.32900000000052</v>
+      </c>
+      <c r="O21" s="7">
+        <f t="shared" si="8"/>
+        <v>-106.89200000000011</v>
+      </c>
+      <c r="P21" s="7"/>
+      <c r="Q21" s="7"/>
+      <c r="R21" s="7"/>
+      <c r="S21" s="7"/>
+      <c r="T21" s="7">
+        <f t="shared" ref="T21:V21" si="9">+T17+T18-T19+T20</f>
         <v>-284.92099999999971</v>
       </c>
-      <c r="Q21" s="7">
+      <c r="U21" s="7">
         <f t="shared" si="9"/>
         <v>145.05100000000033</v>
       </c>
-      <c r="R21" s="7">
+      <c r="V21" s="7">
         <f t="shared" si="9"/>
         <v>341.2179999999999</v>
       </c>
-      <c r="S21" s="7"/>
-      <c r="T21" s="7"/>
-      <c r="U21" s="7"/>
-      <c r="V21" s="7"/>
       <c r="W21" s="7"/>
       <c r="X21" s="7"/>
       <c r="Y21" s="7"/>
@@ -4109,10 +4311,10 @@
       <c r="CG21" s="7"/>
       <c r="CH21" s="7"/>
       <c r="CI21" s="7"/>
-      <c r="CJ21" s="3"/>
-      <c r="CK21" s="3"/>
-      <c r="CL21" s="3"/>
-      <c r="CM21" s="3"/>
+      <c r="CJ21" s="7"/>
+      <c r="CK21" s="7"/>
+      <c r="CL21" s="7"/>
+      <c r="CM21" s="7"/>
       <c r="CN21" s="3"/>
       <c r="CO21" s="3"/>
       <c r="CP21" s="3"/>
@@ -4229,8 +4431,12 @@
       <c r="GW21" s="3"/>
       <c r="GX21" s="3"/>
       <c r="GY21" s="3"/>
+      <c r="GZ21" s="3"/>
+      <c r="HA21" s="3"/>
+      <c r="HB21" s="3"/>
+      <c r="HC21" s="3"/>
     </row>
-    <row r="22" spans="2:207" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:211" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
         <v>29</v>
       </c>
@@ -4263,21 +4469,26 @@
       <c r="M22" s="7">
         <v>62.014000000000003</v>
       </c>
-      <c r="N22" s="7"/>
-      <c r="O22" s="7"/>
-      <c r="P22" s="7">
+      <c r="N22" s="7">
+        <f>+V22-SUM(K22:M22)</f>
+        <v>-44.046999999999997</v>
+      </c>
+      <c r="O22" s="7">
+        <v>-9.74</v>
+      </c>
+      <c r="P22" s="7"/>
+      <c r="Q22" s="7"/>
+      <c r="R22" s="7"/>
+      <c r="S22" s="7"/>
+      <c r="T22" s="7">
         <v>733.55600000000004</v>
       </c>
-      <c r="Q22" s="7">
+      <c r="U22" s="7">
         <v>75.837000000000003</v>
       </c>
-      <c r="R22" s="7">
+      <c r="V22" s="7">
         <v>86.298000000000002</v>
       </c>
-      <c r="S22" s="7"/>
-      <c r="T22" s="7"/>
-      <c r="U22" s="7"/>
-      <c r="V22" s="7"/>
       <c r="W22" s="7"/>
       <c r="X22" s="7"/>
       <c r="Y22" s="7"/>
@@ -4343,10 +4554,10 @@
       <c r="CG22" s="7"/>
       <c r="CH22" s="7"/>
       <c r="CI22" s="7"/>
-      <c r="CJ22" s="3"/>
-      <c r="CK22" s="3"/>
-      <c r="CL22" s="3"/>
-      <c r="CM22" s="3"/>
+      <c r="CJ22" s="7"/>
+      <c r="CK22" s="7"/>
+      <c r="CL22" s="7"/>
+      <c r="CM22" s="7"/>
       <c r="CN22" s="3"/>
       <c r="CO22" s="3"/>
       <c r="CP22" s="3"/>
@@ -4463,8 +4674,12 @@
       <c r="GW22" s="3"/>
       <c r="GX22" s="3"/>
       <c r="GY22" s="3"/>
+      <c r="GZ22" s="3"/>
+      <c r="HA22" s="3"/>
+      <c r="HB22" s="3"/>
+      <c r="HC22" s="3"/>
     </row>
-    <row r="23" spans="2:207" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:211" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
         <v>30</v>
       </c>
@@ -4497,7 +4712,7 @@
         <v>169.10899999999978</v>
       </c>
       <c r="J23" s="7">
-        <f t="shared" ref="J23:M23" si="11">+J21-J22</f>
+        <f t="shared" ref="J23:O24" si="11">+J21-J22</f>
         <v>-150.26699999999997</v>
       </c>
       <c r="K23" s="7">
@@ -4512,24 +4727,30 @@
         <f t="shared" si="11"/>
         <v>300.84499999999997</v>
       </c>
-      <c r="N23" s="7"/>
-      <c r="O23" s="7"/>
-      <c r="P23" s="7">
-        <f t="shared" ref="P23:R23" si="12">+P21-P22</f>
+      <c r="N23" s="7">
+        <f t="shared" si="11"/>
+        <v>-119.28200000000052</v>
+      </c>
+      <c r="O23" s="7">
+        <f t="shared" si="11"/>
+        <v>-97.152000000000115</v>
+      </c>
+      <c r="P23" s="7"/>
+      <c r="Q23" s="7"/>
+      <c r="R23" s="7"/>
+      <c r="S23" s="7"/>
+      <c r="T23" s="7">
+        <f t="shared" ref="T23:V23" si="12">+T21-T22</f>
         <v>-1018.4769999999997</v>
       </c>
-      <c r="Q23" s="7">
+      <c r="U23" s="7">
         <f t="shared" si="12"/>
         <v>69.214000000000325</v>
       </c>
-      <c r="R23" s="7">
+      <c r="V23" s="7">
         <f t="shared" si="12"/>
         <v>254.9199999999999</v>
       </c>
-      <c r="S23" s="7"/>
-      <c r="T23" s="7"/>
-      <c r="U23" s="7"/>
-      <c r="V23" s="7"/>
       <c r="W23" s="7"/>
       <c r="X23" s="7"/>
       <c r="Y23" s="7"/>
@@ -4595,10 +4816,10 @@
       <c r="CG23" s="7"/>
       <c r="CH23" s="7"/>
       <c r="CI23" s="7"/>
-      <c r="CJ23" s="3"/>
-      <c r="CK23" s="3"/>
-      <c r="CL23" s="3"/>
-      <c r="CM23" s="3"/>
+      <c r="CJ23" s="7"/>
+      <c r="CK23" s="7"/>
+      <c r="CL23" s="7"/>
+      <c r="CM23" s="7"/>
       <c r="CN23" s="3"/>
       <c r="CO23" s="3"/>
       <c r="CP23" s="3"/>
@@ -4715,8 +4936,12 @@
       <c r="GW23" s="3"/>
       <c r="GX23" s="3"/>
       <c r="GY23" s="3"/>
+      <c r="GZ23" s="3"/>
+      <c r="HA23" s="3"/>
+      <c r="HB23" s="3"/>
+      <c r="HC23" s="3"/>
     </row>
-    <row r="24" spans="2:207" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:211" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
         <v>31</v>
       </c>
@@ -4749,21 +4974,26 @@
       <c r="M24" s="7">
         <v>0</v>
       </c>
-      <c r="N24" s="7"/>
-      <c r="O24" s="7"/>
-      <c r="P24" s="7">
+      <c r="N24" s="7">
+        <f t="shared" si="11"/>
+        <v>75.235000000000525</v>
+      </c>
+      <c r="O24" s="7">
+        <v>0</v>
+      </c>
+      <c r="P24" s="7"/>
+      <c r="Q24" s="7"/>
+      <c r="R24" s="7"/>
+      <c r="S24" s="7"/>
+      <c r="T24" s="7">
         <v>-49.594999999999999</v>
       </c>
-      <c r="Q24" s="7">
+      <c r="U24" s="7">
         <v>259.04000000000002</v>
       </c>
-      <c r="R24" s="7">
+      <c r="V24" s="7">
         <v>0</v>
       </c>
-      <c r="S24" s="7"/>
-      <c r="T24" s="7"/>
-      <c r="U24" s="7"/>
-      <c r="V24" s="7"/>
       <c r="W24" s="7"/>
       <c r="X24" s="7"/>
       <c r="Y24" s="7"/>
@@ -4829,10 +5059,10 @@
       <c r="CG24" s="7"/>
       <c r="CH24" s="7"/>
       <c r="CI24" s="7"/>
-      <c r="CJ24" s="3"/>
-      <c r="CK24" s="3"/>
-      <c r="CL24" s="3"/>
-      <c r="CM24" s="3"/>
+      <c r="CJ24" s="7"/>
+      <c r="CK24" s="7"/>
+      <c r="CL24" s="7"/>
+      <c r="CM24" s="7"/>
       <c r="CN24" s="3"/>
       <c r="CO24" s="3"/>
       <c r="CP24" s="3"/>
@@ -4949,8 +5179,12 @@
       <c r="GW24" s="3"/>
       <c r="GX24" s="3"/>
       <c r="GY24" s="3"/>
+      <c r="GZ24" s="3"/>
+      <c r="HA24" s="3"/>
+      <c r="HB24" s="3"/>
+      <c r="HC24" s="3"/>
     </row>
-    <row r="25" spans="2:207" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:211" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
         <v>32</v>
       </c>
@@ -4983,7 +5217,7 @@
         <v>167.77999999999977</v>
       </c>
       <c r="J25" s="7">
-        <f t="shared" ref="J25:M25" si="14">+J23-J24</f>
+        <f t="shared" ref="J25:O25" si="14">+J23-J24</f>
         <v>-150.78799999999995</v>
       </c>
       <c r="K25" s="7">
@@ -4998,24 +5232,30 @@
         <f t="shared" si="14"/>
         <v>300.84499999999997</v>
       </c>
-      <c r="N25" s="7"/>
-      <c r="O25" s="7"/>
-      <c r="P25" s="7">
-        <f t="shared" ref="P25:Q25" si="15">+P23-P24</f>
+      <c r="N25" s="7">
+        <f t="shared" si="14"/>
+        <v>-194.51700000000105</v>
+      </c>
+      <c r="O25" s="7">
+        <f t="shared" si="14"/>
+        <v>-97.152000000000115</v>
+      </c>
+      <c r="P25" s="7"/>
+      <c r="Q25" s="7"/>
+      <c r="R25" s="7"/>
+      <c r="S25" s="7"/>
+      <c r="T25" s="7">
+        <f t="shared" ref="T25:U25" si="15">+T23-T24</f>
         <v>-968.88199999999972</v>
       </c>
-      <c r="Q25" s="7">
+      <c r="U25" s="7">
         <f t="shared" si="15"/>
         <v>-189.82599999999968</v>
       </c>
-      <c r="R25" s="7">
-        <f>+R23-R24</f>
+      <c r="V25" s="7">
+        <f>+V23-V24</f>
         <v>254.9199999999999</v>
       </c>
-      <c r="S25" s="7"/>
-      <c r="T25" s="7"/>
-      <c r="U25" s="7"/>
-      <c r="V25" s="7"/>
       <c r="W25" s="7"/>
       <c r="X25" s="7"/>
       <c r="Y25" s="7"/>
@@ -5081,10 +5321,10 @@
       <c r="CG25" s="7"/>
       <c r="CH25" s="7"/>
       <c r="CI25" s="7"/>
-      <c r="CJ25" s="3"/>
-      <c r="CK25" s="3"/>
-      <c r="CL25" s="3"/>
-      <c r="CM25" s="3"/>
+      <c r="CJ25" s="7"/>
+      <c r="CK25" s="7"/>
+      <c r="CL25" s="7"/>
+      <c r="CM25" s="7"/>
       <c r="CN25" s="3"/>
       <c r="CO25" s="3"/>
       <c r="CP25" s="3"/>
@@ -5201,8 +5441,12 @@
       <c r="GW25" s="3"/>
       <c r="GX25" s="3"/>
       <c r="GY25" s="3"/>
+      <c r="GZ25" s="3"/>
+      <c r="HA25" s="3"/>
+      <c r="HB25" s="3"/>
+      <c r="HC25" s="3"/>
     </row>
-    <row r="26" spans="2:207" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:211" x14ac:dyDescent="0.2">
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
@@ -5288,10 +5532,10 @@
       <c r="CG26" s="7"/>
       <c r="CH26" s="7"/>
       <c r="CI26" s="7"/>
-      <c r="CJ26" s="3"/>
-      <c r="CK26" s="3"/>
-      <c r="CL26" s="3"/>
-      <c r="CM26" s="3"/>
+      <c r="CJ26" s="7"/>
+      <c r="CK26" s="7"/>
+      <c r="CL26" s="7"/>
+      <c r="CM26" s="7"/>
       <c r="CN26" s="3"/>
       <c r="CO26" s="3"/>
       <c r="CP26" s="3"/>
@@ -5408,8 +5652,12 @@
       <c r="GW26" s="3"/>
       <c r="GX26" s="3"/>
       <c r="GY26" s="3"/>
+      <c r="GZ26" s="3"/>
+      <c r="HA26" s="3"/>
+      <c r="HB26" s="3"/>
+      <c r="HC26" s="3"/>
     </row>
-    <row r="27" spans="2:207" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:211" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
         <v>33</v>
       </c>
@@ -5426,7 +5674,7 @@
         <v>-0.10930447522162451</v>
       </c>
       <c r="F27" s="9">
-        <f t="shared" ref="F27:M27" si="17">+F25/F28</f>
+        <f t="shared" ref="F27:O27" si="17">+F25/F28</f>
         <v>-1.0765623753406826</v>
       </c>
       <c r="G27" s="9">
@@ -5457,24 +5705,30 @@
         <f t="shared" si="17"/>
         <v>0.7695918550068428</v>
       </c>
-      <c r="N27" s="7"/>
-      <c r="O27" s="7"/>
-      <c r="P27" s="9">
-        <f t="shared" ref="P27:Q27" si="18">+P25/P28</f>
+      <c r="N27" s="9">
+        <f t="shared" si="17"/>
+        <v>-0.49759410613560756</v>
+      </c>
+      <c r="O27" s="9">
+        <f t="shared" si="17"/>
+        <v>-0.24776910384155373</v>
+      </c>
+      <c r="P27" s="7"/>
+      <c r="Q27" s="7"/>
+      <c r="R27" s="7"/>
+      <c r="S27" s="7"/>
+      <c r="T27" s="9">
+        <f t="shared" ref="T27:U27" si="18">+T25/T28</f>
         <v>-2.4971185567010301</v>
       </c>
-      <c r="Q27" s="9">
+      <c r="U27" s="9">
         <f t="shared" si="18"/>
         <v>-0.48779397253515255</v>
       </c>
-      <c r="R27" s="9">
-        <f>+R25/R28</f>
+      <c r="V27" s="9">
+        <f>+V25/V28</f>
         <v>0.65240480218253083</v>
       </c>
-      <c r="S27" s="7"/>
-      <c r="T27" s="7"/>
-      <c r="U27" s="7"/>
-      <c r="V27" s="7"/>
       <c r="W27" s="7"/>
       <c r="X27" s="7"/>
       <c r="Y27" s="7"/>
@@ -5540,10 +5794,10 @@
       <c r="CG27" s="7"/>
       <c r="CH27" s="7"/>
       <c r="CI27" s="7"/>
-      <c r="CJ27" s="3"/>
-      <c r="CK27" s="3"/>
-      <c r="CL27" s="3"/>
-      <c r="CM27" s="3"/>
+      <c r="CJ27" s="7"/>
+      <c r="CK27" s="7"/>
+      <c r="CL27" s="7"/>
+      <c r="CM27" s="7"/>
       <c r="CN27" s="3"/>
       <c r="CO27" s="3"/>
       <c r="CP27" s="3"/>
@@ -5660,8 +5914,12 @@
       <c r="GW27" s="3"/>
       <c r="GX27" s="3"/>
       <c r="GY27" s="3"/>
+      <c r="GZ27" s="3"/>
+      <c r="HA27" s="3"/>
+      <c r="HB27" s="3"/>
+      <c r="HC27" s="3"/>
     </row>
-    <row r="28" spans="2:207" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:211" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
         <v>5</v>
       </c>
@@ -5694,21 +5952,25 @@
       <c r="M28" s="7">
         <v>390.91500000000002</v>
       </c>
-      <c r="N28" s="7"/>
-      <c r="O28" s="7"/>
-      <c r="P28" s="7">
+      <c r="N28" s="7">
+        <v>390.91500000000002</v>
+      </c>
+      <c r="O28" s="7">
+        <v>392.10700000000003</v>
+      </c>
+      <c r="P28" s="7"/>
+      <c r="Q28" s="7"/>
+      <c r="R28" s="7"/>
+      <c r="S28" s="7"/>
+      <c r="T28" s="7">
         <v>388</v>
       </c>
-      <c r="Q28" s="7">
+      <c r="U28" s="7">
         <v>389.15199999999999</v>
       </c>
-      <c r="R28" s="7">
+      <c r="V28" s="7">
         <v>390.73899999999998</v>
       </c>
-      <c r="S28" s="7"/>
-      <c r="T28" s="7"/>
-      <c r="U28" s="7"/>
-      <c r="V28" s="7"/>
       <c r="W28" s="7"/>
       <c r="X28" s="7"/>
       <c r="Y28" s="7"/>
@@ -5774,10 +6036,10 @@
       <c r="CG28" s="7"/>
       <c r="CH28" s="7"/>
       <c r="CI28" s="7"/>
-      <c r="CJ28" s="3"/>
-      <c r="CK28" s="3"/>
-      <c r="CL28" s="3"/>
-      <c r="CM28" s="3"/>
+      <c r="CJ28" s="7"/>
+      <c r="CK28" s="7"/>
+      <c r="CL28" s="7"/>
+      <c r="CM28" s="7"/>
       <c r="CN28" s="3"/>
       <c r="CO28" s="3"/>
       <c r="CP28" s="3"/>
@@ -5894,8 +6156,12 @@
       <c r="GW28" s="3"/>
       <c r="GX28" s="3"/>
       <c r="GY28" s="3"/>
+      <c r="GZ28" s="3"/>
+      <c r="HA28" s="3"/>
+      <c r="HB28" s="3"/>
+      <c r="HC28" s="3"/>
     </row>
-    <row r="29" spans="2:207" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:211" x14ac:dyDescent="0.2">
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
@@ -5981,10 +6247,10 @@
       <c r="CG29" s="7"/>
       <c r="CH29" s="7"/>
       <c r="CI29" s="7"/>
-      <c r="CJ29" s="3"/>
-      <c r="CK29" s="3"/>
-      <c r="CL29" s="3"/>
-      <c r="CM29" s="3"/>
+      <c r="CJ29" s="7"/>
+      <c r="CK29" s="7"/>
+      <c r="CL29" s="7"/>
+      <c r="CM29" s="7"/>
       <c r="CN29" s="3"/>
       <c r="CO29" s="3"/>
       <c r="CP29" s="3"/>
@@ -6101,8 +6367,12 @@
       <c r="GW29" s="3"/>
       <c r="GX29" s="3"/>
       <c r="GY29" s="3"/>
+      <c r="GZ29" s="3"/>
+      <c r="HA29" s="3"/>
+      <c r="HB29" s="3"/>
+      <c r="HC29" s="3"/>
     </row>
-    <row r="30" spans="2:207" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:211" x14ac:dyDescent="0.2">
       <c r="B30" s="1" t="s">
         <v>48</v>
       </c>
@@ -6138,17 +6408,23 @@
         <f>+M12/I12-1</f>
         <v>1.4781334071064967E-2</v>
       </c>
-      <c r="N30" s="8"/>
-      <c r="O30" s="8"/>
+      <c r="N30" s="12">
+        <f t="shared" ref="N30:O30" si="20">+N12/J12-1</f>
+        <v>1.0384971155967371E-2</v>
+      </c>
+      <c r="O30" s="12">
+        <f t="shared" si="20"/>
+        <v>-5.1847993884132526E-2</v>
+      </c>
       <c r="P30" s="8"/>
       <c r="Q30" s="8"/>
       <c r="R30" s="8"/>
       <c r="S30" s="8"/>
       <c r="T30" s="8"/>
-      <c r="U30" s="7"/>
-      <c r="V30" s="7"/>
-      <c r="W30" s="7"/>
-      <c r="X30" s="7"/>
+      <c r="U30" s="8"/>
+      <c r="V30" s="8"/>
+      <c r="W30" s="8"/>
+      <c r="X30" s="8"/>
       <c r="Y30" s="7"/>
       <c r="Z30" s="7"/>
       <c r="AA30" s="7"/>
@@ -6212,10 +6488,10 @@
       <c r="CG30" s="7"/>
       <c r="CH30" s="7"/>
       <c r="CI30" s="7"/>
-      <c r="CJ30" s="3"/>
-      <c r="CK30" s="3"/>
-      <c r="CL30" s="3"/>
-      <c r="CM30" s="3"/>
+      <c r="CJ30" s="7"/>
+      <c r="CK30" s="7"/>
+      <c r="CL30" s="7"/>
+      <c r="CM30" s="7"/>
       <c r="CN30" s="3"/>
       <c r="CO30" s="3"/>
       <c r="CP30" s="3"/>
@@ -6332,45 +6608,49 @@
       <c r="GW30" s="3"/>
       <c r="GX30" s="3"/>
       <c r="GY30" s="3"/>
+      <c r="GZ30" s="3"/>
+      <c r="HA30" s="3"/>
+      <c r="HB30" s="3"/>
+      <c r="HC30" s="3"/>
     </row>
-    <row r="31" spans="2:207" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:211" x14ac:dyDescent="0.2">
       <c r="B31" s="11" t="s">
         <v>49</v>
       </c>
       <c r="C31" s="13" t="e">
-        <f t="shared" ref="C31" si="20">+C14/C12</f>
+        <f t="shared" ref="C31" si="21">+C14/C12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D31" s="13" t="e">
-        <f t="shared" ref="D31:K31" si="21">+D14/D12</f>
+        <f t="shared" ref="D31:K31" si="22">+D14/D12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E31" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.54636690820856382</v>
       </c>
       <c r="F31" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.47832374700640495</v>
       </c>
       <c r="G31" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.51195437124800747</v>
       </c>
       <c r="H31" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.52232928249553645</v>
       </c>
       <c r="I31" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.56288762671529669</v>
       </c>
       <c r="J31" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.53291886120299237</v>
       </c>
       <c r="K31" s="13">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.53900171866782232</v>
       </c>
       <c r="L31" s="13">
@@ -6381,8 +6661,14 @@
         <f>+M14/M12</f>
         <v>0.56622172396490578</v>
       </c>
-      <c r="N31" s="7"/>
-      <c r="O31" s="7"/>
+      <c r="N31" s="13">
+        <f t="shared" ref="N31:O31" si="23">+N14/N12</f>
+        <v>0.56413149562749232</v>
+      </c>
+      <c r="O31" s="13">
+        <f t="shared" si="23"/>
+        <v>0.54933241642550912</v>
+      </c>
       <c r="P31" s="7"/>
       <c r="Q31" s="7"/>
       <c r="R31" s="7"/>
@@ -6455,10 +6741,10 @@
       <c r="CG31" s="7"/>
       <c r="CH31" s="7"/>
       <c r="CI31" s="7"/>
-      <c r="CJ31" s="3"/>
-      <c r="CK31" s="3"/>
-      <c r="CL31" s="3"/>
-      <c r="CM31" s="3"/>
+      <c r="CJ31" s="7"/>
+      <c r="CK31" s="7"/>
+      <c r="CL31" s="7"/>
+      <c r="CM31" s="7"/>
       <c r="CN31" s="3"/>
       <c r="CO31" s="3"/>
       <c r="CP31" s="3"/>
@@ -6575,45 +6861,49 @@
       <c r="GW31" s="3"/>
       <c r="GX31" s="3"/>
       <c r="GY31" s="3"/>
+      <c r="GZ31" s="3"/>
+      <c r="HA31" s="3"/>
+      <c r="HB31" s="3"/>
+      <c r="HC31" s="3"/>
     </row>
-    <row r="32" spans="2:207" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:211" x14ac:dyDescent="0.2">
       <c r="B32" s="11" t="s">
         <v>50</v>
       </c>
       <c r="C32" s="13" t="e">
-        <f t="shared" ref="C32" si="22">+C17/C12</f>
+        <f t="shared" ref="C32" si="24">+C17/C12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D32" s="13" t="e">
-        <f t="shared" ref="D32:K32" si="23">+D17/D12</f>
+        <f t="shared" ref="D32:K32" si="25">+D17/D12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E32" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-3.2818573092381391E-2</v>
       </c>
       <c r="F32" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-0.16614752471634839</v>
       </c>
       <c r="G32" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-6.9539755576407861E-2</v>
       </c>
       <c r="H32" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>9.9314055232368345E-2</v>
       </c>
       <c r="I32" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>7.9669728629541012E-2</v>
       </c>
       <c r="J32" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-3.3999433708171239E-2</v>
       </c>
       <c r="K32" s="13">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>-4.9191044752383561E-2</v>
       </c>
       <c r="L32" s="13">
@@ -6624,8 +6914,14 @@
         <f>+M17/M12</f>
         <v>0.10051251807757212</v>
       </c>
-      <c r="N32" s="7"/>
-      <c r="O32" s="7"/>
+      <c r="N32" s="13">
+        <f t="shared" ref="N32:O32" si="26">+N17/N12</f>
+        <v>2.8394752806280725E-2</v>
+      </c>
+      <c r="O32" s="13">
+        <f t="shared" si="26"/>
+        <v>-4.9762216968106177E-2</v>
+      </c>
       <c r="P32" s="7"/>
       <c r="Q32" s="7"/>
       <c r="R32" s="7"/>
@@ -6698,10 +6994,10 @@
       <c r="CG32" s="7"/>
       <c r="CH32" s="7"/>
       <c r="CI32" s="7"/>
-      <c r="CJ32" s="3"/>
-      <c r="CK32" s="3"/>
-      <c r="CL32" s="3"/>
-      <c r="CM32" s="3"/>
+      <c r="CJ32" s="7"/>
+      <c r="CK32" s="7"/>
+      <c r="CL32" s="7"/>
+      <c r="CM32" s="7"/>
       <c r="CN32" s="3"/>
       <c r="CO32" s="3"/>
       <c r="CP32" s="3"/>
@@ -6818,45 +7114,49 @@
       <c r="GW32" s="3"/>
       <c r="GX32" s="3"/>
       <c r="GY32" s="3"/>
+      <c r="GZ32" s="3"/>
+      <c r="HA32" s="3"/>
+      <c r="HB32" s="3"/>
+      <c r="HC32" s="3"/>
     </row>
-    <row r="33" spans="2:207" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:211" x14ac:dyDescent="0.2">
       <c r="B33" s="11" t="s">
         <v>51</v>
       </c>
       <c r="C33" s="13" t="e">
-        <f t="shared" ref="C33" si="24">+C22/C21</f>
+        <f t="shared" ref="C33" si="27">+C22/C21</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D33" s="13" t="e">
-        <f t="shared" ref="D33:K33" si="25">+D22/D21</f>
+        <f t="shared" ref="D33:K33" si="28">+D22/D21</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E33" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0.17602888605457423</v>
       </c>
       <c r="F33" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>-8.7428721306379313E-4</v>
       </c>
       <c r="G33" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>8.1146911811813591E-2</v>
       </c>
       <c r="H33" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0.12164559432673341</v>
       </c>
       <c r="I33" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>0.1401339306143827</v>
       </c>
       <c r="J33" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>-0.28862876254180608</v>
       </c>
       <c r="K33" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>8.0454685488139055E-2</v>
       </c>
       <c r="L33" s="13">
@@ -6867,8 +7167,14 @@
         <f>+M22/M21</f>
         <v>0.17090384970470626</v>
       </c>
-      <c r="N33" s="7"/>
-      <c r="O33" s="7"/>
+      <c r="N33" s="13">
+        <f t="shared" ref="N33:O33" si="29">+N22/N21</f>
+        <v>0.26968266505029637</v>
+      </c>
+      <c r="O33" s="13">
+        <f t="shared" si="29"/>
+        <v>9.1120008981027484E-2</v>
+      </c>
       <c r="P33" s="7"/>
       <c r="Q33" s="7"/>
       <c r="R33" s="7"/>
@@ -6941,10 +7247,10 @@
       <c r="CG33" s="7"/>
       <c r="CH33" s="7"/>
       <c r="CI33" s="7"/>
-      <c r="CJ33" s="3"/>
-      <c r="CK33" s="3"/>
-      <c r="CL33" s="3"/>
-      <c r="CM33" s="3"/>
+      <c r="CJ33" s="7"/>
+      <c r="CK33" s="7"/>
+      <c r="CL33" s="7"/>
+      <c r="CM33" s="7"/>
       <c r="CN33" s="3"/>
       <c r="CO33" s="3"/>
       <c r="CP33" s="3"/>
@@ -7061,8 +7367,12 @@
       <c r="GW33" s="3"/>
       <c r="GX33" s="3"/>
       <c r="GY33" s="3"/>
+      <c r="GZ33" s="3"/>
+      <c r="HA33" s="3"/>
+      <c r="HB33" s="3"/>
+      <c r="HC33" s="3"/>
     </row>
-    <row r="34" spans="2:207" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:211" x14ac:dyDescent="0.2">
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
       <c r="E34" s="7"/>
@@ -7148,10 +7458,10 @@
       <c r="CG34" s="7"/>
       <c r="CH34" s="7"/>
       <c r="CI34" s="7"/>
-      <c r="CJ34" s="3"/>
-      <c r="CK34" s="3"/>
-      <c r="CL34" s="3"/>
-      <c r="CM34" s="3"/>
+      <c r="CJ34" s="7"/>
+      <c r="CK34" s="7"/>
+      <c r="CL34" s="7"/>
+      <c r="CM34" s="7"/>
       <c r="CN34" s="3"/>
       <c r="CO34" s="3"/>
       <c r="CP34" s="3"/>
@@ -7268,8 +7578,12 @@
       <c r="GW34" s="3"/>
       <c r="GX34" s="3"/>
       <c r="GY34" s="3"/>
+      <c r="GZ34" s="3"/>
+      <c r="HA34" s="3"/>
+      <c r="HB34" s="3"/>
+      <c r="HC34" s="3"/>
     </row>
-    <row r="35" spans="2:207" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:211" x14ac:dyDescent="0.2">
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
       <c r="E35" s="7"/>
@@ -7355,10 +7669,10 @@
       <c r="CG35" s="7"/>
       <c r="CH35" s="7"/>
       <c r="CI35" s="7"/>
-      <c r="CJ35" s="3"/>
-      <c r="CK35" s="3"/>
-      <c r="CL35" s="3"/>
-      <c r="CM35" s="3"/>
+      <c r="CJ35" s="7"/>
+      <c r="CK35" s="7"/>
+      <c r="CL35" s="7"/>
+      <c r="CM35" s="7"/>
       <c r="CN35" s="3"/>
       <c r="CO35" s="3"/>
       <c r="CP35" s="3"/>
@@ -7475,8 +7789,12 @@
       <c r="GW35" s="3"/>
       <c r="GX35" s="3"/>
       <c r="GY35" s="3"/>
+      <c r="GZ35" s="3"/>
+      <c r="HA35" s="3"/>
+      <c r="HB35" s="3"/>
+      <c r="HC35" s="3"/>
     </row>
-    <row r="36" spans="2:207" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:211" x14ac:dyDescent="0.2">
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
       <c r="E36" s="7"/>
@@ -7562,10 +7880,10 @@
       <c r="CG36" s="7"/>
       <c r="CH36" s="7"/>
       <c r="CI36" s="7"/>
-      <c r="CJ36" s="3"/>
-      <c r="CK36" s="3"/>
-      <c r="CL36" s="3"/>
-      <c r="CM36" s="3"/>
+      <c r="CJ36" s="7"/>
+      <c r="CK36" s="7"/>
+      <c r="CL36" s="7"/>
+      <c r="CM36" s="7"/>
       <c r="CN36" s="3"/>
       <c r="CO36" s="3"/>
       <c r="CP36" s="3"/>
@@ -7682,8 +8000,12 @@
       <c r="GW36" s="3"/>
       <c r="GX36" s="3"/>
       <c r="GY36" s="3"/>
+      <c r="GZ36" s="3"/>
+      <c r="HA36" s="3"/>
+      <c r="HB36" s="3"/>
+      <c r="HC36" s="3"/>
     </row>
-    <row r="37" spans="2:207" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:211" x14ac:dyDescent="0.2">
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
       <c r="E37" s="7"/>
@@ -7769,10 +8091,10 @@
       <c r="CG37" s="7"/>
       <c r="CH37" s="7"/>
       <c r="CI37" s="7"/>
-      <c r="CJ37" s="3"/>
-      <c r="CK37" s="3"/>
-      <c r="CL37" s="3"/>
-      <c r="CM37" s="3"/>
+      <c r="CJ37" s="7"/>
+      <c r="CK37" s="7"/>
+      <c r="CL37" s="7"/>
+      <c r="CM37" s="7"/>
       <c r="CN37" s="3"/>
       <c r="CO37" s="3"/>
       <c r="CP37" s="3"/>
@@ -7889,8 +8211,12 @@
       <c r="GW37" s="3"/>
       <c r="GX37" s="3"/>
       <c r="GY37" s="3"/>
+      <c r="GZ37" s="3"/>
+      <c r="HA37" s="3"/>
+      <c r="HB37" s="3"/>
+      <c r="HC37" s="3"/>
     </row>
-    <row r="38" spans="2:207" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:211" x14ac:dyDescent="0.2">
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
@@ -7976,10 +8302,10 @@
       <c r="CG38" s="7"/>
       <c r="CH38" s="7"/>
       <c r="CI38" s="7"/>
-      <c r="CJ38" s="3"/>
-      <c r="CK38" s="3"/>
-      <c r="CL38" s="3"/>
-      <c r="CM38" s="3"/>
+      <c r="CJ38" s="7"/>
+      <c r="CK38" s="7"/>
+      <c r="CL38" s="7"/>
+      <c r="CM38" s="7"/>
       <c r="CN38" s="3"/>
       <c r="CO38" s="3"/>
       <c r="CP38" s="3"/>
@@ -8096,8 +8422,12 @@
       <c r="GW38" s="3"/>
       <c r="GX38" s="3"/>
       <c r="GY38" s="3"/>
+      <c r="GZ38" s="3"/>
+      <c r="HA38" s="3"/>
+      <c r="HB38" s="3"/>
+      <c r="HC38" s="3"/>
     </row>
-    <row r="39" spans="2:207" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:211" x14ac:dyDescent="0.2">
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
       <c r="E39" s="7"/>
@@ -8183,10 +8513,10 @@
       <c r="CG39" s="7"/>
       <c r="CH39" s="7"/>
       <c r="CI39" s="7"/>
-      <c r="CJ39" s="3"/>
-      <c r="CK39" s="3"/>
-      <c r="CL39" s="3"/>
-      <c r="CM39" s="3"/>
+      <c r="CJ39" s="7"/>
+      <c r="CK39" s="7"/>
+      <c r="CL39" s="7"/>
+      <c r="CM39" s="7"/>
       <c r="CN39" s="3"/>
       <c r="CO39" s="3"/>
       <c r="CP39" s="3"/>
@@ -8303,8 +8633,12 @@
       <c r="GW39" s="3"/>
       <c r="GX39" s="3"/>
       <c r="GY39" s="3"/>
+      <c r="GZ39" s="3"/>
+      <c r="HA39" s="3"/>
+      <c r="HB39" s="3"/>
+      <c r="HC39" s="3"/>
     </row>
-    <row r="40" spans="2:207" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:211" x14ac:dyDescent="0.2">
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
       <c r="E40" s="7"/>
@@ -8390,10 +8724,10 @@
       <c r="CG40" s="7"/>
       <c r="CH40" s="7"/>
       <c r="CI40" s="7"/>
-      <c r="CJ40" s="3"/>
-      <c r="CK40" s="3"/>
-      <c r="CL40" s="3"/>
-      <c r="CM40" s="3"/>
+      <c r="CJ40" s="7"/>
+      <c r="CK40" s="7"/>
+      <c r="CL40" s="7"/>
+      <c r="CM40" s="7"/>
       <c r="CN40" s="3"/>
       <c r="CO40" s="3"/>
       <c r="CP40" s="3"/>
@@ -8510,8 +8844,12 @@
       <c r="GW40" s="3"/>
       <c r="GX40" s="3"/>
       <c r="GY40" s="3"/>
+      <c r="GZ40" s="3"/>
+      <c r="HA40" s="3"/>
+      <c r="HB40" s="3"/>
+      <c r="HC40" s="3"/>
     </row>
-    <row r="41" spans="2:207" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:211" x14ac:dyDescent="0.2">
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
       <c r="E41" s="7"/>
@@ -8597,10 +8935,10 @@
       <c r="CG41" s="7"/>
       <c r="CH41" s="7"/>
       <c r="CI41" s="7"/>
-      <c r="CJ41" s="3"/>
-      <c r="CK41" s="3"/>
-      <c r="CL41" s="3"/>
-      <c r="CM41" s="3"/>
+      <c r="CJ41" s="7"/>
+      <c r="CK41" s="7"/>
+      <c r="CL41" s="7"/>
+      <c r="CM41" s="7"/>
       <c r="CN41" s="3"/>
       <c r="CO41" s="3"/>
       <c r="CP41" s="3"/>
@@ -8717,8 +9055,12 @@
       <c r="GW41" s="3"/>
       <c r="GX41" s="3"/>
       <c r="GY41" s="3"/>
+      <c r="GZ41" s="3"/>
+      <c r="HA41" s="3"/>
+      <c r="HB41" s="3"/>
+      <c r="HC41" s="3"/>
     </row>
-    <row r="42" spans="2:207" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:211" x14ac:dyDescent="0.2">
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
       <c r="E42" s="7"/>
@@ -8804,10 +9146,10 @@
       <c r="CG42" s="7"/>
       <c r="CH42" s="7"/>
       <c r="CI42" s="7"/>
-      <c r="CJ42" s="3"/>
-      <c r="CK42" s="3"/>
-      <c r="CL42" s="3"/>
-      <c r="CM42" s="3"/>
+      <c r="CJ42" s="7"/>
+      <c r="CK42" s="7"/>
+      <c r="CL42" s="7"/>
+      <c r="CM42" s="7"/>
       <c r="CN42" s="3"/>
       <c r="CO42" s="3"/>
       <c r="CP42" s="3"/>
@@ -8924,8 +9266,12 @@
       <c r="GW42" s="3"/>
       <c r="GX42" s="3"/>
       <c r="GY42" s="3"/>
+      <c r="GZ42" s="3"/>
+      <c r="HA42" s="3"/>
+      <c r="HB42" s="3"/>
+      <c r="HC42" s="3"/>
     </row>
-    <row r="43" spans="2:207" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:211" x14ac:dyDescent="0.2">
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
@@ -9011,10 +9357,10 @@
       <c r="CG43" s="7"/>
       <c r="CH43" s="7"/>
       <c r="CI43" s="7"/>
-      <c r="CJ43" s="3"/>
-      <c r="CK43" s="3"/>
-      <c r="CL43" s="3"/>
-      <c r="CM43" s="3"/>
+      <c r="CJ43" s="7"/>
+      <c r="CK43" s="7"/>
+      <c r="CL43" s="7"/>
+      <c r="CM43" s="7"/>
       <c r="CN43" s="3"/>
       <c r="CO43" s="3"/>
       <c r="CP43" s="3"/>
@@ -9131,8 +9477,12 @@
       <c r="GW43" s="3"/>
       <c r="GX43" s="3"/>
       <c r="GY43" s="3"/>
+      <c r="GZ43" s="3"/>
+      <c r="HA43" s="3"/>
+      <c r="HB43" s="3"/>
+      <c r="HC43" s="3"/>
     </row>
-    <row r="44" spans="2:207" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:211" x14ac:dyDescent="0.2">
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
       <c r="E44" s="7"/>
@@ -9218,10 +9568,10 @@
       <c r="CG44" s="7"/>
       <c r="CH44" s="7"/>
       <c r="CI44" s="7"/>
-      <c r="CJ44" s="3"/>
-      <c r="CK44" s="3"/>
-      <c r="CL44" s="3"/>
-      <c r="CM44" s="3"/>
+      <c r="CJ44" s="7"/>
+      <c r="CK44" s="7"/>
+      <c r="CL44" s="7"/>
+      <c r="CM44" s="7"/>
       <c r="CN44" s="3"/>
       <c r="CO44" s="3"/>
       <c r="CP44" s="3"/>
@@ -9338,8 +9688,12 @@
       <c r="GW44" s="3"/>
       <c r="GX44" s="3"/>
       <c r="GY44" s="3"/>
+      <c r="GZ44" s="3"/>
+      <c r="HA44" s="3"/>
+      <c r="HB44" s="3"/>
+      <c r="HC44" s="3"/>
     </row>
-    <row r="45" spans="2:207" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:211" x14ac:dyDescent="0.2">
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
@@ -9425,10 +9779,10 @@
       <c r="CG45" s="7"/>
       <c r="CH45" s="7"/>
       <c r="CI45" s="7"/>
-      <c r="CJ45" s="3"/>
-      <c r="CK45" s="3"/>
-      <c r="CL45" s="3"/>
-      <c r="CM45" s="3"/>
+      <c r="CJ45" s="7"/>
+      <c r="CK45" s="7"/>
+      <c r="CL45" s="7"/>
+      <c r="CM45" s="7"/>
       <c r="CN45" s="3"/>
       <c r="CO45" s="3"/>
       <c r="CP45" s="3"/>
@@ -9545,8 +9899,12 @@
       <c r="GW45" s="3"/>
       <c r="GX45" s="3"/>
       <c r="GY45" s="3"/>
+      <c r="GZ45" s="3"/>
+      <c r="HA45" s="3"/>
+      <c r="HB45" s="3"/>
+      <c r="HC45" s="3"/>
     </row>
-    <row r="46" spans="2:207" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:211" x14ac:dyDescent="0.2">
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
@@ -9632,10 +9990,10 @@
       <c r="CG46" s="7"/>
       <c r="CH46" s="7"/>
       <c r="CI46" s="7"/>
-      <c r="CJ46" s="3"/>
-      <c r="CK46" s="3"/>
-      <c r="CL46" s="3"/>
-      <c r="CM46" s="3"/>
+      <c r="CJ46" s="7"/>
+      <c r="CK46" s="7"/>
+      <c r="CL46" s="7"/>
+      <c r="CM46" s="7"/>
       <c r="CN46" s="3"/>
       <c r="CO46" s="3"/>
       <c r="CP46" s="3"/>
@@ -9752,8 +10110,12 @@
       <c r="GW46" s="3"/>
       <c r="GX46" s="3"/>
       <c r="GY46" s="3"/>
+      <c r="GZ46" s="3"/>
+      <c r="HA46" s="3"/>
+      <c r="HB46" s="3"/>
+      <c r="HC46" s="3"/>
     </row>
-    <row r="47" spans="2:207" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:211" x14ac:dyDescent="0.2">
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
@@ -9839,10 +10201,10 @@
       <c r="CG47" s="7"/>
       <c r="CH47" s="7"/>
       <c r="CI47" s="7"/>
-      <c r="CJ47" s="3"/>
-      <c r="CK47" s="3"/>
-      <c r="CL47" s="3"/>
-      <c r="CM47" s="3"/>
+      <c r="CJ47" s="7"/>
+      <c r="CK47" s="7"/>
+      <c r="CL47" s="7"/>
+      <c r="CM47" s="7"/>
       <c r="CN47" s="3"/>
       <c r="CO47" s="3"/>
       <c r="CP47" s="3"/>
@@ -9959,8 +10321,12 @@
       <c r="GW47" s="3"/>
       <c r="GX47" s="3"/>
       <c r="GY47" s="3"/>
+      <c r="GZ47" s="3"/>
+      <c r="HA47" s="3"/>
+      <c r="HB47" s="3"/>
+      <c r="HC47" s="3"/>
     </row>
-    <row r="48" spans="2:207" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:211" x14ac:dyDescent="0.2">
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
       <c r="E48" s="7"/>
@@ -10046,10 +10412,10 @@
       <c r="CG48" s="7"/>
       <c r="CH48" s="7"/>
       <c r="CI48" s="7"/>
-      <c r="CJ48" s="3"/>
-      <c r="CK48" s="3"/>
-      <c r="CL48" s="3"/>
-      <c r="CM48" s="3"/>
+      <c r="CJ48" s="7"/>
+      <c r="CK48" s="7"/>
+      <c r="CL48" s="7"/>
+      <c r="CM48" s="7"/>
       <c r="CN48" s="3"/>
       <c r="CO48" s="3"/>
       <c r="CP48" s="3"/>
@@ -10166,8 +10532,12 @@
       <c r="GW48" s="3"/>
       <c r="GX48" s="3"/>
       <c r="GY48" s="3"/>
+      <c r="GZ48" s="3"/>
+      <c r="HA48" s="3"/>
+      <c r="HB48" s="3"/>
+      <c r="HC48" s="3"/>
     </row>
-    <row r="49" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C49" s="7"/>
       <c r="D49" s="7"/>
       <c r="E49" s="7"/>
@@ -10253,10 +10623,10 @@
       <c r="CG49" s="7"/>
       <c r="CH49" s="7"/>
       <c r="CI49" s="7"/>
-      <c r="CJ49" s="3"/>
-      <c r="CK49" s="3"/>
-      <c r="CL49" s="3"/>
-      <c r="CM49" s="3"/>
+      <c r="CJ49" s="7"/>
+      <c r="CK49" s="7"/>
+      <c r="CL49" s="7"/>
+      <c r="CM49" s="7"/>
       <c r="CN49" s="3"/>
       <c r="CO49" s="3"/>
       <c r="CP49" s="3"/>
@@ -10373,8 +10743,12 @@
       <c r="GW49" s="3"/>
       <c r="GX49" s="3"/>
       <c r="GY49" s="3"/>
+      <c r="GZ49" s="3"/>
+      <c r="HA49" s="3"/>
+      <c r="HB49" s="3"/>
+      <c r="HC49" s="3"/>
     </row>
-    <row r="50" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C50" s="7"/>
       <c r="D50" s="7"/>
       <c r="E50" s="7"/>
@@ -10460,10 +10834,10 @@
       <c r="CG50" s="7"/>
       <c r="CH50" s="7"/>
       <c r="CI50" s="7"/>
-      <c r="CJ50" s="3"/>
-      <c r="CK50" s="3"/>
-      <c r="CL50" s="3"/>
-      <c r="CM50" s="3"/>
+      <c r="CJ50" s="7"/>
+      <c r="CK50" s="7"/>
+      <c r="CL50" s="7"/>
+      <c r="CM50" s="7"/>
       <c r="CN50" s="3"/>
       <c r="CO50" s="3"/>
       <c r="CP50" s="3"/>
@@ -10580,8 +10954,12 @@
       <c r="GW50" s="3"/>
       <c r="GX50" s="3"/>
       <c r="GY50" s="3"/>
+      <c r="GZ50" s="3"/>
+      <c r="HA50" s="3"/>
+      <c r="HB50" s="3"/>
+      <c r="HC50" s="3"/>
     </row>
-    <row r="51" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C51" s="7"/>
       <c r="D51" s="7"/>
       <c r="E51" s="7"/>
@@ -10667,10 +11045,10 @@
       <c r="CG51" s="7"/>
       <c r="CH51" s="7"/>
       <c r="CI51" s="7"/>
-      <c r="CJ51" s="3"/>
-      <c r="CK51" s="3"/>
-      <c r="CL51" s="3"/>
-      <c r="CM51" s="3"/>
+      <c r="CJ51" s="7"/>
+      <c r="CK51" s="7"/>
+      <c r="CL51" s="7"/>
+      <c r="CM51" s="7"/>
       <c r="CN51" s="3"/>
       <c r="CO51" s="3"/>
       <c r="CP51" s="3"/>
@@ -10787,8 +11165,12 @@
       <c r="GW51" s="3"/>
       <c r="GX51" s="3"/>
       <c r="GY51" s="3"/>
+      <c r="GZ51" s="3"/>
+      <c r="HA51" s="3"/>
+      <c r="HB51" s="3"/>
+      <c r="HC51" s="3"/>
     </row>
-    <row r="52" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C52" s="7"/>
       <c r="D52" s="7"/>
       <c r="E52" s="7"/>
@@ -10874,10 +11256,10 @@
       <c r="CG52" s="7"/>
       <c r="CH52" s="7"/>
       <c r="CI52" s="7"/>
-      <c r="CJ52" s="3"/>
-      <c r="CK52" s="3"/>
-      <c r="CL52" s="3"/>
-      <c r="CM52" s="3"/>
+      <c r="CJ52" s="7"/>
+      <c r="CK52" s="7"/>
+      <c r="CL52" s="7"/>
+      <c r="CM52" s="7"/>
       <c r="CN52" s="3"/>
       <c r="CO52" s="3"/>
       <c r="CP52" s="3"/>
@@ -10994,8 +11376,12 @@
       <c r="GW52" s="3"/>
       <c r="GX52" s="3"/>
       <c r="GY52" s="3"/>
+      <c r="GZ52" s="3"/>
+      <c r="HA52" s="3"/>
+      <c r="HB52" s="3"/>
+      <c r="HC52" s="3"/>
     </row>
-    <row r="53" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C53" s="7"/>
       <c r="D53" s="7"/>
       <c r="E53" s="7"/>
@@ -11081,10 +11467,10 @@
       <c r="CG53" s="7"/>
       <c r="CH53" s="7"/>
       <c r="CI53" s="7"/>
-      <c r="CJ53" s="3"/>
-      <c r="CK53" s="3"/>
-      <c r="CL53" s="3"/>
-      <c r="CM53" s="3"/>
+      <c r="CJ53" s="7"/>
+      <c r="CK53" s="7"/>
+      <c r="CL53" s="7"/>
+      <c r="CM53" s="7"/>
       <c r="CN53" s="3"/>
       <c r="CO53" s="3"/>
       <c r="CP53" s="3"/>
@@ -11201,8 +11587,12 @@
       <c r="GW53" s="3"/>
       <c r="GX53" s="3"/>
       <c r="GY53" s="3"/>
+      <c r="GZ53" s="3"/>
+      <c r="HA53" s="3"/>
+      <c r="HB53" s="3"/>
+      <c r="HC53" s="3"/>
     </row>
-    <row r="54" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
       <c r="E54" s="7"/>
@@ -11288,10 +11678,10 @@
       <c r="CG54" s="7"/>
       <c r="CH54" s="7"/>
       <c r="CI54" s="7"/>
-      <c r="CJ54" s="3"/>
-      <c r="CK54" s="3"/>
-      <c r="CL54" s="3"/>
-      <c r="CM54" s="3"/>
+      <c r="CJ54" s="7"/>
+      <c r="CK54" s="7"/>
+      <c r="CL54" s="7"/>
+      <c r="CM54" s="7"/>
       <c r="CN54" s="3"/>
       <c r="CO54" s="3"/>
       <c r="CP54" s="3"/>
@@ -11408,8 +11798,12 @@
       <c r="GW54" s="3"/>
       <c r="GX54" s="3"/>
       <c r="GY54" s="3"/>
+      <c r="GZ54" s="3"/>
+      <c r="HA54" s="3"/>
+      <c r="HB54" s="3"/>
+      <c r="HC54" s="3"/>
     </row>
-    <row r="55" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C55" s="7"/>
       <c r="D55" s="7"/>
       <c r="E55" s="7"/>
@@ -11495,10 +11889,10 @@
       <c r="CG55" s="7"/>
       <c r="CH55" s="7"/>
       <c r="CI55" s="7"/>
-      <c r="CJ55" s="3"/>
-      <c r="CK55" s="3"/>
-      <c r="CL55" s="3"/>
-      <c r="CM55" s="3"/>
+      <c r="CJ55" s="7"/>
+      <c r="CK55" s="7"/>
+      <c r="CL55" s="7"/>
+      <c r="CM55" s="7"/>
       <c r="CN55" s="3"/>
       <c r="CO55" s="3"/>
       <c r="CP55" s="3"/>
@@ -11615,8 +12009,12 @@
       <c r="GW55" s="3"/>
       <c r="GX55" s="3"/>
       <c r="GY55" s="3"/>
+      <c r="GZ55" s="3"/>
+      <c r="HA55" s="3"/>
+      <c r="HB55" s="3"/>
+      <c r="HC55" s="3"/>
     </row>
-    <row r="56" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C56" s="7"/>
       <c r="D56" s="7"/>
       <c r="E56" s="7"/>
@@ -11702,10 +12100,10 @@
       <c r="CG56" s="7"/>
       <c r="CH56" s="7"/>
       <c r="CI56" s="7"/>
-      <c r="CJ56" s="3"/>
-      <c r="CK56" s="3"/>
-      <c r="CL56" s="3"/>
-      <c r="CM56" s="3"/>
+      <c r="CJ56" s="7"/>
+      <c r="CK56" s="7"/>
+      <c r="CL56" s="7"/>
+      <c r="CM56" s="7"/>
       <c r="CN56" s="3"/>
       <c r="CO56" s="3"/>
       <c r="CP56" s="3"/>
@@ -11822,8 +12220,12 @@
       <c r="GW56" s="3"/>
       <c r="GX56" s="3"/>
       <c r="GY56" s="3"/>
+      <c r="GZ56" s="3"/>
+      <c r="HA56" s="3"/>
+      <c r="HB56" s="3"/>
+      <c r="HC56" s="3"/>
     </row>
-    <row r="57" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
       <c r="E57" s="7"/>
@@ -11909,10 +12311,10 @@
       <c r="CG57" s="7"/>
       <c r="CH57" s="7"/>
       <c r="CI57" s="7"/>
-      <c r="CJ57" s="3"/>
-      <c r="CK57" s="3"/>
-      <c r="CL57" s="3"/>
-      <c r="CM57" s="3"/>
+      <c r="CJ57" s="7"/>
+      <c r="CK57" s="7"/>
+      <c r="CL57" s="7"/>
+      <c r="CM57" s="7"/>
       <c r="CN57" s="3"/>
       <c r="CO57" s="3"/>
       <c r="CP57" s="3"/>
@@ -12029,8 +12431,12 @@
       <c r="GW57" s="3"/>
       <c r="GX57" s="3"/>
       <c r="GY57" s="3"/>
+      <c r="GZ57" s="3"/>
+      <c r="HA57" s="3"/>
+      <c r="HB57" s="3"/>
+      <c r="HC57" s="3"/>
     </row>
-    <row r="58" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C58" s="7"/>
       <c r="D58" s="7"/>
       <c r="E58" s="7"/>
@@ -12116,10 +12522,10 @@
       <c r="CG58" s="7"/>
       <c r="CH58" s="7"/>
       <c r="CI58" s="7"/>
-      <c r="CJ58" s="3"/>
-      <c r="CK58" s="3"/>
-      <c r="CL58" s="3"/>
-      <c r="CM58" s="3"/>
+      <c r="CJ58" s="7"/>
+      <c r="CK58" s="7"/>
+      <c r="CL58" s="7"/>
+      <c r="CM58" s="7"/>
       <c r="CN58" s="3"/>
       <c r="CO58" s="3"/>
       <c r="CP58" s="3"/>
@@ -12236,8 +12642,12 @@
       <c r="GW58" s="3"/>
       <c r="GX58" s="3"/>
       <c r="GY58" s="3"/>
+      <c r="GZ58" s="3"/>
+      <c r="HA58" s="3"/>
+      <c r="HB58" s="3"/>
+      <c r="HC58" s="3"/>
     </row>
-    <row r="59" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C59" s="7"/>
       <c r="D59" s="7"/>
       <c r="E59" s="7"/>
@@ -12323,10 +12733,10 @@
       <c r="CG59" s="7"/>
       <c r="CH59" s="7"/>
       <c r="CI59" s="7"/>
-      <c r="CJ59" s="3"/>
-      <c r="CK59" s="3"/>
-      <c r="CL59" s="3"/>
-      <c r="CM59" s="3"/>
+      <c r="CJ59" s="7"/>
+      <c r="CK59" s="7"/>
+      <c r="CL59" s="7"/>
+      <c r="CM59" s="7"/>
       <c r="CN59" s="3"/>
       <c r="CO59" s="3"/>
       <c r="CP59" s="3"/>
@@ -12443,8 +12853,12 @@
       <c r="GW59" s="3"/>
       <c r="GX59" s="3"/>
       <c r="GY59" s="3"/>
+      <c r="GZ59" s="3"/>
+      <c r="HA59" s="3"/>
+      <c r="HB59" s="3"/>
+      <c r="HC59" s="3"/>
     </row>
-    <row r="60" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C60" s="7"/>
       <c r="D60" s="7"/>
       <c r="E60" s="7"/>
@@ -12530,10 +12944,10 @@
       <c r="CG60" s="7"/>
       <c r="CH60" s="7"/>
       <c r="CI60" s="7"/>
-      <c r="CJ60" s="3"/>
-      <c r="CK60" s="3"/>
-      <c r="CL60" s="3"/>
-      <c r="CM60" s="3"/>
+      <c r="CJ60" s="7"/>
+      <c r="CK60" s="7"/>
+      <c r="CL60" s="7"/>
+      <c r="CM60" s="7"/>
       <c r="CN60" s="3"/>
       <c r="CO60" s="3"/>
       <c r="CP60" s="3"/>
@@ -12650,8 +13064,12 @@
       <c r="GW60" s="3"/>
       <c r="GX60" s="3"/>
       <c r="GY60" s="3"/>
+      <c r="GZ60" s="3"/>
+      <c r="HA60" s="3"/>
+      <c r="HB60" s="3"/>
+      <c r="HC60" s="3"/>
     </row>
-    <row r="61" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C61" s="7"/>
       <c r="D61" s="7"/>
       <c r="E61" s="7"/>
@@ -12737,10 +13155,10 @@
       <c r="CG61" s="7"/>
       <c r="CH61" s="7"/>
       <c r="CI61" s="7"/>
-      <c r="CJ61" s="3"/>
-      <c r="CK61" s="3"/>
-      <c r="CL61" s="3"/>
-      <c r="CM61" s="3"/>
+      <c r="CJ61" s="7"/>
+      <c r="CK61" s="7"/>
+      <c r="CL61" s="7"/>
+      <c r="CM61" s="7"/>
       <c r="CN61" s="3"/>
       <c r="CO61" s="3"/>
       <c r="CP61" s="3"/>
@@ -12857,8 +13275,12 @@
       <c r="GW61" s="3"/>
       <c r="GX61" s="3"/>
       <c r="GY61" s="3"/>
+      <c r="GZ61" s="3"/>
+      <c r="HA61" s="3"/>
+      <c r="HB61" s="3"/>
+      <c r="HC61" s="3"/>
     </row>
-    <row r="62" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C62" s="7"/>
       <c r="D62" s="7"/>
       <c r="E62" s="7"/>
@@ -12944,10 +13366,10 @@
       <c r="CG62" s="7"/>
       <c r="CH62" s="7"/>
       <c r="CI62" s="7"/>
-      <c r="CJ62" s="3"/>
-      <c r="CK62" s="3"/>
-      <c r="CL62" s="3"/>
-      <c r="CM62" s="3"/>
+      <c r="CJ62" s="7"/>
+      <c r="CK62" s="7"/>
+      <c r="CL62" s="7"/>
+      <c r="CM62" s="7"/>
       <c r="CN62" s="3"/>
       <c r="CO62" s="3"/>
       <c r="CP62" s="3"/>
@@ -13064,8 +13486,12 @@
       <c r="GW62" s="3"/>
       <c r="GX62" s="3"/>
       <c r="GY62" s="3"/>
+      <c r="GZ62" s="3"/>
+      <c r="HA62" s="3"/>
+      <c r="HB62" s="3"/>
+      <c r="HC62" s="3"/>
     </row>
-    <row r="63" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C63" s="7"/>
       <c r="D63" s="7"/>
       <c r="E63" s="7"/>
@@ -13151,10 +13577,10 @@
       <c r="CG63" s="7"/>
       <c r="CH63" s="7"/>
       <c r="CI63" s="7"/>
-      <c r="CJ63" s="3"/>
-      <c r="CK63" s="3"/>
-      <c r="CL63" s="3"/>
-      <c r="CM63" s="3"/>
+      <c r="CJ63" s="7"/>
+      <c r="CK63" s="7"/>
+      <c r="CL63" s="7"/>
+      <c r="CM63" s="7"/>
       <c r="CN63" s="3"/>
       <c r="CO63" s="3"/>
       <c r="CP63" s="3"/>
@@ -13271,8 +13697,12 @@
       <c r="GW63" s="3"/>
       <c r="GX63" s="3"/>
       <c r="GY63" s="3"/>
+      <c r="GZ63" s="3"/>
+      <c r="HA63" s="3"/>
+      <c r="HB63" s="3"/>
+      <c r="HC63" s="3"/>
     </row>
-    <row r="64" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C64" s="7"/>
       <c r="D64" s="7"/>
       <c r="E64" s="7"/>
@@ -13358,10 +13788,10 @@
       <c r="CG64" s="7"/>
       <c r="CH64" s="7"/>
       <c r="CI64" s="7"/>
-      <c r="CJ64" s="3"/>
-      <c r="CK64" s="3"/>
-      <c r="CL64" s="3"/>
-      <c r="CM64" s="3"/>
+      <c r="CJ64" s="7"/>
+      <c r="CK64" s="7"/>
+      <c r="CL64" s="7"/>
+      <c r="CM64" s="7"/>
       <c r="CN64" s="3"/>
       <c r="CO64" s="3"/>
       <c r="CP64" s="3"/>
@@ -13478,8 +13908,12 @@
       <c r="GW64" s="3"/>
       <c r="GX64" s="3"/>
       <c r="GY64" s="3"/>
+      <c r="GZ64" s="3"/>
+      <c r="HA64" s="3"/>
+      <c r="HB64" s="3"/>
+      <c r="HC64" s="3"/>
     </row>
-    <row r="65" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="65" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C65" s="7"/>
       <c r="D65" s="7"/>
       <c r="E65" s="7"/>
@@ -13565,10 +13999,10 @@
       <c r="CG65" s="7"/>
       <c r="CH65" s="7"/>
       <c r="CI65" s="7"/>
-      <c r="CJ65" s="3"/>
-      <c r="CK65" s="3"/>
-      <c r="CL65" s="3"/>
-      <c r="CM65" s="3"/>
+      <c r="CJ65" s="7"/>
+      <c r="CK65" s="7"/>
+      <c r="CL65" s="7"/>
+      <c r="CM65" s="7"/>
       <c r="CN65" s="3"/>
       <c r="CO65" s="3"/>
       <c r="CP65" s="3"/>
@@ -13685,8 +14119,12 @@
       <c r="GW65" s="3"/>
       <c r="GX65" s="3"/>
       <c r="GY65" s="3"/>
+      <c r="GZ65" s="3"/>
+      <c r="HA65" s="3"/>
+      <c r="HB65" s="3"/>
+      <c r="HC65" s="3"/>
     </row>
-    <row r="66" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="66" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C66" s="7"/>
       <c r="D66" s="7"/>
       <c r="E66" s="7"/>
@@ -13772,10 +14210,10 @@
       <c r="CG66" s="7"/>
       <c r="CH66" s="7"/>
       <c r="CI66" s="7"/>
-      <c r="CJ66" s="3"/>
-      <c r="CK66" s="3"/>
-      <c r="CL66" s="3"/>
-      <c r="CM66" s="3"/>
+      <c r="CJ66" s="7"/>
+      <c r="CK66" s="7"/>
+      <c r="CL66" s="7"/>
+      <c r="CM66" s="7"/>
       <c r="CN66" s="3"/>
       <c r="CO66" s="3"/>
       <c r="CP66" s="3"/>
@@ -13892,8 +14330,12 @@
       <c r="GW66" s="3"/>
       <c r="GX66" s="3"/>
       <c r="GY66" s="3"/>
+      <c r="GZ66" s="3"/>
+      <c r="HA66" s="3"/>
+      <c r="HB66" s="3"/>
+      <c r="HC66" s="3"/>
     </row>
-    <row r="67" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="67" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C67" s="7"/>
       <c r="D67" s="7"/>
       <c r="E67" s="7"/>
@@ -13979,10 +14421,10 @@
       <c r="CG67" s="7"/>
       <c r="CH67" s="7"/>
       <c r="CI67" s="7"/>
-      <c r="CJ67" s="3"/>
-      <c r="CK67" s="3"/>
-      <c r="CL67" s="3"/>
-      <c r="CM67" s="3"/>
+      <c r="CJ67" s="7"/>
+      <c r="CK67" s="7"/>
+      <c r="CL67" s="7"/>
+      <c r="CM67" s="7"/>
       <c r="CN67" s="3"/>
       <c r="CO67" s="3"/>
       <c r="CP67" s="3"/>
@@ -14099,8 +14541,12 @@
       <c r="GW67" s="3"/>
       <c r="GX67" s="3"/>
       <c r="GY67" s="3"/>
+      <c r="GZ67" s="3"/>
+      <c r="HA67" s="3"/>
+      <c r="HB67" s="3"/>
+      <c r="HC67" s="3"/>
     </row>
-    <row r="68" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="68" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C68" s="7"/>
       <c r="D68" s="7"/>
       <c r="E68" s="7"/>
@@ -14186,10 +14632,10 @@
       <c r="CG68" s="7"/>
       <c r="CH68" s="7"/>
       <c r="CI68" s="7"/>
-      <c r="CJ68" s="3"/>
-      <c r="CK68" s="3"/>
-      <c r="CL68" s="3"/>
-      <c r="CM68" s="3"/>
+      <c r="CJ68" s="7"/>
+      <c r="CK68" s="7"/>
+      <c r="CL68" s="7"/>
+      <c r="CM68" s="7"/>
       <c r="CN68" s="3"/>
       <c r="CO68" s="3"/>
       <c r="CP68" s="3"/>
@@ -14306,8 +14752,12 @@
       <c r="GW68" s="3"/>
       <c r="GX68" s="3"/>
       <c r="GY68" s="3"/>
+      <c r="GZ68" s="3"/>
+      <c r="HA68" s="3"/>
+      <c r="HB68" s="3"/>
+      <c r="HC68" s="3"/>
     </row>
-    <row r="69" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="69" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C69" s="7"/>
       <c r="D69" s="7"/>
       <c r="E69" s="7"/>
@@ -14393,10 +14843,10 @@
       <c r="CG69" s="7"/>
       <c r="CH69" s="7"/>
       <c r="CI69" s="7"/>
-      <c r="CJ69" s="3"/>
-      <c r="CK69" s="3"/>
-      <c r="CL69" s="3"/>
-      <c r="CM69" s="3"/>
+      <c r="CJ69" s="7"/>
+      <c r="CK69" s="7"/>
+      <c r="CL69" s="7"/>
+      <c r="CM69" s="7"/>
       <c r="CN69" s="3"/>
       <c r="CO69" s="3"/>
       <c r="CP69" s="3"/>
@@ -14513,8 +14963,12 @@
       <c r="GW69" s="3"/>
       <c r="GX69" s="3"/>
       <c r="GY69" s="3"/>
+      <c r="GZ69" s="3"/>
+      <c r="HA69" s="3"/>
+      <c r="HB69" s="3"/>
+      <c r="HC69" s="3"/>
     </row>
-    <row r="70" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="70" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C70" s="7"/>
       <c r="D70" s="7"/>
       <c r="E70" s="7"/>
@@ -14600,10 +15054,10 @@
       <c r="CG70" s="7"/>
       <c r="CH70" s="7"/>
       <c r="CI70" s="7"/>
-      <c r="CJ70" s="3"/>
-      <c r="CK70" s="3"/>
-      <c r="CL70" s="3"/>
-      <c r="CM70" s="3"/>
+      <c r="CJ70" s="7"/>
+      <c r="CK70" s="7"/>
+      <c r="CL70" s="7"/>
+      <c r="CM70" s="7"/>
       <c r="CN70" s="3"/>
       <c r="CO70" s="3"/>
       <c r="CP70" s="3"/>
@@ -14720,8 +15174,12 @@
       <c r="GW70" s="3"/>
       <c r="GX70" s="3"/>
       <c r="GY70" s="3"/>
+      <c r="GZ70" s="3"/>
+      <c r="HA70" s="3"/>
+      <c r="HB70" s="3"/>
+      <c r="HC70" s="3"/>
     </row>
-    <row r="71" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="71" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C71" s="7"/>
       <c r="D71" s="7"/>
       <c r="E71" s="7"/>
@@ -14807,10 +15265,10 @@
       <c r="CG71" s="7"/>
       <c r="CH71" s="7"/>
       <c r="CI71" s="7"/>
-      <c r="CJ71" s="3"/>
-      <c r="CK71" s="3"/>
-      <c r="CL71" s="3"/>
-      <c r="CM71" s="3"/>
+      <c r="CJ71" s="7"/>
+      <c r="CK71" s="7"/>
+      <c r="CL71" s="7"/>
+      <c r="CM71" s="7"/>
       <c r="CN71" s="3"/>
       <c r="CO71" s="3"/>
       <c r="CP71" s="3"/>
@@ -14927,8 +15385,12 @@
       <c r="GW71" s="3"/>
       <c r="GX71" s="3"/>
       <c r="GY71" s="3"/>
+      <c r="GZ71" s="3"/>
+      <c r="HA71" s="3"/>
+      <c r="HB71" s="3"/>
+      <c r="HC71" s="3"/>
     </row>
-    <row r="72" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="72" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C72" s="7"/>
       <c r="D72" s="7"/>
       <c r="E72" s="7"/>
@@ -15014,10 +15476,10 @@
       <c r="CG72" s="7"/>
       <c r="CH72" s="7"/>
       <c r="CI72" s="7"/>
-      <c r="CJ72" s="3"/>
-      <c r="CK72" s="3"/>
-      <c r="CL72" s="3"/>
-      <c r="CM72" s="3"/>
+      <c r="CJ72" s="7"/>
+      <c r="CK72" s="7"/>
+      <c r="CL72" s="7"/>
+      <c r="CM72" s="7"/>
       <c r="CN72" s="3"/>
       <c r="CO72" s="3"/>
       <c r="CP72" s="3"/>
@@ -15134,8 +15596,12 @@
       <c r="GW72" s="3"/>
       <c r="GX72" s="3"/>
       <c r="GY72" s="3"/>
+      <c r="GZ72" s="3"/>
+      <c r="HA72" s="3"/>
+      <c r="HB72" s="3"/>
+      <c r="HC72" s="3"/>
     </row>
-    <row r="73" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="73" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C73" s="7"/>
       <c r="D73" s="7"/>
       <c r="E73" s="7"/>
@@ -15221,10 +15687,10 @@
       <c r="CG73" s="7"/>
       <c r="CH73" s="7"/>
       <c r="CI73" s="7"/>
-      <c r="CJ73" s="3"/>
-      <c r="CK73" s="3"/>
-      <c r="CL73" s="3"/>
-      <c r="CM73" s="3"/>
+      <c r="CJ73" s="7"/>
+      <c r="CK73" s="7"/>
+      <c r="CL73" s="7"/>
+      <c r="CM73" s="7"/>
       <c r="CN73" s="3"/>
       <c r="CO73" s="3"/>
       <c r="CP73" s="3"/>
@@ -15341,8 +15807,12 @@
       <c r="GW73" s="3"/>
       <c r="GX73" s="3"/>
       <c r="GY73" s="3"/>
+      <c r="GZ73" s="3"/>
+      <c r="HA73" s="3"/>
+      <c r="HB73" s="3"/>
+      <c r="HC73" s="3"/>
     </row>
-    <row r="74" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="74" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C74" s="7"/>
       <c r="D74" s="7"/>
       <c r="E74" s="7"/>
@@ -15428,10 +15898,10 @@
       <c r="CG74" s="7"/>
       <c r="CH74" s="7"/>
       <c r="CI74" s="7"/>
-      <c r="CJ74" s="3"/>
-      <c r="CK74" s="3"/>
-      <c r="CL74" s="3"/>
-      <c r="CM74" s="3"/>
+      <c r="CJ74" s="7"/>
+      <c r="CK74" s="7"/>
+      <c r="CL74" s="7"/>
+      <c r="CM74" s="7"/>
       <c r="CN74" s="3"/>
       <c r="CO74" s="3"/>
       <c r="CP74" s="3"/>
@@ -15548,8 +16018,12 @@
       <c r="GW74" s="3"/>
       <c r="GX74" s="3"/>
       <c r="GY74" s="3"/>
+      <c r="GZ74" s="3"/>
+      <c r="HA74" s="3"/>
+      <c r="HB74" s="3"/>
+      <c r="HC74" s="3"/>
     </row>
-    <row r="75" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="75" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C75" s="7"/>
       <c r="D75" s="7"/>
       <c r="E75" s="7"/>
@@ -15635,10 +16109,10 @@
       <c r="CG75" s="7"/>
       <c r="CH75" s="7"/>
       <c r="CI75" s="7"/>
-      <c r="CJ75" s="3"/>
-      <c r="CK75" s="3"/>
-      <c r="CL75" s="3"/>
-      <c r="CM75" s="3"/>
+      <c r="CJ75" s="7"/>
+      <c r="CK75" s="7"/>
+      <c r="CL75" s="7"/>
+      <c r="CM75" s="7"/>
       <c r="CN75" s="3"/>
       <c r="CO75" s="3"/>
       <c r="CP75" s="3"/>
@@ -15755,8 +16229,12 @@
       <c r="GW75" s="3"/>
       <c r="GX75" s="3"/>
       <c r="GY75" s="3"/>
+      <c r="GZ75" s="3"/>
+      <c r="HA75" s="3"/>
+      <c r="HB75" s="3"/>
+      <c r="HC75" s="3"/>
     </row>
-    <row r="76" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="76" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C76" s="7"/>
       <c r="D76" s="7"/>
       <c r="E76" s="7"/>
@@ -15842,10 +16320,10 @@
       <c r="CG76" s="7"/>
       <c r="CH76" s="7"/>
       <c r="CI76" s="7"/>
-      <c r="CJ76" s="3"/>
-      <c r="CK76" s="3"/>
-      <c r="CL76" s="3"/>
-      <c r="CM76" s="3"/>
+      <c r="CJ76" s="7"/>
+      <c r="CK76" s="7"/>
+      <c r="CL76" s="7"/>
+      <c r="CM76" s="7"/>
       <c r="CN76" s="3"/>
       <c r="CO76" s="3"/>
       <c r="CP76" s="3"/>
@@ -15962,8 +16440,12 @@
       <c r="GW76" s="3"/>
       <c r="GX76" s="3"/>
       <c r="GY76" s="3"/>
+      <c r="GZ76" s="3"/>
+      <c r="HA76" s="3"/>
+      <c r="HB76" s="3"/>
+      <c r="HC76" s="3"/>
     </row>
-    <row r="77" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="77" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C77" s="7"/>
       <c r="D77" s="7"/>
       <c r="E77" s="7"/>
@@ -16049,10 +16531,10 @@
       <c r="CG77" s="7"/>
       <c r="CH77" s="7"/>
       <c r="CI77" s="7"/>
-      <c r="CJ77" s="3"/>
-      <c r="CK77" s="3"/>
-      <c r="CL77" s="3"/>
-      <c r="CM77" s="3"/>
+      <c r="CJ77" s="7"/>
+      <c r="CK77" s="7"/>
+      <c r="CL77" s="7"/>
+      <c r="CM77" s="7"/>
       <c r="CN77" s="3"/>
       <c r="CO77" s="3"/>
       <c r="CP77" s="3"/>
@@ -16169,8 +16651,12 @@
       <c r="GW77" s="3"/>
       <c r="GX77" s="3"/>
       <c r="GY77" s="3"/>
+      <c r="GZ77" s="3"/>
+      <c r="HA77" s="3"/>
+      <c r="HB77" s="3"/>
+      <c r="HC77" s="3"/>
     </row>
-    <row r="78" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="78" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C78" s="7"/>
       <c r="D78" s="7"/>
       <c r="E78" s="7"/>
@@ -16256,10 +16742,10 @@
       <c r="CG78" s="7"/>
       <c r="CH78" s="7"/>
       <c r="CI78" s="7"/>
-      <c r="CJ78" s="3"/>
-      <c r="CK78" s="3"/>
-      <c r="CL78" s="3"/>
-      <c r="CM78" s="3"/>
+      <c r="CJ78" s="7"/>
+      <c r="CK78" s="7"/>
+      <c r="CL78" s="7"/>
+      <c r="CM78" s="7"/>
       <c r="CN78" s="3"/>
       <c r="CO78" s="3"/>
       <c r="CP78" s="3"/>
@@ -16376,8 +16862,12 @@
       <c r="GW78" s="3"/>
       <c r="GX78" s="3"/>
       <c r="GY78" s="3"/>
+      <c r="GZ78" s="3"/>
+      <c r="HA78" s="3"/>
+      <c r="HB78" s="3"/>
+      <c r="HC78" s="3"/>
     </row>
-    <row r="79" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="79" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C79" s="7"/>
       <c r="D79" s="7"/>
       <c r="E79" s="7"/>
@@ -16463,10 +16953,10 @@
       <c r="CG79" s="7"/>
       <c r="CH79" s="7"/>
       <c r="CI79" s="7"/>
-      <c r="CJ79" s="3"/>
-      <c r="CK79" s="3"/>
-      <c r="CL79" s="3"/>
-      <c r="CM79" s="3"/>
+      <c r="CJ79" s="7"/>
+      <c r="CK79" s="7"/>
+      <c r="CL79" s="7"/>
+      <c r="CM79" s="7"/>
       <c r="CN79" s="3"/>
       <c r="CO79" s="3"/>
       <c r="CP79" s="3"/>
@@ -16583,8 +17073,12 @@
       <c r="GW79" s="3"/>
       <c r="GX79" s="3"/>
       <c r="GY79" s="3"/>
+      <c r="GZ79" s="3"/>
+      <c r="HA79" s="3"/>
+      <c r="HB79" s="3"/>
+      <c r="HC79" s="3"/>
     </row>
-    <row r="80" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="80" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C80" s="7"/>
       <c r="D80" s="7"/>
       <c r="E80" s="7"/>
@@ -16670,10 +17164,10 @@
       <c r="CG80" s="7"/>
       <c r="CH80" s="7"/>
       <c r="CI80" s="7"/>
-      <c r="CJ80" s="3"/>
-      <c r="CK80" s="3"/>
-      <c r="CL80" s="3"/>
-      <c r="CM80" s="3"/>
+      <c r="CJ80" s="7"/>
+      <c r="CK80" s="7"/>
+      <c r="CL80" s="7"/>
+      <c r="CM80" s="7"/>
       <c r="CN80" s="3"/>
       <c r="CO80" s="3"/>
       <c r="CP80" s="3"/>
@@ -16790,8 +17284,12 @@
       <c r="GW80" s="3"/>
       <c r="GX80" s="3"/>
       <c r="GY80" s="3"/>
+      <c r="GZ80" s="3"/>
+      <c r="HA80" s="3"/>
+      <c r="HB80" s="3"/>
+      <c r="HC80" s="3"/>
     </row>
-    <row r="81" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C81" s="7"/>
       <c r="D81" s="7"/>
       <c r="E81" s="7"/>
@@ -16877,10 +17375,10 @@
       <c r="CG81" s="7"/>
       <c r="CH81" s="7"/>
       <c r="CI81" s="7"/>
-      <c r="CJ81" s="3"/>
-      <c r="CK81" s="3"/>
-      <c r="CL81" s="3"/>
-      <c r="CM81" s="3"/>
+      <c r="CJ81" s="7"/>
+      <c r="CK81" s="7"/>
+      <c r="CL81" s="7"/>
+      <c r="CM81" s="7"/>
       <c r="CN81" s="3"/>
       <c r="CO81" s="3"/>
       <c r="CP81" s="3"/>
@@ -16997,8 +17495,12 @@
       <c r="GW81" s="3"/>
       <c r="GX81" s="3"/>
       <c r="GY81" s="3"/>
+      <c r="GZ81" s="3"/>
+      <c r="HA81" s="3"/>
+      <c r="HB81" s="3"/>
+      <c r="HC81" s="3"/>
     </row>
-    <row r="82" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C82" s="7"/>
       <c r="D82" s="7"/>
       <c r="E82" s="7"/>
@@ -17084,10 +17586,10 @@
       <c r="CG82" s="7"/>
       <c r="CH82" s="7"/>
       <c r="CI82" s="7"/>
-      <c r="CJ82" s="3"/>
-      <c r="CK82" s="3"/>
-      <c r="CL82" s="3"/>
-      <c r="CM82" s="3"/>
+      <c r="CJ82" s="7"/>
+      <c r="CK82" s="7"/>
+      <c r="CL82" s="7"/>
+      <c r="CM82" s="7"/>
       <c r="CN82" s="3"/>
       <c r="CO82" s="3"/>
       <c r="CP82" s="3"/>
@@ -17204,8 +17706,12 @@
       <c r="GW82" s="3"/>
       <c r="GX82" s="3"/>
       <c r="GY82" s="3"/>
+      <c r="GZ82" s="3"/>
+      <c r="HA82" s="3"/>
+      <c r="HB82" s="3"/>
+      <c r="HC82" s="3"/>
     </row>
-    <row r="83" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C83" s="7"/>
       <c r="D83" s="7"/>
       <c r="E83" s="7"/>
@@ -17291,10 +17797,10 @@
       <c r="CG83" s="7"/>
       <c r="CH83" s="7"/>
       <c r="CI83" s="7"/>
-      <c r="CJ83" s="3"/>
-      <c r="CK83" s="3"/>
-      <c r="CL83" s="3"/>
-      <c r="CM83" s="3"/>
+      <c r="CJ83" s="7"/>
+      <c r="CK83" s="7"/>
+      <c r="CL83" s="7"/>
+      <c r="CM83" s="7"/>
       <c r="CN83" s="3"/>
       <c r="CO83" s="3"/>
       <c r="CP83" s="3"/>
@@ -17411,8 +17917,12 @@
       <c r="GW83" s="3"/>
       <c r="GX83" s="3"/>
       <c r="GY83" s="3"/>
+      <c r="GZ83" s="3"/>
+      <c r="HA83" s="3"/>
+      <c r="HB83" s="3"/>
+      <c r="HC83" s="3"/>
     </row>
-    <row r="84" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C84" s="7"/>
       <c r="D84" s="7"/>
       <c r="E84" s="7"/>
@@ -17498,10 +18008,10 @@
       <c r="CG84" s="7"/>
       <c r="CH84" s="7"/>
       <c r="CI84" s="7"/>
-      <c r="CJ84" s="3"/>
-      <c r="CK84" s="3"/>
-      <c r="CL84" s="3"/>
-      <c r="CM84" s="3"/>
+      <c r="CJ84" s="7"/>
+      <c r="CK84" s="7"/>
+      <c r="CL84" s="7"/>
+      <c r="CM84" s="7"/>
       <c r="CN84" s="3"/>
       <c r="CO84" s="3"/>
       <c r="CP84" s="3"/>
@@ -17618,8 +18128,12 @@
       <c r="GW84" s="3"/>
       <c r="GX84" s="3"/>
       <c r="GY84" s="3"/>
+      <c r="GZ84" s="3"/>
+      <c r="HA84" s="3"/>
+      <c r="HB84" s="3"/>
+      <c r="HC84" s="3"/>
     </row>
-    <row r="85" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C85" s="7"/>
       <c r="D85" s="7"/>
       <c r="E85" s="7"/>
@@ -17705,10 +18219,10 @@
       <c r="CG85" s="7"/>
       <c r="CH85" s="7"/>
       <c r="CI85" s="7"/>
-      <c r="CJ85" s="3"/>
-      <c r="CK85" s="3"/>
-      <c r="CL85" s="3"/>
-      <c r="CM85" s="3"/>
+      <c r="CJ85" s="7"/>
+      <c r="CK85" s="7"/>
+      <c r="CL85" s="7"/>
+      <c r="CM85" s="7"/>
       <c r="CN85" s="3"/>
       <c r="CO85" s="3"/>
       <c r="CP85" s="3"/>
@@ -17825,8 +18339,12 @@
       <c r="GW85" s="3"/>
       <c r="GX85" s="3"/>
       <c r="GY85" s="3"/>
+      <c r="GZ85" s="3"/>
+      <c r="HA85" s="3"/>
+      <c r="HB85" s="3"/>
+      <c r="HC85" s="3"/>
     </row>
-    <row r="86" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C86" s="7"/>
       <c r="D86" s="7"/>
       <c r="E86" s="7"/>
@@ -17912,10 +18430,10 @@
       <c r="CG86" s="7"/>
       <c r="CH86" s="7"/>
       <c r="CI86" s="7"/>
-      <c r="CJ86" s="3"/>
-      <c r="CK86" s="3"/>
-      <c r="CL86" s="3"/>
-      <c r="CM86" s="3"/>
+      <c r="CJ86" s="7"/>
+      <c r="CK86" s="7"/>
+      <c r="CL86" s="7"/>
+      <c r="CM86" s="7"/>
       <c r="CN86" s="3"/>
       <c r="CO86" s="3"/>
       <c r="CP86" s="3"/>
@@ -18032,8 +18550,12 @@
       <c r="GW86" s="3"/>
       <c r="GX86" s="3"/>
       <c r="GY86" s="3"/>
+      <c r="GZ86" s="3"/>
+      <c r="HA86" s="3"/>
+      <c r="HB86" s="3"/>
+      <c r="HC86" s="3"/>
     </row>
-    <row r="87" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C87" s="7"/>
       <c r="D87" s="7"/>
       <c r="E87" s="7"/>
@@ -18119,10 +18641,10 @@
       <c r="CG87" s="7"/>
       <c r="CH87" s="7"/>
       <c r="CI87" s="7"/>
-      <c r="CJ87" s="3"/>
-      <c r="CK87" s="3"/>
-      <c r="CL87" s="3"/>
-      <c r="CM87" s="3"/>
+      <c r="CJ87" s="7"/>
+      <c r="CK87" s="7"/>
+      <c r="CL87" s="7"/>
+      <c r="CM87" s="7"/>
       <c r="CN87" s="3"/>
       <c r="CO87" s="3"/>
       <c r="CP87" s="3"/>
@@ -18239,8 +18761,12 @@
       <c r="GW87" s="3"/>
       <c r="GX87" s="3"/>
       <c r="GY87" s="3"/>
+      <c r="GZ87" s="3"/>
+      <c r="HA87" s="3"/>
+      <c r="HB87" s="3"/>
+      <c r="HC87" s="3"/>
     </row>
-    <row r="88" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C88" s="7"/>
       <c r="D88" s="7"/>
       <c r="E88" s="7"/>
@@ -18326,10 +18852,10 @@
       <c r="CG88" s="7"/>
       <c r="CH88" s="7"/>
       <c r="CI88" s="7"/>
-      <c r="CJ88" s="3"/>
-      <c r="CK88" s="3"/>
-      <c r="CL88" s="3"/>
-      <c r="CM88" s="3"/>
+      <c r="CJ88" s="7"/>
+      <c r="CK88" s="7"/>
+      <c r="CL88" s="7"/>
+      <c r="CM88" s="7"/>
       <c r="CN88" s="3"/>
       <c r="CO88" s="3"/>
       <c r="CP88" s="3"/>
@@ -18446,8 +18972,12 @@
       <c r="GW88" s="3"/>
       <c r="GX88" s="3"/>
       <c r="GY88" s="3"/>
+      <c r="GZ88" s="3"/>
+      <c r="HA88" s="3"/>
+      <c r="HB88" s="3"/>
+      <c r="HC88" s="3"/>
     </row>
-    <row r="89" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C89" s="7"/>
       <c r="D89" s="7"/>
       <c r="E89" s="7"/>
@@ -18533,10 +19063,10 @@
       <c r="CG89" s="7"/>
       <c r="CH89" s="7"/>
       <c r="CI89" s="7"/>
-      <c r="CJ89" s="3"/>
-      <c r="CK89" s="3"/>
-      <c r="CL89" s="3"/>
-      <c r="CM89" s="3"/>
+      <c r="CJ89" s="7"/>
+      <c r="CK89" s="7"/>
+      <c r="CL89" s="7"/>
+      <c r="CM89" s="7"/>
       <c r="CN89" s="3"/>
       <c r="CO89" s="3"/>
       <c r="CP89" s="3"/>
@@ -18653,8 +19183,12 @@
       <c r="GW89" s="3"/>
       <c r="GX89" s="3"/>
       <c r="GY89" s="3"/>
+      <c r="GZ89" s="3"/>
+      <c r="HA89" s="3"/>
+      <c r="HB89" s="3"/>
+      <c r="HC89" s="3"/>
     </row>
-    <row r="90" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C90" s="7"/>
       <c r="D90" s="7"/>
       <c r="E90" s="7"/>
@@ -18740,10 +19274,10 @@
       <c r="CG90" s="7"/>
       <c r="CH90" s="7"/>
       <c r="CI90" s="7"/>
-      <c r="CJ90" s="3"/>
-      <c r="CK90" s="3"/>
-      <c r="CL90" s="3"/>
-      <c r="CM90" s="3"/>
+      <c r="CJ90" s="7"/>
+      <c r="CK90" s="7"/>
+      <c r="CL90" s="7"/>
+      <c r="CM90" s="7"/>
       <c r="CN90" s="3"/>
       <c r="CO90" s="3"/>
       <c r="CP90" s="3"/>
@@ -18860,8 +19394,12 @@
       <c r="GW90" s="3"/>
       <c r="GX90" s="3"/>
       <c r="GY90" s="3"/>
+      <c r="GZ90" s="3"/>
+      <c r="HA90" s="3"/>
+      <c r="HB90" s="3"/>
+      <c r="HC90" s="3"/>
     </row>
-    <row r="91" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C91" s="7"/>
       <c r="D91" s="7"/>
       <c r="E91" s="7"/>
@@ -18947,10 +19485,10 @@
       <c r="CG91" s="7"/>
       <c r="CH91" s="7"/>
       <c r="CI91" s="7"/>
-      <c r="CJ91" s="3"/>
-      <c r="CK91" s="3"/>
-      <c r="CL91" s="3"/>
-      <c r="CM91" s="3"/>
+      <c r="CJ91" s="7"/>
+      <c r="CK91" s="7"/>
+      <c r="CL91" s="7"/>
+      <c r="CM91" s="7"/>
       <c r="CN91" s="3"/>
       <c r="CO91" s="3"/>
       <c r="CP91" s="3"/>
@@ -19067,8 +19605,12 @@
       <c r="GW91" s="3"/>
       <c r="GX91" s="3"/>
       <c r="GY91" s="3"/>
+      <c r="GZ91" s="3"/>
+      <c r="HA91" s="3"/>
+      <c r="HB91" s="3"/>
+      <c r="HC91" s="3"/>
     </row>
-    <row r="92" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C92" s="7"/>
       <c r="D92" s="7"/>
       <c r="E92" s="7"/>
@@ -19154,10 +19696,10 @@
       <c r="CG92" s="7"/>
       <c r="CH92" s="7"/>
       <c r="CI92" s="7"/>
-      <c r="CJ92" s="3"/>
-      <c r="CK92" s="3"/>
-      <c r="CL92" s="3"/>
-      <c r="CM92" s="3"/>
+      <c r="CJ92" s="7"/>
+      <c r="CK92" s="7"/>
+      <c r="CL92" s="7"/>
+      <c r="CM92" s="7"/>
       <c r="CN92" s="3"/>
       <c r="CO92" s="3"/>
       <c r="CP92" s="3"/>
@@ -19274,8 +19816,12 @@
       <c r="GW92" s="3"/>
       <c r="GX92" s="3"/>
       <c r="GY92" s="3"/>
+      <c r="GZ92" s="3"/>
+      <c r="HA92" s="3"/>
+      <c r="HB92" s="3"/>
+      <c r="HC92" s="3"/>
     </row>
-    <row r="93" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C93" s="7"/>
       <c r="D93" s="7"/>
       <c r="E93" s="7"/>
@@ -19361,10 +19907,10 @@
       <c r="CG93" s="7"/>
       <c r="CH93" s="7"/>
       <c r="CI93" s="7"/>
-      <c r="CJ93" s="3"/>
-      <c r="CK93" s="3"/>
-      <c r="CL93" s="3"/>
-      <c r="CM93" s="3"/>
+      <c r="CJ93" s="7"/>
+      <c r="CK93" s="7"/>
+      <c r="CL93" s="7"/>
+      <c r="CM93" s="7"/>
       <c r="CN93" s="3"/>
       <c r="CO93" s="3"/>
       <c r="CP93" s="3"/>
@@ -19481,8 +20027,12 @@
       <c r="GW93" s="3"/>
       <c r="GX93" s="3"/>
       <c r="GY93" s="3"/>
+      <c r="GZ93" s="3"/>
+      <c r="HA93" s="3"/>
+      <c r="HB93" s="3"/>
+      <c r="HC93" s="3"/>
     </row>
-    <row r="94" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C94" s="7"/>
       <c r="D94" s="7"/>
       <c r="E94" s="7"/>
@@ -19568,10 +20118,10 @@
       <c r="CG94" s="7"/>
       <c r="CH94" s="7"/>
       <c r="CI94" s="7"/>
-      <c r="CJ94" s="3"/>
-      <c r="CK94" s="3"/>
-      <c r="CL94" s="3"/>
-      <c r="CM94" s="3"/>
+      <c r="CJ94" s="7"/>
+      <c r="CK94" s="7"/>
+      <c r="CL94" s="7"/>
+      <c r="CM94" s="7"/>
       <c r="CN94" s="3"/>
       <c r="CO94" s="3"/>
       <c r="CP94" s="3"/>
@@ -19688,8 +20238,12 @@
       <c r="GW94" s="3"/>
       <c r="GX94" s="3"/>
       <c r="GY94" s="3"/>
+      <c r="GZ94" s="3"/>
+      <c r="HA94" s="3"/>
+      <c r="HB94" s="3"/>
+      <c r="HC94" s="3"/>
     </row>
-    <row r="95" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C95" s="7"/>
       <c r="D95" s="7"/>
       <c r="E95" s="7"/>
@@ -19775,10 +20329,10 @@
       <c r="CG95" s="7"/>
       <c r="CH95" s="7"/>
       <c r="CI95" s="7"/>
-      <c r="CJ95" s="3"/>
-      <c r="CK95" s="3"/>
-      <c r="CL95" s="3"/>
-      <c r="CM95" s="3"/>
+      <c r="CJ95" s="7"/>
+      <c r="CK95" s="7"/>
+      <c r="CL95" s="7"/>
+      <c r="CM95" s="7"/>
       <c r="CN95" s="3"/>
       <c r="CO95" s="3"/>
       <c r="CP95" s="3"/>
@@ -19895,8 +20449,12 @@
       <c r="GW95" s="3"/>
       <c r="GX95" s="3"/>
       <c r="GY95" s="3"/>
+      <c r="GZ95" s="3"/>
+      <c r="HA95" s="3"/>
+      <c r="HB95" s="3"/>
+      <c r="HC95" s="3"/>
     </row>
-    <row r="96" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C96" s="7"/>
       <c r="D96" s="7"/>
       <c r="E96" s="7"/>
@@ -19982,10 +20540,10 @@
       <c r="CG96" s="7"/>
       <c r="CH96" s="7"/>
       <c r="CI96" s="7"/>
-      <c r="CJ96" s="3"/>
-      <c r="CK96" s="3"/>
-      <c r="CL96" s="3"/>
-      <c r="CM96" s="3"/>
+      <c r="CJ96" s="7"/>
+      <c r="CK96" s="7"/>
+      <c r="CL96" s="7"/>
+      <c r="CM96" s="7"/>
       <c r="CN96" s="3"/>
       <c r="CO96" s="3"/>
       <c r="CP96" s="3"/>
@@ -20102,8 +20660,12 @@
       <c r="GW96" s="3"/>
       <c r="GX96" s="3"/>
       <c r="GY96" s="3"/>
+      <c r="GZ96" s="3"/>
+      <c r="HA96" s="3"/>
+      <c r="HB96" s="3"/>
+      <c r="HC96" s="3"/>
     </row>
-    <row r="97" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C97" s="7"/>
       <c r="D97" s="7"/>
       <c r="E97" s="7"/>
@@ -20189,10 +20751,10 @@
       <c r="CG97" s="7"/>
       <c r="CH97" s="7"/>
       <c r="CI97" s="7"/>
-      <c r="CJ97" s="3"/>
-      <c r="CK97" s="3"/>
-      <c r="CL97" s="3"/>
-      <c r="CM97" s="3"/>
+      <c r="CJ97" s="7"/>
+      <c r="CK97" s="7"/>
+      <c r="CL97" s="7"/>
+      <c r="CM97" s="7"/>
       <c r="CN97" s="3"/>
       <c r="CO97" s="3"/>
       <c r="CP97" s="3"/>
@@ -20309,8 +20871,12 @@
       <c r="GW97" s="3"/>
       <c r="GX97" s="3"/>
       <c r="GY97" s="3"/>
+      <c r="GZ97" s="3"/>
+      <c r="HA97" s="3"/>
+      <c r="HB97" s="3"/>
+      <c r="HC97" s="3"/>
     </row>
-    <row r="98" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C98" s="7"/>
       <c r="D98" s="7"/>
       <c r="E98" s="7"/>
@@ -20396,10 +20962,10 @@
       <c r="CG98" s="7"/>
       <c r="CH98" s="7"/>
       <c r="CI98" s="7"/>
-      <c r="CJ98" s="3"/>
-      <c r="CK98" s="3"/>
-      <c r="CL98" s="3"/>
-      <c r="CM98" s="3"/>
+      <c r="CJ98" s="7"/>
+      <c r="CK98" s="7"/>
+      <c r="CL98" s="7"/>
+      <c r="CM98" s="7"/>
       <c r="CN98" s="3"/>
       <c r="CO98" s="3"/>
       <c r="CP98" s="3"/>
@@ -20516,8 +21082,12 @@
       <c r="GW98" s="3"/>
       <c r="GX98" s="3"/>
       <c r="GY98" s="3"/>
+      <c r="GZ98" s="3"/>
+      <c r="HA98" s="3"/>
+      <c r="HB98" s="3"/>
+      <c r="HC98" s="3"/>
     </row>
-    <row r="99" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C99" s="7"/>
       <c r="D99" s="7"/>
       <c r="E99" s="7"/>
@@ -20603,10 +21173,10 @@
       <c r="CG99" s="7"/>
       <c r="CH99" s="7"/>
       <c r="CI99" s="7"/>
-      <c r="CJ99" s="3"/>
-      <c r="CK99" s="3"/>
-      <c r="CL99" s="3"/>
-      <c r="CM99" s="3"/>
+      <c r="CJ99" s="7"/>
+      <c r="CK99" s="7"/>
+      <c r="CL99" s="7"/>
+      <c r="CM99" s="7"/>
       <c r="CN99" s="3"/>
       <c r="CO99" s="3"/>
       <c r="CP99" s="3"/>
@@ -20723,8 +21293,12 @@
       <c r="GW99" s="3"/>
       <c r="GX99" s="3"/>
       <c r="GY99" s="3"/>
+      <c r="GZ99" s="3"/>
+      <c r="HA99" s="3"/>
+      <c r="HB99" s="3"/>
+      <c r="HC99" s="3"/>
     </row>
-    <row r="100" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C100" s="7"/>
       <c r="D100" s="7"/>
       <c r="E100" s="7"/>
@@ -20810,10 +21384,10 @@
       <c r="CG100" s="7"/>
       <c r="CH100" s="7"/>
       <c r="CI100" s="7"/>
-      <c r="CJ100" s="3"/>
-      <c r="CK100" s="3"/>
-      <c r="CL100" s="3"/>
-      <c r="CM100" s="3"/>
+      <c r="CJ100" s="7"/>
+      <c r="CK100" s="7"/>
+      <c r="CL100" s="7"/>
+      <c r="CM100" s="7"/>
       <c r="CN100" s="3"/>
       <c r="CO100" s="3"/>
       <c r="CP100" s="3"/>
@@ -20930,8 +21504,12 @@
       <c r="GW100" s="3"/>
       <c r="GX100" s="3"/>
       <c r="GY100" s="3"/>
+      <c r="GZ100" s="3"/>
+      <c r="HA100" s="3"/>
+      <c r="HB100" s="3"/>
+      <c r="HC100" s="3"/>
     </row>
-    <row r="101" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C101" s="7"/>
       <c r="D101" s="7"/>
       <c r="E101" s="7"/>
@@ -21017,10 +21595,10 @@
       <c r="CG101" s="7"/>
       <c r="CH101" s="7"/>
       <c r="CI101" s="7"/>
-      <c r="CJ101" s="3"/>
-      <c r="CK101" s="3"/>
-      <c r="CL101" s="3"/>
-      <c r="CM101" s="3"/>
+      <c r="CJ101" s="7"/>
+      <c r="CK101" s="7"/>
+      <c r="CL101" s="7"/>
+      <c r="CM101" s="7"/>
       <c r="CN101" s="3"/>
       <c r="CO101" s="3"/>
       <c r="CP101" s="3"/>
@@ -21137,8 +21715,12 @@
       <c r="GW101" s="3"/>
       <c r="GX101" s="3"/>
       <c r="GY101" s="3"/>
+      <c r="GZ101" s="3"/>
+      <c r="HA101" s="3"/>
+      <c r="HB101" s="3"/>
+      <c r="HC101" s="3"/>
     </row>
-    <row r="102" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C102" s="7"/>
       <c r="D102" s="7"/>
       <c r="E102" s="7"/>
@@ -21224,10 +21806,10 @@
       <c r="CG102" s="7"/>
       <c r="CH102" s="7"/>
       <c r="CI102" s="7"/>
-      <c r="CJ102" s="3"/>
-      <c r="CK102" s="3"/>
-      <c r="CL102" s="3"/>
-      <c r="CM102" s="3"/>
+      <c r="CJ102" s="7"/>
+      <c r="CK102" s="7"/>
+      <c r="CL102" s="7"/>
+      <c r="CM102" s="7"/>
       <c r="CN102" s="3"/>
       <c r="CO102" s="3"/>
       <c r="CP102" s="3"/>
@@ -21344,8 +21926,12 @@
       <c r="GW102" s="3"/>
       <c r="GX102" s="3"/>
       <c r="GY102" s="3"/>
+      <c r="GZ102" s="3"/>
+      <c r="HA102" s="3"/>
+      <c r="HB102" s="3"/>
+      <c r="HC102" s="3"/>
     </row>
-    <row r="103" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="103" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C103" s="7"/>
       <c r="D103" s="7"/>
       <c r="E103" s="7"/>
@@ -21431,10 +22017,10 @@
       <c r="CG103" s="7"/>
       <c r="CH103" s="7"/>
       <c r="CI103" s="7"/>
-      <c r="CJ103" s="3"/>
-      <c r="CK103" s="3"/>
-      <c r="CL103" s="3"/>
-      <c r="CM103" s="3"/>
+      <c r="CJ103" s="7"/>
+      <c r="CK103" s="7"/>
+      <c r="CL103" s="7"/>
+      <c r="CM103" s="7"/>
       <c r="CN103" s="3"/>
       <c r="CO103" s="3"/>
       <c r="CP103" s="3"/>
@@ -21551,8 +22137,12 @@
       <c r="GW103" s="3"/>
       <c r="GX103" s="3"/>
       <c r="GY103" s="3"/>
+      <c r="GZ103" s="3"/>
+      <c r="HA103" s="3"/>
+      <c r="HB103" s="3"/>
+      <c r="HC103" s="3"/>
     </row>
-    <row r="104" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="104" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C104" s="7"/>
       <c r="D104" s="7"/>
       <c r="E104" s="7"/>
@@ -21638,10 +22228,10 @@
       <c r="CG104" s="7"/>
       <c r="CH104" s="7"/>
       <c r="CI104" s="7"/>
-      <c r="CJ104" s="3"/>
-      <c r="CK104" s="3"/>
-      <c r="CL104" s="3"/>
-      <c r="CM104" s="3"/>
+      <c r="CJ104" s="7"/>
+      <c r="CK104" s="7"/>
+      <c r="CL104" s="7"/>
+      <c r="CM104" s="7"/>
       <c r="CN104" s="3"/>
       <c r="CO104" s="3"/>
       <c r="CP104" s="3"/>
@@ -21758,8 +22348,12 @@
       <c r="GW104" s="3"/>
       <c r="GX104" s="3"/>
       <c r="GY104" s="3"/>
+      <c r="GZ104" s="3"/>
+      <c r="HA104" s="3"/>
+      <c r="HB104" s="3"/>
+      <c r="HC104" s="3"/>
     </row>
-    <row r="105" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="105" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C105" s="7"/>
       <c r="D105" s="7"/>
       <c r="E105" s="7"/>
@@ -21845,10 +22439,10 @@
       <c r="CG105" s="7"/>
       <c r="CH105" s="7"/>
       <c r="CI105" s="7"/>
-      <c r="CJ105" s="3"/>
-      <c r="CK105" s="3"/>
-      <c r="CL105" s="3"/>
-      <c r="CM105" s="3"/>
+      <c r="CJ105" s="7"/>
+      <c r="CK105" s="7"/>
+      <c r="CL105" s="7"/>
+      <c r="CM105" s="7"/>
       <c r="CN105" s="3"/>
       <c r="CO105" s="3"/>
       <c r="CP105" s="3"/>
@@ -21965,8 +22559,12 @@
       <c r="GW105" s="3"/>
       <c r="GX105" s="3"/>
       <c r="GY105" s="3"/>
+      <c r="GZ105" s="3"/>
+      <c r="HA105" s="3"/>
+      <c r="HB105" s="3"/>
+      <c r="HC105" s="3"/>
     </row>
-    <row r="106" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="106" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C106" s="7"/>
       <c r="D106" s="7"/>
       <c r="E106" s="7"/>
@@ -22052,10 +22650,10 @@
       <c r="CG106" s="7"/>
       <c r="CH106" s="7"/>
       <c r="CI106" s="7"/>
-      <c r="CJ106" s="3"/>
-      <c r="CK106" s="3"/>
-      <c r="CL106" s="3"/>
-      <c r="CM106" s="3"/>
+      <c r="CJ106" s="7"/>
+      <c r="CK106" s="7"/>
+      <c r="CL106" s="7"/>
+      <c r="CM106" s="7"/>
       <c r="CN106" s="3"/>
       <c r="CO106" s="3"/>
       <c r="CP106" s="3"/>
@@ -22172,8 +22770,12 @@
       <c r="GW106" s="3"/>
       <c r="GX106" s="3"/>
       <c r="GY106" s="3"/>
+      <c r="GZ106" s="3"/>
+      <c r="HA106" s="3"/>
+      <c r="HB106" s="3"/>
+      <c r="HC106" s="3"/>
     </row>
-    <row r="107" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="107" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C107" s="7"/>
       <c r="D107" s="7"/>
       <c r="E107" s="7"/>
@@ -22259,10 +22861,10 @@
       <c r="CG107" s="7"/>
       <c r="CH107" s="7"/>
       <c r="CI107" s="7"/>
-      <c r="CJ107" s="3"/>
-      <c r="CK107" s="3"/>
-      <c r="CL107" s="3"/>
-      <c r="CM107" s="3"/>
+      <c r="CJ107" s="7"/>
+      <c r="CK107" s="7"/>
+      <c r="CL107" s="7"/>
+      <c r="CM107" s="7"/>
       <c r="CN107" s="3"/>
       <c r="CO107" s="3"/>
       <c r="CP107" s="3"/>
@@ -22379,8 +22981,12 @@
       <c r="GW107" s="3"/>
       <c r="GX107" s="3"/>
       <c r="GY107" s="3"/>
+      <c r="GZ107" s="3"/>
+      <c r="HA107" s="3"/>
+      <c r="HB107" s="3"/>
+      <c r="HC107" s="3"/>
     </row>
-    <row r="108" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="108" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C108" s="7"/>
       <c r="D108" s="7"/>
       <c r="E108" s="7"/>
@@ -22466,10 +23072,10 @@
       <c r="CG108" s="7"/>
       <c r="CH108" s="7"/>
       <c r="CI108" s="7"/>
-      <c r="CJ108" s="3"/>
-      <c r="CK108" s="3"/>
-      <c r="CL108" s="3"/>
-      <c r="CM108" s="3"/>
+      <c r="CJ108" s="7"/>
+      <c r="CK108" s="7"/>
+      <c r="CL108" s="7"/>
+      <c r="CM108" s="7"/>
       <c r="CN108" s="3"/>
       <c r="CO108" s="3"/>
       <c r="CP108" s="3"/>
@@ -22586,8 +23192,12 @@
       <c r="GW108" s="3"/>
       <c r="GX108" s="3"/>
       <c r="GY108" s="3"/>
+      <c r="GZ108" s="3"/>
+      <c r="HA108" s="3"/>
+      <c r="HB108" s="3"/>
+      <c r="HC108" s="3"/>
     </row>
-    <row r="109" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="109" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C109" s="7"/>
       <c r="D109" s="7"/>
       <c r="E109" s="7"/>
@@ -22673,10 +23283,10 @@
       <c r="CG109" s="7"/>
       <c r="CH109" s="7"/>
       <c r="CI109" s="7"/>
-      <c r="CJ109" s="3"/>
-      <c r="CK109" s="3"/>
-      <c r="CL109" s="3"/>
-      <c r="CM109" s="3"/>
+      <c r="CJ109" s="7"/>
+      <c r="CK109" s="7"/>
+      <c r="CL109" s="7"/>
+      <c r="CM109" s="7"/>
       <c r="CN109" s="3"/>
       <c r="CO109" s="3"/>
       <c r="CP109" s="3"/>
@@ -22793,8 +23403,12 @@
       <c r="GW109" s="3"/>
       <c r="GX109" s="3"/>
       <c r="GY109" s="3"/>
+      <c r="GZ109" s="3"/>
+      <c r="HA109" s="3"/>
+      <c r="HB109" s="3"/>
+      <c r="HC109" s="3"/>
     </row>
-    <row r="110" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="110" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C110" s="7"/>
       <c r="D110" s="7"/>
       <c r="E110" s="7"/>
@@ -22880,10 +23494,10 @@
       <c r="CG110" s="7"/>
       <c r="CH110" s="7"/>
       <c r="CI110" s="7"/>
-      <c r="CJ110" s="3"/>
-      <c r="CK110" s="3"/>
-      <c r="CL110" s="3"/>
-      <c r="CM110" s="3"/>
+      <c r="CJ110" s="7"/>
+      <c r="CK110" s="7"/>
+      <c r="CL110" s="7"/>
+      <c r="CM110" s="7"/>
       <c r="CN110" s="3"/>
       <c r="CO110" s="3"/>
       <c r="CP110" s="3"/>
@@ -23000,8 +23614,12 @@
       <c r="GW110" s="3"/>
       <c r="GX110" s="3"/>
       <c r="GY110" s="3"/>
+      <c r="GZ110" s="3"/>
+      <c r="HA110" s="3"/>
+      <c r="HB110" s="3"/>
+      <c r="HC110" s="3"/>
     </row>
-    <row r="111" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="111" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C111" s="7"/>
       <c r="D111" s="7"/>
       <c r="E111" s="7"/>
@@ -23087,10 +23705,10 @@
       <c r="CG111" s="7"/>
       <c r="CH111" s="7"/>
       <c r="CI111" s="7"/>
-      <c r="CJ111" s="3"/>
-      <c r="CK111" s="3"/>
-      <c r="CL111" s="3"/>
-      <c r="CM111" s="3"/>
+      <c r="CJ111" s="7"/>
+      <c r="CK111" s="7"/>
+      <c r="CL111" s="7"/>
+      <c r="CM111" s="7"/>
       <c r="CN111" s="3"/>
       <c r="CO111" s="3"/>
       <c r="CP111" s="3"/>
@@ -23207,8 +23825,12 @@
       <c r="GW111" s="3"/>
       <c r="GX111" s="3"/>
       <c r="GY111" s="3"/>
+      <c r="GZ111" s="3"/>
+      <c r="HA111" s="3"/>
+      <c r="HB111" s="3"/>
+      <c r="HC111" s="3"/>
     </row>
-    <row r="112" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="112" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C112" s="7"/>
       <c r="D112" s="7"/>
       <c r="E112" s="7"/>
@@ -23294,10 +23916,10 @@
       <c r="CG112" s="7"/>
       <c r="CH112" s="7"/>
       <c r="CI112" s="7"/>
-      <c r="CJ112" s="3"/>
-      <c r="CK112" s="3"/>
-      <c r="CL112" s="3"/>
-      <c r="CM112" s="3"/>
+      <c r="CJ112" s="7"/>
+      <c r="CK112" s="7"/>
+      <c r="CL112" s="7"/>
+      <c r="CM112" s="7"/>
       <c r="CN112" s="3"/>
       <c r="CO112" s="3"/>
       <c r="CP112" s="3"/>
@@ -23414,8 +24036,12 @@
       <c r="GW112" s="3"/>
       <c r="GX112" s="3"/>
       <c r="GY112" s="3"/>
+      <c r="GZ112" s="3"/>
+      <c r="HA112" s="3"/>
+      <c r="HB112" s="3"/>
+      <c r="HC112" s="3"/>
     </row>
-    <row r="113" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="113" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C113" s="7"/>
       <c r="D113" s="7"/>
       <c r="E113" s="7"/>
@@ -23501,10 +24127,10 @@
       <c r="CG113" s="7"/>
       <c r="CH113" s="7"/>
       <c r="CI113" s="7"/>
-      <c r="CJ113" s="3"/>
-      <c r="CK113" s="3"/>
-      <c r="CL113" s="3"/>
-      <c r="CM113" s="3"/>
+      <c r="CJ113" s="7"/>
+      <c r="CK113" s="7"/>
+      <c r="CL113" s="7"/>
+      <c r="CM113" s="7"/>
       <c r="CN113" s="3"/>
       <c r="CO113" s="3"/>
       <c r="CP113" s="3"/>
@@ -23621,8 +24247,12 @@
       <c r="GW113" s="3"/>
       <c r="GX113" s="3"/>
       <c r="GY113" s="3"/>
+      <c r="GZ113" s="3"/>
+      <c r="HA113" s="3"/>
+      <c r="HB113" s="3"/>
+      <c r="HC113" s="3"/>
     </row>
-    <row r="114" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="114" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C114" s="7"/>
       <c r="D114" s="7"/>
       <c r="E114" s="7"/>
@@ -23708,10 +24338,10 @@
       <c r="CG114" s="7"/>
       <c r="CH114" s="7"/>
       <c r="CI114" s="7"/>
-      <c r="CJ114" s="3"/>
-      <c r="CK114" s="3"/>
-      <c r="CL114" s="3"/>
-      <c r="CM114" s="3"/>
+      <c r="CJ114" s="7"/>
+      <c r="CK114" s="7"/>
+      <c r="CL114" s="7"/>
+      <c r="CM114" s="7"/>
       <c r="CN114" s="3"/>
       <c r="CO114" s="3"/>
       <c r="CP114" s="3"/>
@@ -23828,8 +24458,12 @@
       <c r="GW114" s="3"/>
       <c r="GX114" s="3"/>
       <c r="GY114" s="3"/>
+      <c r="GZ114" s="3"/>
+      <c r="HA114" s="3"/>
+      <c r="HB114" s="3"/>
+      <c r="HC114" s="3"/>
     </row>
-    <row r="115" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="115" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C115" s="7"/>
       <c r="D115" s="7"/>
       <c r="E115" s="7"/>
@@ -23915,10 +24549,10 @@
       <c r="CG115" s="7"/>
       <c r="CH115" s="7"/>
       <c r="CI115" s="7"/>
-      <c r="CJ115" s="3"/>
-      <c r="CK115" s="3"/>
-      <c r="CL115" s="3"/>
-      <c r="CM115" s="3"/>
+      <c r="CJ115" s="7"/>
+      <c r="CK115" s="7"/>
+      <c r="CL115" s="7"/>
+      <c r="CM115" s="7"/>
       <c r="CN115" s="3"/>
       <c r="CO115" s="3"/>
       <c r="CP115" s="3"/>
@@ -24035,8 +24669,12 @@
       <c r="GW115" s="3"/>
       <c r="GX115" s="3"/>
       <c r="GY115" s="3"/>
+      <c r="GZ115" s="3"/>
+      <c r="HA115" s="3"/>
+      <c r="HB115" s="3"/>
+      <c r="HC115" s="3"/>
     </row>
-    <row r="116" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="116" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C116" s="7"/>
       <c r="D116" s="7"/>
       <c r="E116" s="7"/>
@@ -24122,10 +24760,10 @@
       <c r="CG116" s="7"/>
       <c r="CH116" s="7"/>
       <c r="CI116" s="7"/>
-      <c r="CJ116" s="3"/>
-      <c r="CK116" s="3"/>
-      <c r="CL116" s="3"/>
-      <c r="CM116" s="3"/>
+      <c r="CJ116" s="7"/>
+      <c r="CK116" s="7"/>
+      <c r="CL116" s="7"/>
+      <c r="CM116" s="7"/>
       <c r="CN116" s="3"/>
       <c r="CO116" s="3"/>
       <c r="CP116" s="3"/>
@@ -24242,8 +24880,12 @@
       <c r="GW116" s="3"/>
       <c r="GX116" s="3"/>
       <c r="GY116" s="3"/>
+      <c r="GZ116" s="3"/>
+      <c r="HA116" s="3"/>
+      <c r="HB116" s="3"/>
+      <c r="HC116" s="3"/>
     </row>
-    <row r="117" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="117" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C117" s="7"/>
       <c r="D117" s="7"/>
       <c r="E117" s="7"/>
@@ -24329,10 +24971,10 @@
       <c r="CG117" s="7"/>
       <c r="CH117" s="7"/>
       <c r="CI117" s="7"/>
-      <c r="CJ117" s="3"/>
-      <c r="CK117" s="3"/>
-      <c r="CL117" s="3"/>
-      <c r="CM117" s="3"/>
+      <c r="CJ117" s="7"/>
+      <c r="CK117" s="7"/>
+      <c r="CL117" s="7"/>
+      <c r="CM117" s="7"/>
       <c r="CN117" s="3"/>
       <c r="CO117" s="3"/>
       <c r="CP117" s="3"/>
@@ -24449,8 +25091,12 @@
       <c r="GW117" s="3"/>
       <c r="GX117" s="3"/>
       <c r="GY117" s="3"/>
+      <c r="GZ117" s="3"/>
+      <c r="HA117" s="3"/>
+      <c r="HB117" s="3"/>
+      <c r="HC117" s="3"/>
     </row>
-    <row r="118" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="118" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C118" s="7"/>
       <c r="D118" s="7"/>
       <c r="E118" s="7"/>
@@ -24536,10 +25182,10 @@
       <c r="CG118" s="7"/>
       <c r="CH118" s="7"/>
       <c r="CI118" s="7"/>
-      <c r="CJ118" s="3"/>
-      <c r="CK118" s="3"/>
-      <c r="CL118" s="3"/>
-      <c r="CM118" s="3"/>
+      <c r="CJ118" s="7"/>
+      <c r="CK118" s="7"/>
+      <c r="CL118" s="7"/>
+      <c r="CM118" s="7"/>
       <c r="CN118" s="3"/>
       <c r="CO118" s="3"/>
       <c r="CP118" s="3"/>
@@ -24656,8 +25302,12 @@
       <c r="GW118" s="3"/>
       <c r="GX118" s="3"/>
       <c r="GY118" s="3"/>
+      <c r="GZ118" s="3"/>
+      <c r="HA118" s="3"/>
+      <c r="HB118" s="3"/>
+      <c r="HC118" s="3"/>
     </row>
-    <row r="119" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="119" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C119" s="7"/>
       <c r="D119" s="7"/>
       <c r="E119" s="7"/>
@@ -24743,10 +25393,10 @@
       <c r="CG119" s="7"/>
       <c r="CH119" s="7"/>
       <c r="CI119" s="7"/>
-      <c r="CJ119" s="3"/>
-      <c r="CK119" s="3"/>
-      <c r="CL119" s="3"/>
-      <c r="CM119" s="3"/>
+      <c r="CJ119" s="7"/>
+      <c r="CK119" s="7"/>
+      <c r="CL119" s="7"/>
+      <c r="CM119" s="7"/>
       <c r="CN119" s="3"/>
       <c r="CO119" s="3"/>
       <c r="CP119" s="3"/>
@@ -24863,8 +25513,12 @@
       <c r="GW119" s="3"/>
       <c r="GX119" s="3"/>
       <c r="GY119" s="3"/>
+      <c r="GZ119" s="3"/>
+      <c r="HA119" s="3"/>
+      <c r="HB119" s="3"/>
+      <c r="HC119" s="3"/>
     </row>
-    <row r="120" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="120" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C120" s="7"/>
       <c r="D120" s="7"/>
       <c r="E120" s="7"/>
@@ -24950,10 +25604,10 @@
       <c r="CG120" s="7"/>
       <c r="CH120" s="7"/>
       <c r="CI120" s="7"/>
-      <c r="CJ120" s="3"/>
-      <c r="CK120" s="3"/>
-      <c r="CL120" s="3"/>
-      <c r="CM120" s="3"/>
+      <c r="CJ120" s="7"/>
+      <c r="CK120" s="7"/>
+      <c r="CL120" s="7"/>
+      <c r="CM120" s="7"/>
       <c r="CN120" s="3"/>
       <c r="CO120" s="3"/>
       <c r="CP120" s="3"/>
@@ -25070,8 +25724,12 @@
       <c r="GW120" s="3"/>
       <c r="GX120" s="3"/>
       <c r="GY120" s="3"/>
+      <c r="GZ120" s="3"/>
+      <c r="HA120" s="3"/>
+      <c r="HB120" s="3"/>
+      <c r="HC120" s="3"/>
     </row>
-    <row r="121" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="121" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C121" s="7"/>
       <c r="D121" s="7"/>
       <c r="E121" s="7"/>
@@ -25157,10 +25815,10 @@
       <c r="CG121" s="7"/>
       <c r="CH121" s="7"/>
       <c r="CI121" s="7"/>
-      <c r="CJ121" s="3"/>
-      <c r="CK121" s="3"/>
-      <c r="CL121" s="3"/>
-      <c r="CM121" s="3"/>
+      <c r="CJ121" s="7"/>
+      <c r="CK121" s="7"/>
+      <c r="CL121" s="7"/>
+      <c r="CM121" s="7"/>
       <c r="CN121" s="3"/>
       <c r="CO121" s="3"/>
       <c r="CP121" s="3"/>
@@ -25277,8 +25935,12 @@
       <c r="GW121" s="3"/>
       <c r="GX121" s="3"/>
       <c r="GY121" s="3"/>
+      <c r="GZ121" s="3"/>
+      <c r="HA121" s="3"/>
+      <c r="HB121" s="3"/>
+      <c r="HC121" s="3"/>
     </row>
-    <row r="122" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="122" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C122" s="7"/>
       <c r="D122" s="7"/>
       <c r="E122" s="7"/>
@@ -25364,10 +26026,10 @@
       <c r="CG122" s="7"/>
       <c r="CH122" s="7"/>
       <c r="CI122" s="7"/>
-      <c r="CJ122" s="3"/>
-      <c r="CK122" s="3"/>
-      <c r="CL122" s="3"/>
-      <c r="CM122" s="3"/>
+      <c r="CJ122" s="7"/>
+      <c r="CK122" s="7"/>
+      <c r="CL122" s="7"/>
+      <c r="CM122" s="7"/>
       <c r="CN122" s="3"/>
       <c r="CO122" s="3"/>
       <c r="CP122" s="3"/>
@@ -25484,8 +26146,12 @@
       <c r="GW122" s="3"/>
       <c r="GX122" s="3"/>
       <c r="GY122" s="3"/>
+      <c r="GZ122" s="3"/>
+      <c r="HA122" s="3"/>
+      <c r="HB122" s="3"/>
+      <c r="HC122" s="3"/>
     </row>
-    <row r="123" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="123" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C123" s="7"/>
       <c r="D123" s="7"/>
       <c r="E123" s="7"/>
@@ -25571,10 +26237,10 @@
       <c r="CG123" s="7"/>
       <c r="CH123" s="7"/>
       <c r="CI123" s="7"/>
-      <c r="CJ123" s="3"/>
-      <c r="CK123" s="3"/>
-      <c r="CL123" s="3"/>
-      <c r="CM123" s="3"/>
+      <c r="CJ123" s="7"/>
+      <c r="CK123" s="7"/>
+      <c r="CL123" s="7"/>
+      <c r="CM123" s="7"/>
       <c r="CN123" s="3"/>
       <c r="CO123" s="3"/>
       <c r="CP123" s="3"/>
@@ -25691,8 +26357,12 @@
       <c r="GW123" s="3"/>
       <c r="GX123" s="3"/>
       <c r="GY123" s="3"/>
+      <c r="GZ123" s="3"/>
+      <c r="HA123" s="3"/>
+      <c r="HB123" s="3"/>
+      <c r="HC123" s="3"/>
     </row>
-    <row r="124" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="124" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C124" s="7"/>
       <c r="D124" s="7"/>
       <c r="E124" s="7"/>
@@ -25778,10 +26448,10 @@
       <c r="CG124" s="7"/>
       <c r="CH124" s="7"/>
       <c r="CI124" s="7"/>
-      <c r="CJ124" s="3"/>
-      <c r="CK124" s="3"/>
-      <c r="CL124" s="3"/>
-      <c r="CM124" s="3"/>
+      <c r="CJ124" s="7"/>
+      <c r="CK124" s="7"/>
+      <c r="CL124" s="7"/>
+      <c r="CM124" s="7"/>
       <c r="CN124" s="3"/>
       <c r="CO124" s="3"/>
       <c r="CP124" s="3"/>
@@ -25898,8 +26568,12 @@
       <c r="GW124" s="3"/>
       <c r="GX124" s="3"/>
       <c r="GY124" s="3"/>
+      <c r="GZ124" s="3"/>
+      <c r="HA124" s="3"/>
+      <c r="HB124" s="3"/>
+      <c r="HC124" s="3"/>
     </row>
-    <row r="125" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="125" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C125" s="7"/>
       <c r="D125" s="7"/>
       <c r="E125" s="7"/>
@@ -25985,10 +26659,10 @@
       <c r="CG125" s="7"/>
       <c r="CH125" s="7"/>
       <c r="CI125" s="7"/>
-      <c r="CJ125" s="3"/>
-      <c r="CK125" s="3"/>
-      <c r="CL125" s="3"/>
-      <c r="CM125" s="3"/>
+      <c r="CJ125" s="7"/>
+      <c r="CK125" s="7"/>
+      <c r="CL125" s="7"/>
+      <c r="CM125" s="7"/>
       <c r="CN125" s="3"/>
       <c r="CO125" s="3"/>
       <c r="CP125" s="3"/>
@@ -26105,8 +26779,12 @@
       <c r="GW125" s="3"/>
       <c r="GX125" s="3"/>
       <c r="GY125" s="3"/>
+      <c r="GZ125" s="3"/>
+      <c r="HA125" s="3"/>
+      <c r="HB125" s="3"/>
+      <c r="HC125" s="3"/>
     </row>
-    <row r="126" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="126" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C126" s="7"/>
       <c r="D126" s="7"/>
       <c r="E126" s="7"/>
@@ -26192,10 +26870,10 @@
       <c r="CG126" s="7"/>
       <c r="CH126" s="7"/>
       <c r="CI126" s="7"/>
-      <c r="CJ126" s="3"/>
-      <c r="CK126" s="3"/>
-      <c r="CL126" s="3"/>
-      <c r="CM126" s="3"/>
+      <c r="CJ126" s="7"/>
+      <c r="CK126" s="7"/>
+      <c r="CL126" s="7"/>
+      <c r="CM126" s="7"/>
       <c r="CN126" s="3"/>
       <c r="CO126" s="3"/>
       <c r="CP126" s="3"/>
@@ -26312,8 +26990,12 @@
       <c r="GW126" s="3"/>
       <c r="GX126" s="3"/>
       <c r="GY126" s="3"/>
+      <c r="GZ126" s="3"/>
+      <c r="HA126" s="3"/>
+      <c r="HB126" s="3"/>
+      <c r="HC126" s="3"/>
     </row>
-    <row r="127" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="127" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C127" s="7"/>
       <c r="D127" s="7"/>
       <c r="E127" s="7"/>
@@ -26399,10 +27081,10 @@
       <c r="CG127" s="7"/>
       <c r="CH127" s="7"/>
       <c r="CI127" s="7"/>
-      <c r="CJ127" s="3"/>
-      <c r="CK127" s="3"/>
-      <c r="CL127" s="3"/>
-      <c r="CM127" s="3"/>
+      <c r="CJ127" s="7"/>
+      <c r="CK127" s="7"/>
+      <c r="CL127" s="7"/>
+      <c r="CM127" s="7"/>
       <c r="CN127" s="3"/>
       <c r="CO127" s="3"/>
       <c r="CP127" s="3"/>
@@ -26519,8 +27201,12 @@
       <c r="GW127" s="3"/>
       <c r="GX127" s="3"/>
       <c r="GY127" s="3"/>
+      <c r="GZ127" s="3"/>
+      <c r="HA127" s="3"/>
+      <c r="HB127" s="3"/>
+      <c r="HC127" s="3"/>
     </row>
-    <row r="128" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="128" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C128" s="7"/>
       <c r="D128" s="7"/>
       <c r="E128" s="7"/>
@@ -26606,10 +27292,10 @@
       <c r="CG128" s="7"/>
       <c r="CH128" s="7"/>
       <c r="CI128" s="7"/>
-      <c r="CJ128" s="3"/>
-      <c r="CK128" s="3"/>
-      <c r="CL128" s="3"/>
-      <c r="CM128" s="3"/>
+      <c r="CJ128" s="7"/>
+      <c r="CK128" s="7"/>
+      <c r="CL128" s="7"/>
+      <c r="CM128" s="7"/>
       <c r="CN128" s="3"/>
       <c r="CO128" s="3"/>
       <c r="CP128" s="3"/>
@@ -26726,8 +27412,12 @@
       <c r="GW128" s="3"/>
       <c r="GX128" s="3"/>
       <c r="GY128" s="3"/>
+      <c r="GZ128" s="3"/>
+      <c r="HA128" s="3"/>
+      <c r="HB128" s="3"/>
+      <c r="HC128" s="3"/>
     </row>
-    <row r="129" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="129" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C129" s="7"/>
       <c r="D129" s="7"/>
       <c r="E129" s="7"/>
@@ -26813,10 +27503,10 @@
       <c r="CG129" s="7"/>
       <c r="CH129" s="7"/>
       <c r="CI129" s="7"/>
-      <c r="CJ129" s="3"/>
-      <c r="CK129" s="3"/>
-      <c r="CL129" s="3"/>
-      <c r="CM129" s="3"/>
+      <c r="CJ129" s="7"/>
+      <c r="CK129" s="7"/>
+      <c r="CL129" s="7"/>
+      <c r="CM129" s="7"/>
       <c r="CN129" s="3"/>
       <c r="CO129" s="3"/>
       <c r="CP129" s="3"/>
@@ -26933,8 +27623,12 @@
       <c r="GW129" s="3"/>
       <c r="GX129" s="3"/>
       <c r="GY129" s="3"/>
+      <c r="GZ129" s="3"/>
+      <c r="HA129" s="3"/>
+      <c r="HB129" s="3"/>
+      <c r="HC129" s="3"/>
     </row>
-    <row r="130" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="130" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C130" s="7"/>
       <c r="D130" s="7"/>
       <c r="E130" s="7"/>
@@ -27020,10 +27714,10 @@
       <c r="CG130" s="7"/>
       <c r="CH130" s="7"/>
       <c r="CI130" s="7"/>
-      <c r="CJ130" s="3"/>
-      <c r="CK130" s="3"/>
-      <c r="CL130" s="3"/>
-      <c r="CM130" s="3"/>
+      <c r="CJ130" s="7"/>
+      <c r="CK130" s="7"/>
+      <c r="CL130" s="7"/>
+      <c r="CM130" s="7"/>
       <c r="CN130" s="3"/>
       <c r="CO130" s="3"/>
       <c r="CP130" s="3"/>
@@ -27140,8 +27834,12 @@
       <c r="GW130" s="3"/>
       <c r="GX130" s="3"/>
       <c r="GY130" s="3"/>
+      <c r="GZ130" s="3"/>
+      <c r="HA130" s="3"/>
+      <c r="HB130" s="3"/>
+      <c r="HC130" s="3"/>
     </row>
-    <row r="131" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="131" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C131" s="7"/>
       <c r="D131" s="7"/>
       <c r="E131" s="7"/>
@@ -27227,10 +27925,10 @@
       <c r="CG131" s="7"/>
       <c r="CH131" s="7"/>
       <c r="CI131" s="7"/>
-      <c r="CJ131" s="3"/>
-      <c r="CK131" s="3"/>
-      <c r="CL131" s="3"/>
-      <c r="CM131" s="3"/>
+      <c r="CJ131" s="7"/>
+      <c r="CK131" s="7"/>
+      <c r="CL131" s="7"/>
+      <c r="CM131" s="7"/>
       <c r="CN131" s="3"/>
       <c r="CO131" s="3"/>
       <c r="CP131" s="3"/>
@@ -27347,8 +28045,12 @@
       <c r="GW131" s="3"/>
       <c r="GX131" s="3"/>
       <c r="GY131" s="3"/>
+      <c r="GZ131" s="3"/>
+      <c r="HA131" s="3"/>
+      <c r="HB131" s="3"/>
+      <c r="HC131" s="3"/>
     </row>
-    <row r="132" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="132" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C132" s="7"/>
       <c r="D132" s="7"/>
       <c r="E132" s="7"/>
@@ -27434,10 +28136,10 @@
       <c r="CG132" s="7"/>
       <c r="CH132" s="7"/>
       <c r="CI132" s="7"/>
-      <c r="CJ132" s="3"/>
-      <c r="CK132" s="3"/>
-      <c r="CL132" s="3"/>
-      <c r="CM132" s="3"/>
+      <c r="CJ132" s="7"/>
+      <c r="CK132" s="7"/>
+      <c r="CL132" s="7"/>
+      <c r="CM132" s="7"/>
       <c r="CN132" s="3"/>
       <c r="CO132" s="3"/>
       <c r="CP132" s="3"/>
@@ -27554,8 +28256,12 @@
       <c r="GW132" s="3"/>
       <c r="GX132" s="3"/>
       <c r="GY132" s="3"/>
+      <c r="GZ132" s="3"/>
+      <c r="HA132" s="3"/>
+      <c r="HB132" s="3"/>
+      <c r="HC132" s="3"/>
     </row>
-    <row r="133" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="133" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C133" s="7"/>
       <c r="D133" s="7"/>
       <c r="E133" s="7"/>
@@ -27641,10 +28347,10 @@
       <c r="CG133" s="7"/>
       <c r="CH133" s="7"/>
       <c r="CI133" s="7"/>
-      <c r="CJ133" s="3"/>
-      <c r="CK133" s="3"/>
-      <c r="CL133" s="3"/>
-      <c r="CM133" s="3"/>
+      <c r="CJ133" s="7"/>
+      <c r="CK133" s="7"/>
+      <c r="CL133" s="7"/>
+      <c r="CM133" s="7"/>
       <c r="CN133" s="3"/>
       <c r="CO133" s="3"/>
       <c r="CP133" s="3"/>
@@ -27761,8 +28467,12 @@
       <c r="GW133" s="3"/>
       <c r="GX133" s="3"/>
       <c r="GY133" s="3"/>
+      <c r="GZ133" s="3"/>
+      <c r="HA133" s="3"/>
+      <c r="HB133" s="3"/>
+      <c r="HC133" s="3"/>
     </row>
-    <row r="134" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="134" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C134" s="7"/>
       <c r="D134" s="7"/>
       <c r="E134" s="7"/>
@@ -27848,10 +28558,10 @@
       <c r="CG134" s="7"/>
       <c r="CH134" s="7"/>
       <c r="CI134" s="7"/>
-      <c r="CJ134" s="3"/>
-      <c r="CK134" s="3"/>
-      <c r="CL134" s="3"/>
-      <c r="CM134" s="3"/>
+      <c r="CJ134" s="7"/>
+      <c r="CK134" s="7"/>
+      <c r="CL134" s="7"/>
+      <c r="CM134" s="7"/>
       <c r="CN134" s="3"/>
       <c r="CO134" s="3"/>
       <c r="CP134" s="3"/>
@@ -27968,8 +28678,12 @@
       <c r="GW134" s="3"/>
       <c r="GX134" s="3"/>
       <c r="GY134" s="3"/>
+      <c r="GZ134" s="3"/>
+      <c r="HA134" s="3"/>
+      <c r="HB134" s="3"/>
+      <c r="HC134" s="3"/>
     </row>
-    <row r="135" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="135" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C135" s="7"/>
       <c r="D135" s="7"/>
       <c r="E135" s="7"/>
@@ -28055,10 +28769,10 @@
       <c r="CG135" s="7"/>
       <c r="CH135" s="7"/>
       <c r="CI135" s="7"/>
-      <c r="CJ135" s="3"/>
-      <c r="CK135" s="3"/>
-      <c r="CL135" s="3"/>
-      <c r="CM135" s="3"/>
+      <c r="CJ135" s="7"/>
+      <c r="CK135" s="7"/>
+      <c r="CL135" s="7"/>
+      <c r="CM135" s="7"/>
       <c r="CN135" s="3"/>
       <c r="CO135" s="3"/>
       <c r="CP135" s="3"/>
@@ -28175,8 +28889,12 @@
       <c r="GW135" s="3"/>
       <c r="GX135" s="3"/>
       <c r="GY135" s="3"/>
+      <c r="GZ135" s="3"/>
+      <c r="HA135" s="3"/>
+      <c r="HB135" s="3"/>
+      <c r="HC135" s="3"/>
     </row>
-    <row r="136" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="136" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C136" s="7"/>
       <c r="D136" s="7"/>
       <c r="E136" s="7"/>
@@ -28262,10 +28980,10 @@
       <c r="CG136" s="7"/>
       <c r="CH136" s="7"/>
       <c r="CI136" s="7"/>
-      <c r="CJ136" s="3"/>
-      <c r="CK136" s="3"/>
-      <c r="CL136" s="3"/>
-      <c r="CM136" s="3"/>
+      <c r="CJ136" s="7"/>
+      <c r="CK136" s="7"/>
+      <c r="CL136" s="7"/>
+      <c r="CM136" s="7"/>
       <c r="CN136" s="3"/>
       <c r="CO136" s="3"/>
       <c r="CP136" s="3"/>
@@ -28382,8 +29100,12 @@
       <c r="GW136" s="3"/>
       <c r="GX136" s="3"/>
       <c r="GY136" s="3"/>
+      <c r="GZ136" s="3"/>
+      <c r="HA136" s="3"/>
+      <c r="HB136" s="3"/>
+      <c r="HC136" s="3"/>
     </row>
-    <row r="137" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="137" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C137" s="7"/>
       <c r="D137" s="7"/>
       <c r="E137" s="7"/>
@@ -28469,10 +29191,10 @@
       <c r="CG137" s="7"/>
       <c r="CH137" s="7"/>
       <c r="CI137" s="7"/>
-      <c r="CJ137" s="3"/>
-      <c r="CK137" s="3"/>
-      <c r="CL137" s="3"/>
-      <c r="CM137" s="3"/>
+      <c r="CJ137" s="7"/>
+      <c r="CK137" s="7"/>
+      <c r="CL137" s="7"/>
+      <c r="CM137" s="7"/>
       <c r="CN137" s="3"/>
       <c r="CO137" s="3"/>
       <c r="CP137" s="3"/>
@@ -28589,8 +29311,12 @@
       <c r="GW137" s="3"/>
       <c r="GX137" s="3"/>
       <c r="GY137" s="3"/>
+      <c r="GZ137" s="3"/>
+      <c r="HA137" s="3"/>
+      <c r="HB137" s="3"/>
+      <c r="HC137" s="3"/>
     </row>
-    <row r="138" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="138" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C138" s="7"/>
       <c r="D138" s="7"/>
       <c r="E138" s="7"/>
@@ -28676,10 +29402,10 @@
       <c r="CG138" s="7"/>
       <c r="CH138" s="7"/>
       <c r="CI138" s="7"/>
-      <c r="CJ138" s="3"/>
-      <c r="CK138" s="3"/>
-      <c r="CL138" s="3"/>
-      <c r="CM138" s="3"/>
+      <c r="CJ138" s="7"/>
+      <c r="CK138" s="7"/>
+      <c r="CL138" s="7"/>
+      <c r="CM138" s="7"/>
       <c r="CN138" s="3"/>
       <c r="CO138" s="3"/>
       <c r="CP138" s="3"/>
@@ -28796,8 +29522,12 @@
       <c r="GW138" s="3"/>
       <c r="GX138" s="3"/>
       <c r="GY138" s="3"/>
+      <c r="GZ138" s="3"/>
+      <c r="HA138" s="3"/>
+      <c r="HB138" s="3"/>
+      <c r="HC138" s="3"/>
     </row>
-    <row r="139" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="139" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C139" s="7"/>
       <c r="D139" s="7"/>
       <c r="E139" s="7"/>
@@ -28883,10 +29613,10 @@
       <c r="CG139" s="7"/>
       <c r="CH139" s="7"/>
       <c r="CI139" s="7"/>
-      <c r="CJ139" s="3"/>
-      <c r="CK139" s="3"/>
-      <c r="CL139" s="3"/>
-      <c r="CM139" s="3"/>
+      <c r="CJ139" s="7"/>
+      <c r="CK139" s="7"/>
+      <c r="CL139" s="7"/>
+      <c r="CM139" s="7"/>
       <c r="CN139" s="3"/>
       <c r="CO139" s="3"/>
       <c r="CP139" s="3"/>
@@ -29003,8 +29733,12 @@
       <c r="GW139" s="3"/>
       <c r="GX139" s="3"/>
       <c r="GY139" s="3"/>
+      <c r="GZ139" s="3"/>
+      <c r="HA139" s="3"/>
+      <c r="HB139" s="3"/>
+      <c r="HC139" s="3"/>
     </row>
-    <row r="140" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="140" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C140" s="7"/>
       <c r="D140" s="7"/>
       <c r="E140" s="7"/>
@@ -29090,10 +29824,10 @@
       <c r="CG140" s="7"/>
       <c r="CH140" s="7"/>
       <c r="CI140" s="7"/>
-      <c r="CJ140" s="3"/>
-      <c r="CK140" s="3"/>
-      <c r="CL140" s="3"/>
-      <c r="CM140" s="3"/>
+      <c r="CJ140" s="7"/>
+      <c r="CK140" s="7"/>
+      <c r="CL140" s="7"/>
+      <c r="CM140" s="7"/>
       <c r="CN140" s="3"/>
       <c r="CO140" s="3"/>
       <c r="CP140" s="3"/>
@@ -29210,8 +29944,12 @@
       <c r="GW140" s="3"/>
       <c r="GX140" s="3"/>
       <c r="GY140" s="3"/>
+      <c r="GZ140" s="3"/>
+      <c r="HA140" s="3"/>
+      <c r="HB140" s="3"/>
+      <c r="HC140" s="3"/>
     </row>
-    <row r="141" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="141" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C141" s="7"/>
       <c r="D141" s="7"/>
       <c r="E141" s="7"/>
@@ -29297,10 +30035,10 @@
       <c r="CG141" s="7"/>
       <c r="CH141" s="7"/>
       <c r="CI141" s="7"/>
-      <c r="CJ141" s="3"/>
-      <c r="CK141" s="3"/>
-      <c r="CL141" s="3"/>
-      <c r="CM141" s="3"/>
+      <c r="CJ141" s="7"/>
+      <c r="CK141" s="7"/>
+      <c r="CL141" s="7"/>
+      <c r="CM141" s="7"/>
       <c r="CN141" s="3"/>
       <c r="CO141" s="3"/>
       <c r="CP141" s="3"/>
@@ -29417,8 +30155,12 @@
       <c r="GW141" s="3"/>
       <c r="GX141" s="3"/>
       <c r="GY141" s="3"/>
+      <c r="GZ141" s="3"/>
+      <c r="HA141" s="3"/>
+      <c r="HB141" s="3"/>
+      <c r="HC141" s="3"/>
     </row>
-    <row r="142" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="142" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C142" s="7"/>
       <c r="D142" s="7"/>
       <c r="E142" s="7"/>
@@ -29504,10 +30246,10 @@
       <c r="CG142" s="7"/>
       <c r="CH142" s="7"/>
       <c r="CI142" s="7"/>
-      <c r="CJ142" s="3"/>
-      <c r="CK142" s="3"/>
-      <c r="CL142" s="3"/>
-      <c r="CM142" s="3"/>
+      <c r="CJ142" s="7"/>
+      <c r="CK142" s="7"/>
+      <c r="CL142" s="7"/>
+      <c r="CM142" s="7"/>
       <c r="CN142" s="3"/>
       <c r="CO142" s="3"/>
       <c r="CP142" s="3"/>
@@ -29624,8 +30366,12 @@
       <c r="GW142" s="3"/>
       <c r="GX142" s="3"/>
       <c r="GY142" s="3"/>
+      <c r="GZ142" s="3"/>
+      <c r="HA142" s="3"/>
+      <c r="HB142" s="3"/>
+      <c r="HC142" s="3"/>
     </row>
-    <row r="143" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="143" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C143" s="7"/>
       <c r="D143" s="7"/>
       <c r="E143" s="7"/>
@@ -29711,10 +30457,10 @@
       <c r="CG143" s="7"/>
       <c r="CH143" s="7"/>
       <c r="CI143" s="7"/>
-      <c r="CJ143" s="3"/>
-      <c r="CK143" s="3"/>
-      <c r="CL143" s="3"/>
-      <c r="CM143" s="3"/>
+      <c r="CJ143" s="7"/>
+      <c r="CK143" s="7"/>
+      <c r="CL143" s="7"/>
+      <c r="CM143" s="7"/>
       <c r="CN143" s="3"/>
       <c r="CO143" s="3"/>
       <c r="CP143" s="3"/>
@@ -29831,8 +30577,12 @@
       <c r="GW143" s="3"/>
       <c r="GX143" s="3"/>
       <c r="GY143" s="3"/>
+      <c r="GZ143" s="3"/>
+      <c r="HA143" s="3"/>
+      <c r="HB143" s="3"/>
+      <c r="HC143" s="3"/>
     </row>
-    <row r="144" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="144" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C144" s="7"/>
       <c r="D144" s="7"/>
       <c r="E144" s="7"/>
@@ -29918,10 +30668,10 @@
       <c r="CG144" s="7"/>
       <c r="CH144" s="7"/>
       <c r="CI144" s="7"/>
-      <c r="CJ144" s="3"/>
-      <c r="CK144" s="3"/>
-      <c r="CL144" s="3"/>
-      <c r="CM144" s="3"/>
+      <c r="CJ144" s="7"/>
+      <c r="CK144" s="7"/>
+      <c r="CL144" s="7"/>
+      <c r="CM144" s="7"/>
       <c r="CN144" s="3"/>
       <c r="CO144" s="3"/>
       <c r="CP144" s="3"/>
@@ -30038,8 +30788,12 @@
       <c r="GW144" s="3"/>
       <c r="GX144" s="3"/>
       <c r="GY144" s="3"/>
+      <c r="GZ144" s="3"/>
+      <c r="HA144" s="3"/>
+      <c r="HB144" s="3"/>
+      <c r="HC144" s="3"/>
     </row>
-    <row r="145" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="145" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C145" s="7"/>
       <c r="D145" s="7"/>
       <c r="E145" s="7"/>
@@ -30125,10 +30879,10 @@
       <c r="CG145" s="7"/>
       <c r="CH145" s="7"/>
       <c r="CI145" s="7"/>
-      <c r="CJ145" s="3"/>
-      <c r="CK145" s="3"/>
-      <c r="CL145" s="3"/>
-      <c r="CM145" s="3"/>
+      <c r="CJ145" s="7"/>
+      <c r="CK145" s="7"/>
+      <c r="CL145" s="7"/>
+      <c r="CM145" s="7"/>
       <c r="CN145" s="3"/>
       <c r="CO145" s="3"/>
       <c r="CP145" s="3"/>
@@ -30245,8 +30999,12 @@
       <c r="GW145" s="3"/>
       <c r="GX145" s="3"/>
       <c r="GY145" s="3"/>
+      <c r="GZ145" s="3"/>
+      <c r="HA145" s="3"/>
+      <c r="HB145" s="3"/>
+      <c r="HC145" s="3"/>
     </row>
-    <row r="146" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="146" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C146" s="7"/>
       <c r="D146" s="7"/>
       <c r="E146" s="7"/>
@@ -30332,10 +31090,10 @@
       <c r="CG146" s="7"/>
       <c r="CH146" s="7"/>
       <c r="CI146" s="7"/>
-      <c r="CJ146" s="3"/>
-      <c r="CK146" s="3"/>
-      <c r="CL146" s="3"/>
-      <c r="CM146" s="3"/>
+      <c r="CJ146" s="7"/>
+      <c r="CK146" s="7"/>
+      <c r="CL146" s="7"/>
+      <c r="CM146" s="7"/>
       <c r="CN146" s="3"/>
       <c r="CO146" s="3"/>
       <c r="CP146" s="3"/>
@@ -30452,8 +31210,12 @@
       <c r="GW146" s="3"/>
       <c r="GX146" s="3"/>
       <c r="GY146" s="3"/>
+      <c r="GZ146" s="3"/>
+      <c r="HA146" s="3"/>
+      <c r="HB146" s="3"/>
+      <c r="HC146" s="3"/>
     </row>
-    <row r="147" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="147" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C147" s="7"/>
       <c r="D147" s="7"/>
       <c r="E147" s="7"/>
@@ -30539,10 +31301,10 @@
       <c r="CG147" s="7"/>
       <c r="CH147" s="7"/>
       <c r="CI147" s="7"/>
-      <c r="CJ147" s="3"/>
-      <c r="CK147" s="3"/>
-      <c r="CL147" s="3"/>
-      <c r="CM147" s="3"/>
+      <c r="CJ147" s="7"/>
+      <c r="CK147" s="7"/>
+      <c r="CL147" s="7"/>
+      <c r="CM147" s="7"/>
       <c r="CN147" s="3"/>
       <c r="CO147" s="3"/>
       <c r="CP147" s="3"/>
@@ -30659,8 +31421,12 @@
       <c r="GW147" s="3"/>
       <c r="GX147" s="3"/>
       <c r="GY147" s="3"/>
+      <c r="GZ147" s="3"/>
+      <c r="HA147" s="3"/>
+      <c r="HB147" s="3"/>
+      <c r="HC147" s="3"/>
     </row>
-    <row r="148" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="148" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C148" s="7"/>
       <c r="D148" s="7"/>
       <c r="E148" s="7"/>
@@ -30746,10 +31512,10 @@
       <c r="CG148" s="7"/>
       <c r="CH148" s="7"/>
       <c r="CI148" s="7"/>
-      <c r="CJ148" s="3"/>
-      <c r="CK148" s="3"/>
-      <c r="CL148" s="3"/>
-      <c r="CM148" s="3"/>
+      <c r="CJ148" s="7"/>
+      <c r="CK148" s="7"/>
+      <c r="CL148" s="7"/>
+      <c r="CM148" s="7"/>
       <c r="CN148" s="3"/>
       <c r="CO148" s="3"/>
       <c r="CP148" s="3"/>
@@ -30866,8 +31632,12 @@
       <c r="GW148" s="3"/>
       <c r="GX148" s="3"/>
       <c r="GY148" s="3"/>
+      <c r="GZ148" s="3"/>
+      <c r="HA148" s="3"/>
+      <c r="HB148" s="3"/>
+      <c r="HC148" s="3"/>
     </row>
-    <row r="149" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="149" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C149" s="7"/>
       <c r="D149" s="7"/>
       <c r="E149" s="7"/>
@@ -30953,10 +31723,10 @@
       <c r="CG149" s="7"/>
       <c r="CH149" s="7"/>
       <c r="CI149" s="7"/>
-      <c r="CJ149" s="3"/>
-      <c r="CK149" s="3"/>
-      <c r="CL149" s="3"/>
-      <c r="CM149" s="3"/>
+      <c r="CJ149" s="7"/>
+      <c r="CK149" s="7"/>
+      <c r="CL149" s="7"/>
+      <c r="CM149" s="7"/>
       <c r="CN149" s="3"/>
       <c r="CO149" s="3"/>
       <c r="CP149" s="3"/>
@@ -31073,8 +31843,12 @@
       <c r="GW149" s="3"/>
       <c r="GX149" s="3"/>
       <c r="GY149" s="3"/>
+      <c r="GZ149" s="3"/>
+      <c r="HA149" s="3"/>
+      <c r="HB149" s="3"/>
+      <c r="HC149" s="3"/>
     </row>
-    <row r="150" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="150" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C150" s="7"/>
       <c r="D150" s="7"/>
       <c r="E150" s="7"/>
@@ -31160,10 +31934,10 @@
       <c r="CG150" s="7"/>
       <c r="CH150" s="7"/>
       <c r="CI150" s="7"/>
-      <c r="CJ150" s="3"/>
-      <c r="CK150" s="3"/>
-      <c r="CL150" s="3"/>
-      <c r="CM150" s="3"/>
+      <c r="CJ150" s="7"/>
+      <c r="CK150" s="7"/>
+      <c r="CL150" s="7"/>
+      <c r="CM150" s="7"/>
       <c r="CN150" s="3"/>
       <c r="CO150" s="3"/>
       <c r="CP150" s="3"/>
@@ -31280,8 +32054,12 @@
       <c r="GW150" s="3"/>
       <c r="GX150" s="3"/>
       <c r="GY150" s="3"/>
+      <c r="GZ150" s="3"/>
+      <c r="HA150" s="3"/>
+      <c r="HB150" s="3"/>
+      <c r="HC150" s="3"/>
     </row>
-    <row r="151" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="151" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C151" s="7"/>
       <c r="D151" s="7"/>
       <c r="E151" s="7"/>
@@ -31367,10 +32145,10 @@
       <c r="CG151" s="7"/>
       <c r="CH151" s="7"/>
       <c r="CI151" s="7"/>
-      <c r="CJ151" s="3"/>
-      <c r="CK151" s="3"/>
-      <c r="CL151" s="3"/>
-      <c r="CM151" s="3"/>
+      <c r="CJ151" s="7"/>
+      <c r="CK151" s="7"/>
+      <c r="CL151" s="7"/>
+      <c r="CM151" s="7"/>
       <c r="CN151" s="3"/>
       <c r="CO151" s="3"/>
       <c r="CP151" s="3"/>
@@ -31487,8 +32265,12 @@
       <c r="GW151" s="3"/>
       <c r="GX151" s="3"/>
       <c r="GY151" s="3"/>
+      <c r="GZ151" s="3"/>
+      <c r="HA151" s="3"/>
+      <c r="HB151" s="3"/>
+      <c r="HC151" s="3"/>
     </row>
-    <row r="152" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="152" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C152" s="7"/>
       <c r="D152" s="7"/>
       <c r="E152" s="7"/>
@@ -31574,10 +32356,10 @@
       <c r="CG152" s="7"/>
       <c r="CH152" s="7"/>
       <c r="CI152" s="7"/>
-      <c r="CJ152" s="3"/>
-      <c r="CK152" s="3"/>
-      <c r="CL152" s="3"/>
-      <c r="CM152" s="3"/>
+      <c r="CJ152" s="7"/>
+      <c r="CK152" s="7"/>
+      <c r="CL152" s="7"/>
+      <c r="CM152" s="7"/>
       <c r="CN152" s="3"/>
       <c r="CO152" s="3"/>
       <c r="CP152" s="3"/>
@@ -31694,8 +32476,12 @@
       <c r="GW152" s="3"/>
       <c r="GX152" s="3"/>
       <c r="GY152" s="3"/>
+      <c r="GZ152" s="3"/>
+      <c r="HA152" s="3"/>
+      <c r="HB152" s="3"/>
+      <c r="HC152" s="3"/>
     </row>
-    <row r="153" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="153" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C153" s="7"/>
       <c r="D153" s="7"/>
       <c r="E153" s="7"/>
@@ -31781,10 +32567,10 @@
       <c r="CG153" s="7"/>
       <c r="CH153" s="7"/>
       <c r="CI153" s="7"/>
-      <c r="CJ153" s="3"/>
-      <c r="CK153" s="3"/>
-      <c r="CL153" s="3"/>
-      <c r="CM153" s="3"/>
+      <c r="CJ153" s="7"/>
+      <c r="CK153" s="7"/>
+      <c r="CL153" s="7"/>
+      <c r="CM153" s="7"/>
       <c r="CN153" s="3"/>
       <c r="CO153" s="3"/>
       <c r="CP153" s="3"/>
@@ -31901,8 +32687,12 @@
       <c r="GW153" s="3"/>
       <c r="GX153" s="3"/>
       <c r="GY153" s="3"/>
+      <c r="GZ153" s="3"/>
+      <c r="HA153" s="3"/>
+      <c r="HB153" s="3"/>
+      <c r="HC153" s="3"/>
     </row>
-    <row r="154" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="154" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C154" s="7"/>
       <c r="D154" s="7"/>
       <c r="E154" s="7"/>
@@ -31988,10 +32778,10 @@
       <c r="CG154" s="7"/>
       <c r="CH154" s="7"/>
       <c r="CI154" s="7"/>
-      <c r="CJ154" s="3"/>
-      <c r="CK154" s="3"/>
-      <c r="CL154" s="3"/>
-      <c r="CM154" s="3"/>
+      <c r="CJ154" s="7"/>
+      <c r="CK154" s="7"/>
+      <c r="CL154" s="7"/>
+      <c r="CM154" s="7"/>
       <c r="CN154" s="3"/>
       <c r="CO154" s="3"/>
       <c r="CP154" s="3"/>
@@ -32108,8 +32898,12 @@
       <c r="GW154" s="3"/>
       <c r="GX154" s="3"/>
       <c r="GY154" s="3"/>
+      <c r="GZ154" s="3"/>
+      <c r="HA154" s="3"/>
+      <c r="HB154" s="3"/>
+      <c r="HC154" s="3"/>
     </row>
-    <row r="155" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="155" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C155" s="7"/>
       <c r="D155" s="7"/>
       <c r="E155" s="7"/>
@@ -32195,10 +32989,10 @@
       <c r="CG155" s="7"/>
       <c r="CH155" s="7"/>
       <c r="CI155" s="7"/>
-      <c r="CJ155" s="3"/>
-      <c r="CK155" s="3"/>
-      <c r="CL155" s="3"/>
-      <c r="CM155" s="3"/>
+      <c r="CJ155" s="7"/>
+      <c r="CK155" s="7"/>
+      <c r="CL155" s="7"/>
+      <c r="CM155" s="7"/>
       <c r="CN155" s="3"/>
       <c r="CO155" s="3"/>
       <c r="CP155" s="3"/>
@@ -32315,8 +33109,12 @@
       <c r="GW155" s="3"/>
       <c r="GX155" s="3"/>
       <c r="GY155" s="3"/>
+      <c r="GZ155" s="3"/>
+      <c r="HA155" s="3"/>
+      <c r="HB155" s="3"/>
+      <c r="HC155" s="3"/>
     </row>
-    <row r="156" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="156" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C156" s="7"/>
       <c r="D156" s="7"/>
       <c r="E156" s="7"/>
@@ -32402,10 +33200,10 @@
       <c r="CG156" s="7"/>
       <c r="CH156" s="7"/>
       <c r="CI156" s="7"/>
-      <c r="CJ156" s="3"/>
-      <c r="CK156" s="3"/>
-      <c r="CL156" s="3"/>
-      <c r="CM156" s="3"/>
+      <c r="CJ156" s="7"/>
+      <c r="CK156" s="7"/>
+      <c r="CL156" s="7"/>
+      <c r="CM156" s="7"/>
       <c r="CN156" s="3"/>
       <c r="CO156" s="3"/>
       <c r="CP156" s="3"/>
@@ -32522,8 +33320,12 @@
       <c r="GW156" s="3"/>
       <c r="GX156" s="3"/>
       <c r="GY156" s="3"/>
+      <c r="GZ156" s="3"/>
+      <c r="HA156" s="3"/>
+      <c r="HB156" s="3"/>
+      <c r="HC156" s="3"/>
     </row>
-    <row r="157" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="157" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
       <c r="E157" s="3"/>
@@ -32729,8 +33531,12 @@
       <c r="GW157" s="3"/>
       <c r="GX157" s="3"/>
       <c r="GY157" s="3"/>
+      <c r="GZ157" s="3"/>
+      <c r="HA157" s="3"/>
+      <c r="HB157" s="3"/>
+      <c r="HC157" s="3"/>
     </row>
-    <row r="158" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="158" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
       <c r="E158" s="3"/>
@@ -32936,8 +33742,12 @@
       <c r="GW158" s="3"/>
       <c r="GX158" s="3"/>
       <c r="GY158" s="3"/>
+      <c r="GZ158" s="3"/>
+      <c r="HA158" s="3"/>
+      <c r="HB158" s="3"/>
+      <c r="HC158" s="3"/>
     </row>
-    <row r="159" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="159" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
       <c r="E159" s="3"/>
@@ -33143,8 +33953,12 @@
       <c r="GW159" s="3"/>
       <c r="GX159" s="3"/>
       <c r="GY159" s="3"/>
+      <c r="GZ159" s="3"/>
+      <c r="HA159" s="3"/>
+      <c r="HB159" s="3"/>
+      <c r="HC159" s="3"/>
     </row>
-    <row r="160" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="160" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C160" s="3"/>
       <c r="D160" s="3"/>
       <c r="E160" s="3"/>
@@ -33350,8 +34164,12 @@
       <c r="GW160" s="3"/>
       <c r="GX160" s="3"/>
       <c r="GY160" s="3"/>
+      <c r="GZ160" s="3"/>
+      <c r="HA160" s="3"/>
+      <c r="HB160" s="3"/>
+      <c r="HC160" s="3"/>
     </row>
-    <row r="161" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="161" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C161" s="3"/>
       <c r="D161" s="3"/>
       <c r="E161" s="3"/>
@@ -33557,8 +34375,12 @@
       <c r="GW161" s="3"/>
       <c r="GX161" s="3"/>
       <c r="GY161" s="3"/>
+      <c r="GZ161" s="3"/>
+      <c r="HA161" s="3"/>
+      <c r="HB161" s="3"/>
+      <c r="HC161" s="3"/>
     </row>
-    <row r="162" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="162" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C162" s="3"/>
       <c r="D162" s="3"/>
       <c r="E162" s="3"/>
@@ -33764,8 +34586,12 @@
       <c r="GW162" s="3"/>
       <c r="GX162" s="3"/>
       <c r="GY162" s="3"/>
+      <c r="GZ162" s="3"/>
+      <c r="HA162" s="3"/>
+      <c r="HB162" s="3"/>
+      <c r="HC162" s="3"/>
     </row>
-    <row r="163" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="163" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C163" s="3"/>
       <c r="D163" s="3"/>
       <c r="E163" s="3"/>
@@ -33971,8 +34797,12 @@
       <c r="GW163" s="3"/>
       <c r="GX163" s="3"/>
       <c r="GY163" s="3"/>
+      <c r="GZ163" s="3"/>
+      <c r="HA163" s="3"/>
+      <c r="HB163" s="3"/>
+      <c r="HC163" s="3"/>
     </row>
-    <row r="164" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="164" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C164" s="3"/>
       <c r="D164" s="3"/>
       <c r="E164" s="3"/>
@@ -34178,8 +35008,12 @@
       <c r="GW164" s="3"/>
       <c r="GX164" s="3"/>
       <c r="GY164" s="3"/>
+      <c r="GZ164" s="3"/>
+      <c r="HA164" s="3"/>
+      <c r="HB164" s="3"/>
+      <c r="HC164" s="3"/>
     </row>
-    <row r="165" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="165" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C165" s="3"/>
       <c r="D165" s="3"/>
       <c r="E165" s="3"/>
@@ -34385,8 +35219,12 @@
       <c r="GW165" s="3"/>
       <c r="GX165" s="3"/>
       <c r="GY165" s="3"/>
+      <c r="GZ165" s="3"/>
+      <c r="HA165" s="3"/>
+      <c r="HB165" s="3"/>
+      <c r="HC165" s="3"/>
     </row>
-    <row r="166" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="166" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C166" s="3"/>
       <c r="D166" s="3"/>
       <c r="E166" s="3"/>
@@ -34592,8 +35430,12 @@
       <c r="GW166" s="3"/>
       <c r="GX166" s="3"/>
       <c r="GY166" s="3"/>
+      <c r="GZ166" s="3"/>
+      <c r="HA166" s="3"/>
+      <c r="HB166" s="3"/>
+      <c r="HC166" s="3"/>
     </row>
-    <row r="167" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="167" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C167" s="3"/>
       <c r="D167" s="3"/>
       <c r="E167" s="3"/>
@@ -34799,8 +35641,12 @@
       <c r="GW167" s="3"/>
       <c r="GX167" s="3"/>
       <c r="GY167" s="3"/>
+      <c r="GZ167" s="3"/>
+      <c r="HA167" s="3"/>
+      <c r="HB167" s="3"/>
+      <c r="HC167" s="3"/>
     </row>
-    <row r="168" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="168" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C168" s="3"/>
       <c r="D168" s="3"/>
       <c r="E168" s="3"/>
@@ -35006,8 +35852,12 @@
       <c r="GW168" s="3"/>
       <c r="GX168" s="3"/>
       <c r="GY168" s="3"/>
+      <c r="GZ168" s="3"/>
+      <c r="HA168" s="3"/>
+      <c r="HB168" s="3"/>
+      <c r="HC168" s="3"/>
     </row>
-    <row r="169" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="169" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C169" s="3"/>
       <c r="D169" s="3"/>
       <c r="E169" s="3"/>
@@ -35213,8 +36063,12 @@
       <c r="GW169" s="3"/>
       <c r="GX169" s="3"/>
       <c r="GY169" s="3"/>
+      <c r="GZ169" s="3"/>
+      <c r="HA169" s="3"/>
+      <c r="HB169" s="3"/>
+      <c r="HC169" s="3"/>
     </row>
-    <row r="170" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="170" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C170" s="3"/>
       <c r="D170" s="3"/>
       <c r="E170" s="3"/>
@@ -35420,8 +36274,12 @@
       <c r="GW170" s="3"/>
       <c r="GX170" s="3"/>
       <c r="GY170" s="3"/>
+      <c r="GZ170" s="3"/>
+      <c r="HA170" s="3"/>
+      <c r="HB170" s="3"/>
+      <c r="HC170" s="3"/>
     </row>
-    <row r="171" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="171" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C171" s="3"/>
       <c r="D171" s="3"/>
       <c r="E171" s="3"/>
@@ -35627,8 +36485,12 @@
       <c r="GW171" s="3"/>
       <c r="GX171" s="3"/>
       <c r="GY171" s="3"/>
+      <c r="GZ171" s="3"/>
+      <c r="HA171" s="3"/>
+      <c r="HB171" s="3"/>
+      <c r="HC171" s="3"/>
     </row>
-    <row r="172" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="172" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C172" s="3"/>
       <c r="D172" s="3"/>
       <c r="E172" s="3"/>
@@ -35834,8 +36696,12 @@
       <c r="GW172" s="3"/>
       <c r="GX172" s="3"/>
       <c r="GY172" s="3"/>
+      <c r="GZ172" s="3"/>
+      <c r="HA172" s="3"/>
+      <c r="HB172" s="3"/>
+      <c r="HC172" s="3"/>
     </row>
-    <row r="173" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="173" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C173" s="3"/>
       <c r="D173" s="3"/>
       <c r="E173" s="3"/>
@@ -36041,8 +36907,12 @@
       <c r="GW173" s="3"/>
       <c r="GX173" s="3"/>
       <c r="GY173" s="3"/>
+      <c r="GZ173" s="3"/>
+      <c r="HA173" s="3"/>
+      <c r="HB173" s="3"/>
+      <c r="HC173" s="3"/>
     </row>
-    <row r="174" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="174" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C174" s="3"/>
       <c r="D174" s="3"/>
       <c r="E174" s="3"/>
@@ -36248,8 +37118,12 @@
       <c r="GW174" s="3"/>
       <c r="GX174" s="3"/>
       <c r="GY174" s="3"/>
+      <c r="GZ174" s="3"/>
+      <c r="HA174" s="3"/>
+      <c r="HB174" s="3"/>
+      <c r="HC174" s="3"/>
     </row>
-    <row r="175" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="175" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C175" s="3"/>
       <c r="D175" s="3"/>
       <c r="E175" s="3"/>
@@ -36455,8 +37329,12 @@
       <c r="GW175" s="3"/>
       <c r="GX175" s="3"/>
       <c r="GY175" s="3"/>
+      <c r="GZ175" s="3"/>
+      <c r="HA175" s="3"/>
+      <c r="HB175" s="3"/>
+      <c r="HC175" s="3"/>
     </row>
-    <row r="176" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="176" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C176" s="3"/>
       <c r="D176" s="3"/>
       <c r="E176" s="3"/>
@@ -36662,8 +37540,12 @@
       <c r="GW176" s="3"/>
       <c r="GX176" s="3"/>
       <c r="GY176" s="3"/>
+      <c r="GZ176" s="3"/>
+      <c r="HA176" s="3"/>
+      <c r="HB176" s="3"/>
+      <c r="HC176" s="3"/>
     </row>
-    <row r="177" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="177" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C177" s="3"/>
       <c r="D177" s="3"/>
       <c r="E177" s="3"/>
@@ -36869,8 +37751,12 @@
       <c r="GW177" s="3"/>
       <c r="GX177" s="3"/>
       <c r="GY177" s="3"/>
+      <c r="GZ177" s="3"/>
+      <c r="HA177" s="3"/>
+      <c r="HB177" s="3"/>
+      <c r="HC177" s="3"/>
     </row>
-    <row r="178" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="178" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C178" s="3"/>
       <c r="D178" s="3"/>
       <c r="E178" s="3"/>
@@ -37076,8 +37962,12 @@
       <c r="GW178" s="3"/>
       <c r="GX178" s="3"/>
       <c r="GY178" s="3"/>
+      <c r="GZ178" s="3"/>
+      <c r="HA178" s="3"/>
+      <c r="HB178" s="3"/>
+      <c r="HC178" s="3"/>
     </row>
-    <row r="179" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="179" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C179" s="3"/>
       <c r="D179" s="3"/>
       <c r="E179" s="3"/>
@@ -37283,8 +38173,12 @@
       <c r="GW179" s="3"/>
       <c r="GX179" s="3"/>
       <c r="GY179" s="3"/>
+      <c r="GZ179" s="3"/>
+      <c r="HA179" s="3"/>
+      <c r="HB179" s="3"/>
+      <c r="HC179" s="3"/>
     </row>
-    <row r="180" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="180" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C180" s="3"/>
       <c r="D180" s="3"/>
       <c r="E180" s="3"/>
@@ -37490,8 +38384,12 @@
       <c r="GW180" s="3"/>
       <c r="GX180" s="3"/>
       <c r="GY180" s="3"/>
+      <c r="GZ180" s="3"/>
+      <c r="HA180" s="3"/>
+      <c r="HB180" s="3"/>
+      <c r="HC180" s="3"/>
     </row>
-    <row r="181" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="181" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C181" s="3"/>
       <c r="D181" s="3"/>
       <c r="E181" s="3"/>
@@ -37697,8 +38595,12 @@
       <c r="GW181" s="3"/>
       <c r="GX181" s="3"/>
       <c r="GY181" s="3"/>
+      <c r="GZ181" s="3"/>
+      <c r="HA181" s="3"/>
+      <c r="HB181" s="3"/>
+      <c r="HC181" s="3"/>
     </row>
-    <row r="182" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="182" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C182" s="3"/>
       <c r="D182" s="3"/>
       <c r="E182" s="3"/>
@@ -37904,8 +38806,12 @@
       <c r="GW182" s="3"/>
       <c r="GX182" s="3"/>
       <c r="GY182" s="3"/>
+      <c r="GZ182" s="3"/>
+      <c r="HA182" s="3"/>
+      <c r="HB182" s="3"/>
+      <c r="HC182" s="3"/>
     </row>
-    <row r="183" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="183" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C183" s="3"/>
       <c r="D183" s="3"/>
       <c r="E183" s="3"/>
@@ -38111,8 +39017,12 @@
       <c r="GW183" s="3"/>
       <c r="GX183" s="3"/>
       <c r="GY183" s="3"/>
+      <c r="GZ183" s="3"/>
+      <c r="HA183" s="3"/>
+      <c r="HB183" s="3"/>
+      <c r="HC183" s="3"/>
     </row>
-    <row r="184" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="184" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C184" s="3"/>
       <c r="D184" s="3"/>
       <c r="E184" s="3"/>
@@ -38318,8 +39228,12 @@
       <c r="GW184" s="3"/>
       <c r="GX184" s="3"/>
       <c r="GY184" s="3"/>
+      <c r="GZ184" s="3"/>
+      <c r="HA184" s="3"/>
+      <c r="HB184" s="3"/>
+      <c r="HC184" s="3"/>
     </row>
-    <row r="185" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="185" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C185" s="3"/>
       <c r="D185" s="3"/>
       <c r="E185" s="3"/>
@@ -38525,8 +39439,12 @@
       <c r="GW185" s="3"/>
       <c r="GX185" s="3"/>
       <c r="GY185" s="3"/>
+      <c r="GZ185" s="3"/>
+      <c r="HA185" s="3"/>
+      <c r="HB185" s="3"/>
+      <c r="HC185" s="3"/>
     </row>
-    <row r="186" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="186" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C186" s="3"/>
       <c r="D186" s="3"/>
       <c r="E186" s="3"/>
@@ -38732,8 +39650,12 @@
       <c r="GW186" s="3"/>
       <c r="GX186" s="3"/>
       <c r="GY186" s="3"/>
+      <c r="GZ186" s="3"/>
+      <c r="HA186" s="3"/>
+      <c r="HB186" s="3"/>
+      <c r="HC186" s="3"/>
     </row>
-    <row r="187" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="187" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C187" s="3"/>
       <c r="D187" s="3"/>
       <c r="E187" s="3"/>
@@ -38939,8 +39861,12 @@
       <c r="GW187" s="3"/>
       <c r="GX187" s="3"/>
       <c r="GY187" s="3"/>
+      <c r="GZ187" s="3"/>
+      <c r="HA187" s="3"/>
+      <c r="HB187" s="3"/>
+      <c r="HC187" s="3"/>
     </row>
-    <row r="188" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="188" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C188" s="3"/>
       <c r="D188" s="3"/>
       <c r="E188" s="3"/>
@@ -39146,8 +40072,12 @@
       <c r="GW188" s="3"/>
       <c r="GX188" s="3"/>
       <c r="GY188" s="3"/>
+      <c r="GZ188" s="3"/>
+      <c r="HA188" s="3"/>
+      <c r="HB188" s="3"/>
+      <c r="HC188" s="3"/>
     </row>
-    <row r="189" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="189" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C189" s="3"/>
       <c r="D189" s="3"/>
       <c r="E189" s="3"/>
@@ -39353,8 +40283,12 @@
       <c r="GW189" s="3"/>
       <c r="GX189" s="3"/>
       <c r="GY189" s="3"/>
+      <c r="GZ189" s="3"/>
+      <c r="HA189" s="3"/>
+      <c r="HB189" s="3"/>
+      <c r="HC189" s="3"/>
     </row>
-    <row r="190" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="190" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C190" s="3"/>
       <c r="D190" s="3"/>
       <c r="E190" s="3"/>
@@ -39560,8 +40494,12 @@
       <c r="GW190" s="3"/>
       <c r="GX190" s="3"/>
       <c r="GY190" s="3"/>
+      <c r="GZ190" s="3"/>
+      <c r="HA190" s="3"/>
+      <c r="HB190" s="3"/>
+      <c r="HC190" s="3"/>
     </row>
-    <row r="191" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="191" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C191" s="3"/>
       <c r="D191" s="3"/>
       <c r="E191" s="3"/>
@@ -39767,8 +40705,12 @@
       <c r="GW191" s="3"/>
       <c r="GX191" s="3"/>
       <c r="GY191" s="3"/>
+      <c r="GZ191" s="3"/>
+      <c r="HA191" s="3"/>
+      <c r="HB191" s="3"/>
+      <c r="HC191" s="3"/>
     </row>
-    <row r="192" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="192" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C192" s="3"/>
       <c r="D192" s="3"/>
       <c r="E192" s="3"/>
@@ -39974,8 +40916,12 @@
       <c r="GW192" s="3"/>
       <c r="GX192" s="3"/>
       <c r="GY192" s="3"/>
+      <c r="GZ192" s="3"/>
+      <c r="HA192" s="3"/>
+      <c r="HB192" s="3"/>
+      <c r="HC192" s="3"/>
     </row>
-    <row r="193" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="193" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C193" s="3"/>
       <c r="D193" s="3"/>
       <c r="E193" s="3"/>
@@ -40181,8 +41127,12 @@
       <c r="GW193" s="3"/>
       <c r="GX193" s="3"/>
       <c r="GY193" s="3"/>
+      <c r="GZ193" s="3"/>
+      <c r="HA193" s="3"/>
+      <c r="HB193" s="3"/>
+      <c r="HC193" s="3"/>
     </row>
-    <row r="194" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="194" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C194" s="3"/>
       <c r="D194" s="3"/>
       <c r="E194" s="3"/>
@@ -40388,8 +41338,12 @@
       <c r="GW194" s="3"/>
       <c r="GX194" s="3"/>
       <c r="GY194" s="3"/>
+      <c r="GZ194" s="3"/>
+      <c r="HA194" s="3"/>
+      <c r="HB194" s="3"/>
+      <c r="HC194" s="3"/>
     </row>
-    <row r="195" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="195" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C195" s="3"/>
       <c r="D195" s="3"/>
       <c r="E195" s="3"/>
@@ -40595,8 +41549,12 @@
       <c r="GW195" s="3"/>
       <c r="GX195" s="3"/>
       <c r="GY195" s="3"/>
+      <c r="GZ195" s="3"/>
+      <c r="HA195" s="3"/>
+      <c r="HB195" s="3"/>
+      <c r="HC195" s="3"/>
     </row>
-    <row r="196" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="196" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C196" s="3"/>
       <c r="D196" s="3"/>
       <c r="E196" s="3"/>
@@ -40802,8 +41760,12 @@
       <c r="GW196" s="3"/>
       <c r="GX196" s="3"/>
       <c r="GY196" s="3"/>
+      <c r="GZ196" s="3"/>
+      <c r="HA196" s="3"/>
+      <c r="HB196" s="3"/>
+      <c r="HC196" s="3"/>
     </row>
-    <row r="197" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="197" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C197" s="3"/>
       <c r="D197" s="3"/>
       <c r="E197" s="3"/>
@@ -41009,8 +41971,12 @@
       <c r="GW197" s="3"/>
       <c r="GX197" s="3"/>
       <c r="GY197" s="3"/>
+      <c r="GZ197" s="3"/>
+      <c r="HA197" s="3"/>
+      <c r="HB197" s="3"/>
+      <c r="HC197" s="3"/>
     </row>
-    <row r="198" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="198" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C198" s="3"/>
       <c r="D198" s="3"/>
       <c r="E198" s="3"/>
@@ -41216,8 +42182,12 @@
       <c r="GW198" s="3"/>
       <c r="GX198" s="3"/>
       <c r="GY198" s="3"/>
+      <c r="GZ198" s="3"/>
+      <c r="HA198" s="3"/>
+      <c r="HB198" s="3"/>
+      <c r="HC198" s="3"/>
     </row>
-    <row r="199" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="199" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C199" s="3"/>
       <c r="D199" s="3"/>
       <c r="E199" s="3"/>
@@ -41423,8 +42393,12 @@
       <c r="GW199" s="3"/>
       <c r="GX199" s="3"/>
       <c r="GY199" s="3"/>
+      <c r="GZ199" s="3"/>
+      <c r="HA199" s="3"/>
+      <c r="HB199" s="3"/>
+      <c r="HC199" s="3"/>
     </row>
-    <row r="200" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="200" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C200" s="3"/>
       <c r="D200" s="3"/>
       <c r="E200" s="3"/>
@@ -41630,8 +42604,12 @@
       <c r="GW200" s="3"/>
       <c r="GX200" s="3"/>
       <c r="GY200" s="3"/>
+      <c r="GZ200" s="3"/>
+      <c r="HA200" s="3"/>
+      <c r="HB200" s="3"/>
+      <c r="HC200" s="3"/>
     </row>
-    <row r="201" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="201" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C201" s="3"/>
       <c r="D201" s="3"/>
       <c r="E201" s="3"/>
@@ -41837,8 +42815,12 @@
       <c r="GW201" s="3"/>
       <c r="GX201" s="3"/>
       <c r="GY201" s="3"/>
+      <c r="GZ201" s="3"/>
+      <c r="HA201" s="3"/>
+      <c r="HB201" s="3"/>
+      <c r="HC201" s="3"/>
     </row>
-    <row r="202" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="202" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C202" s="3"/>
       <c r="D202" s="3"/>
       <c r="E202" s="3"/>
@@ -42044,8 +43026,12 @@
       <c r="GW202" s="3"/>
       <c r="GX202" s="3"/>
       <c r="GY202" s="3"/>
+      <c r="GZ202" s="3"/>
+      <c r="HA202" s="3"/>
+      <c r="HB202" s="3"/>
+      <c r="HC202" s="3"/>
     </row>
-    <row r="203" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="203" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C203" s="3"/>
       <c r="D203" s="3"/>
       <c r="E203" s="3"/>
@@ -42251,8 +43237,12 @@
       <c r="GW203" s="3"/>
       <c r="GX203" s="3"/>
       <c r="GY203" s="3"/>
+      <c r="GZ203" s="3"/>
+      <c r="HA203" s="3"/>
+      <c r="HB203" s="3"/>
+      <c r="HC203" s="3"/>
     </row>
-    <row r="204" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="204" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C204" s="3"/>
       <c r="D204" s="3"/>
       <c r="E204" s="3"/>
@@ -42458,8 +43448,12 @@
       <c r="GW204" s="3"/>
       <c r="GX204" s="3"/>
       <c r="GY204" s="3"/>
+      <c r="GZ204" s="3"/>
+      <c r="HA204" s="3"/>
+      <c r="HB204" s="3"/>
+      <c r="HC204" s="3"/>
     </row>
-    <row r="205" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="205" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C205" s="3"/>
       <c r="D205" s="3"/>
       <c r="E205" s="3"/>
@@ -42665,8 +43659,12 @@
       <c r="GW205" s="3"/>
       <c r="GX205" s="3"/>
       <c r="GY205" s="3"/>
+      <c r="GZ205" s="3"/>
+      <c r="HA205" s="3"/>
+      <c r="HB205" s="3"/>
+      <c r="HC205" s="3"/>
     </row>
-    <row r="206" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="206" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C206" s="3"/>
       <c r="D206" s="3"/>
       <c r="E206" s="3"/>
@@ -42872,8 +43870,12 @@
       <c r="GW206" s="3"/>
       <c r="GX206" s="3"/>
       <c r="GY206" s="3"/>
+      <c r="GZ206" s="3"/>
+      <c r="HA206" s="3"/>
+      <c r="HB206" s="3"/>
+      <c r="HC206" s="3"/>
     </row>
-    <row r="207" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="207" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C207" s="3"/>
       <c r="D207" s="3"/>
       <c r="E207" s="3"/>
@@ -43079,8 +44081,12 @@
       <c r="GW207" s="3"/>
       <c r="GX207" s="3"/>
       <c r="GY207" s="3"/>
+      <c r="GZ207" s="3"/>
+      <c r="HA207" s="3"/>
+      <c r="HB207" s="3"/>
+      <c r="HC207" s="3"/>
     </row>
-    <row r="208" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="208" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C208" s="3"/>
       <c r="D208" s="3"/>
       <c r="E208" s="3"/>
@@ -43286,8 +44292,12 @@
       <c r="GW208" s="3"/>
       <c r="GX208" s="3"/>
       <c r="GY208" s="3"/>
+      <c r="GZ208" s="3"/>
+      <c r="HA208" s="3"/>
+      <c r="HB208" s="3"/>
+      <c r="HC208" s="3"/>
     </row>
-    <row r="209" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="209" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C209" s="3"/>
       <c r="D209" s="3"/>
       <c r="E209" s="3"/>
@@ -43493,8 +44503,12 @@
       <c r="GW209" s="3"/>
       <c r="GX209" s="3"/>
       <c r="GY209" s="3"/>
+      <c r="GZ209" s="3"/>
+      <c r="HA209" s="3"/>
+      <c r="HB209" s="3"/>
+      <c r="HC209" s="3"/>
     </row>
-    <row r="210" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="210" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C210" s="3"/>
       <c r="D210" s="3"/>
       <c r="E210" s="3"/>
@@ -43700,8 +44714,12 @@
       <c r="GW210" s="3"/>
       <c r="GX210" s="3"/>
       <c r="GY210" s="3"/>
+      <c r="GZ210" s="3"/>
+      <c r="HA210" s="3"/>
+      <c r="HB210" s="3"/>
+      <c r="HC210" s="3"/>
     </row>
-    <row r="211" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="211" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C211" s="3"/>
       <c r="D211" s="3"/>
       <c r="E211" s="3"/>
@@ -43907,8 +44925,12 @@
       <c r="GW211" s="3"/>
       <c r="GX211" s="3"/>
       <c r="GY211" s="3"/>
+      <c r="GZ211" s="3"/>
+      <c r="HA211" s="3"/>
+      <c r="HB211" s="3"/>
+      <c r="HC211" s="3"/>
     </row>
-    <row r="212" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="212" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C212" s="3"/>
       <c r="D212" s="3"/>
       <c r="E212" s="3"/>
@@ -44114,8 +45136,12 @@
       <c r="GW212" s="3"/>
       <c r="GX212" s="3"/>
       <c r="GY212" s="3"/>
+      <c r="GZ212" s="3"/>
+      <c r="HA212" s="3"/>
+      <c r="HB212" s="3"/>
+      <c r="HC212" s="3"/>
     </row>
-    <row r="213" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="213" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C213" s="3"/>
       <c r="D213" s="3"/>
       <c r="E213" s="3"/>
@@ -44321,8 +45347,12 @@
       <c r="GW213" s="3"/>
       <c r="GX213" s="3"/>
       <c r="GY213" s="3"/>
+      <c r="GZ213" s="3"/>
+      <c r="HA213" s="3"/>
+      <c r="HB213" s="3"/>
+      <c r="HC213" s="3"/>
     </row>
-    <row r="214" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="214" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C214" s="3"/>
       <c r="D214" s="3"/>
       <c r="E214" s="3"/>
@@ -44528,8 +45558,12 @@
       <c r="GW214" s="3"/>
       <c r="GX214" s="3"/>
       <c r="GY214" s="3"/>
+      <c r="GZ214" s="3"/>
+      <c r="HA214" s="3"/>
+      <c r="HB214" s="3"/>
+      <c r="HC214" s="3"/>
     </row>
-    <row r="215" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="215" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C215" s="3"/>
       <c r="D215" s="3"/>
       <c r="E215" s="3"/>
@@ -44735,8 +45769,12 @@
       <c r="GW215" s="3"/>
       <c r="GX215" s="3"/>
       <c r="GY215" s="3"/>
+      <c r="GZ215" s="3"/>
+      <c r="HA215" s="3"/>
+      <c r="HB215" s="3"/>
+      <c r="HC215" s="3"/>
     </row>
-    <row r="216" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="216" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C216" s="3"/>
       <c r="D216" s="3"/>
       <c r="E216" s="3"/>
@@ -44942,8 +45980,12 @@
       <c r="GW216" s="3"/>
       <c r="GX216" s="3"/>
       <c r="GY216" s="3"/>
+      <c r="GZ216" s="3"/>
+      <c r="HA216" s="3"/>
+      <c r="HB216" s="3"/>
+      <c r="HC216" s="3"/>
     </row>
-    <row r="217" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="217" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C217" s="3"/>
       <c r="D217" s="3"/>
       <c r="E217" s="3"/>
@@ -45149,8 +46191,12 @@
       <c r="GW217" s="3"/>
       <c r="GX217" s="3"/>
       <c r="GY217" s="3"/>
+      <c r="GZ217" s="3"/>
+      <c r="HA217" s="3"/>
+      <c r="HB217" s="3"/>
+      <c r="HC217" s="3"/>
     </row>
-    <row r="218" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="218" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C218" s="3"/>
       <c r="D218" s="3"/>
       <c r="E218" s="3"/>
@@ -45356,8 +46402,12 @@
       <c r="GW218" s="3"/>
       <c r="GX218" s="3"/>
       <c r="GY218" s="3"/>
+      <c r="GZ218" s="3"/>
+      <c r="HA218" s="3"/>
+      <c r="HB218" s="3"/>
+      <c r="HC218" s="3"/>
     </row>
-    <row r="219" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="219" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C219" s="3"/>
       <c r="D219" s="3"/>
       <c r="E219" s="3"/>
@@ -45563,8 +46613,12 @@
       <c r="GW219" s="3"/>
       <c r="GX219" s="3"/>
       <c r="GY219" s="3"/>
+      <c r="GZ219" s="3"/>
+      <c r="HA219" s="3"/>
+      <c r="HB219" s="3"/>
+      <c r="HC219" s="3"/>
     </row>
-    <row r="220" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="220" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C220" s="3"/>
       <c r="D220" s="3"/>
       <c r="E220" s="3"/>
@@ -45770,8 +46824,12 @@
       <c r="GW220" s="3"/>
       <c r="GX220" s="3"/>
       <c r="GY220" s="3"/>
+      <c r="GZ220" s="3"/>
+      <c r="HA220" s="3"/>
+      <c r="HB220" s="3"/>
+      <c r="HC220" s="3"/>
     </row>
-    <row r="221" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="221" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C221" s="3"/>
       <c r="D221" s="3"/>
       <c r="E221" s="3"/>
@@ -45977,8 +47035,12 @@
       <c r="GW221" s="3"/>
       <c r="GX221" s="3"/>
       <c r="GY221" s="3"/>
+      <c r="GZ221" s="3"/>
+      <c r="HA221" s="3"/>
+      <c r="HB221" s="3"/>
+      <c r="HC221" s="3"/>
     </row>
-    <row r="222" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="222" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C222" s="3"/>
       <c r="D222" s="3"/>
       <c r="E222" s="3"/>
@@ -46184,8 +47246,12 @@
       <c r="GW222" s="3"/>
       <c r="GX222" s="3"/>
       <c r="GY222" s="3"/>
+      <c r="GZ222" s="3"/>
+      <c r="HA222" s="3"/>
+      <c r="HB222" s="3"/>
+      <c r="HC222" s="3"/>
     </row>
-    <row r="223" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="223" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C223" s="3"/>
       <c r="D223" s="3"/>
       <c r="E223" s="3"/>
@@ -46391,8 +47457,12 @@
       <c r="GW223" s="3"/>
       <c r="GX223" s="3"/>
       <c r="GY223" s="3"/>
+      <c r="GZ223" s="3"/>
+      <c r="HA223" s="3"/>
+      <c r="HB223" s="3"/>
+      <c r="HC223" s="3"/>
     </row>
-    <row r="224" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="224" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C224" s="3"/>
       <c r="D224" s="3"/>
       <c r="E224" s="3"/>
@@ -46598,8 +47668,12 @@
       <c r="GW224" s="3"/>
       <c r="GX224" s="3"/>
       <c r="GY224" s="3"/>
+      <c r="GZ224" s="3"/>
+      <c r="HA224" s="3"/>
+      <c r="HB224" s="3"/>
+      <c r="HC224" s="3"/>
     </row>
-    <row r="225" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="225" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C225" s="3"/>
       <c r="D225" s="3"/>
       <c r="E225" s="3"/>
@@ -46805,8 +47879,12 @@
       <c r="GW225" s="3"/>
       <c r="GX225" s="3"/>
       <c r="GY225" s="3"/>
+      <c r="GZ225" s="3"/>
+      <c r="HA225" s="3"/>
+      <c r="HB225" s="3"/>
+      <c r="HC225" s="3"/>
     </row>
-    <row r="226" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="226" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C226" s="3"/>
       <c r="D226" s="3"/>
       <c r="E226" s="3"/>
@@ -47012,8 +48090,12 @@
       <c r="GW226" s="3"/>
       <c r="GX226" s="3"/>
       <c r="GY226" s="3"/>
+      <c r="GZ226" s="3"/>
+      <c r="HA226" s="3"/>
+      <c r="HB226" s="3"/>
+      <c r="HC226" s="3"/>
     </row>
-    <row r="227" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="227" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C227" s="3"/>
       <c r="D227" s="3"/>
       <c r="E227" s="3"/>
@@ -47219,8 +48301,12 @@
       <c r="GW227" s="3"/>
       <c r="GX227" s="3"/>
       <c r="GY227" s="3"/>
+      <c r="GZ227" s="3"/>
+      <c r="HA227" s="3"/>
+      <c r="HB227" s="3"/>
+      <c r="HC227" s="3"/>
     </row>
-    <row r="228" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="228" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C228" s="3"/>
       <c r="D228" s="3"/>
       <c r="E228" s="3"/>
@@ -47426,8 +48512,12 @@
       <c r="GW228" s="3"/>
       <c r="GX228" s="3"/>
       <c r="GY228" s="3"/>
+      <c r="GZ228" s="3"/>
+      <c r="HA228" s="3"/>
+      <c r="HB228" s="3"/>
+      <c r="HC228" s="3"/>
     </row>
-    <row r="229" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="229" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C229" s="3"/>
       <c r="D229" s="3"/>
       <c r="E229" s="3"/>
@@ -47633,8 +48723,12 @@
       <c r="GW229" s="3"/>
       <c r="GX229" s="3"/>
       <c r="GY229" s="3"/>
+      <c r="GZ229" s="3"/>
+      <c r="HA229" s="3"/>
+      <c r="HB229" s="3"/>
+      <c r="HC229" s="3"/>
     </row>
-    <row r="230" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="230" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C230" s="3"/>
       <c r="D230" s="3"/>
       <c r="E230" s="3"/>
@@ -47840,8 +48934,12 @@
       <c r="GW230" s="3"/>
       <c r="GX230" s="3"/>
       <c r="GY230" s="3"/>
+      <c r="GZ230" s="3"/>
+      <c r="HA230" s="3"/>
+      <c r="HB230" s="3"/>
+      <c r="HC230" s="3"/>
     </row>
-    <row r="231" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="231" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C231" s="3"/>
       <c r="D231" s="3"/>
       <c r="E231" s="3"/>
@@ -48047,8 +49145,12 @@
       <c r="GW231" s="3"/>
       <c r="GX231" s="3"/>
       <c r="GY231" s="3"/>
+      <c r="GZ231" s="3"/>
+      <c r="HA231" s="3"/>
+      <c r="HB231" s="3"/>
+      <c r="HC231" s="3"/>
     </row>
-    <row r="232" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="232" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C232" s="3"/>
       <c r="D232" s="3"/>
       <c r="E232" s="3"/>
@@ -48254,8 +49356,12 @@
       <c r="GW232" s="3"/>
       <c r="GX232" s="3"/>
       <c r="GY232" s="3"/>
+      <c r="GZ232" s="3"/>
+      <c r="HA232" s="3"/>
+      <c r="HB232" s="3"/>
+      <c r="HC232" s="3"/>
     </row>
-    <row r="233" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="233" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C233" s="3"/>
       <c r="D233" s="3"/>
       <c r="E233" s="3"/>
@@ -48461,8 +49567,12 @@
       <c r="GW233" s="3"/>
       <c r="GX233" s="3"/>
       <c r="GY233" s="3"/>
+      <c r="GZ233" s="3"/>
+      <c r="HA233" s="3"/>
+      <c r="HB233" s="3"/>
+      <c r="HC233" s="3"/>
     </row>
-    <row r="234" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="234" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C234" s="3"/>
       <c r="D234" s="3"/>
       <c r="E234" s="3"/>
@@ -48668,8 +49778,12 @@
       <c r="GW234" s="3"/>
       <c r="GX234" s="3"/>
       <c r="GY234" s="3"/>
+      <c r="GZ234" s="3"/>
+      <c r="HA234" s="3"/>
+      <c r="HB234" s="3"/>
+      <c r="HC234" s="3"/>
     </row>
-    <row r="235" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="235" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C235" s="3"/>
       <c r="D235" s="3"/>
       <c r="E235" s="3"/>
@@ -48875,8 +49989,12 @@
       <c r="GW235" s="3"/>
       <c r="GX235" s="3"/>
       <c r="GY235" s="3"/>
+      <c r="GZ235" s="3"/>
+      <c r="HA235" s="3"/>
+      <c r="HB235" s="3"/>
+      <c r="HC235" s="3"/>
     </row>
-    <row r="236" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="236" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C236" s="3"/>
       <c r="D236" s="3"/>
       <c r="E236" s="3"/>
@@ -49082,8 +50200,12 @@
       <c r="GW236" s="3"/>
       <c r="GX236" s="3"/>
       <c r="GY236" s="3"/>
+      <c r="GZ236" s="3"/>
+      <c r="HA236" s="3"/>
+      <c r="HB236" s="3"/>
+      <c r="HC236" s="3"/>
     </row>
-    <row r="237" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="237" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C237" s="3"/>
       <c r="D237" s="3"/>
       <c r="E237" s="3"/>
@@ -49289,8 +50411,12 @@
       <c r="GW237" s="3"/>
       <c r="GX237" s="3"/>
       <c r="GY237" s="3"/>
+      <c r="GZ237" s="3"/>
+      <c r="HA237" s="3"/>
+      <c r="HB237" s="3"/>
+      <c r="HC237" s="3"/>
     </row>
-    <row r="238" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="238" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C238" s="3"/>
       <c r="D238" s="3"/>
       <c r="E238" s="3"/>
@@ -49496,8 +50622,12 @@
       <c r="GW238" s="3"/>
       <c r="GX238" s="3"/>
       <c r="GY238" s="3"/>
+      <c r="GZ238" s="3"/>
+      <c r="HA238" s="3"/>
+      <c r="HB238" s="3"/>
+      <c r="HC238" s="3"/>
     </row>
-    <row r="239" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="239" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C239" s="3"/>
       <c r="D239" s="3"/>
       <c r="E239" s="3"/>
@@ -49703,8 +50833,12 @@
       <c r="GW239" s="3"/>
       <c r="GX239" s="3"/>
       <c r="GY239" s="3"/>
+      <c r="GZ239" s="3"/>
+      <c r="HA239" s="3"/>
+      <c r="HB239" s="3"/>
+      <c r="HC239" s="3"/>
     </row>
-    <row r="240" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="240" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C240" s="3"/>
       <c r="D240" s="3"/>
       <c r="E240" s="3"/>
@@ -49910,8 +51044,12 @@
       <c r="GW240" s="3"/>
       <c r="GX240" s="3"/>
       <c r="GY240" s="3"/>
+      <c r="GZ240" s="3"/>
+      <c r="HA240" s="3"/>
+      <c r="HB240" s="3"/>
+      <c r="HC240" s="3"/>
     </row>
-    <row r="241" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="241" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C241" s="3"/>
       <c r="D241" s="3"/>
       <c r="E241" s="3"/>
@@ -50117,8 +51255,12 @@
       <c r="GW241" s="3"/>
       <c r="GX241" s="3"/>
       <c r="GY241" s="3"/>
+      <c r="GZ241" s="3"/>
+      <c r="HA241" s="3"/>
+      <c r="HB241" s="3"/>
+      <c r="HC241" s="3"/>
     </row>
-    <row r="242" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="242" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C242" s="3"/>
       <c r="D242" s="3"/>
       <c r="E242" s="3"/>
@@ -50324,8 +51466,12 @@
       <c r="GW242" s="3"/>
       <c r="GX242" s="3"/>
       <c r="GY242" s="3"/>
+      <c r="GZ242" s="3"/>
+      <c r="HA242" s="3"/>
+      <c r="HB242" s="3"/>
+      <c r="HC242" s="3"/>
     </row>
-    <row r="243" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="243" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C243" s="3"/>
       <c r="D243" s="3"/>
       <c r="E243" s="3"/>
@@ -50531,8 +51677,12 @@
       <c r="GW243" s="3"/>
       <c r="GX243" s="3"/>
       <c r="GY243" s="3"/>
+      <c r="GZ243" s="3"/>
+      <c r="HA243" s="3"/>
+      <c r="HB243" s="3"/>
+      <c r="HC243" s="3"/>
     </row>
-    <row r="244" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="244" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C244" s="3"/>
       <c r="D244" s="3"/>
       <c r="E244" s="3"/>
@@ -50738,8 +51888,12 @@
       <c r="GW244" s="3"/>
       <c r="GX244" s="3"/>
       <c r="GY244" s="3"/>
+      <c r="GZ244" s="3"/>
+      <c r="HA244" s="3"/>
+      <c r="HB244" s="3"/>
+      <c r="HC244" s="3"/>
     </row>
-    <row r="245" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="245" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C245" s="3"/>
       <c r="D245" s="3"/>
       <c r="E245" s="3"/>
@@ -50945,8 +52099,12 @@
       <c r="GW245" s="3"/>
       <c r="GX245" s="3"/>
       <c r="GY245" s="3"/>
+      <c r="GZ245" s="3"/>
+      <c r="HA245" s="3"/>
+      <c r="HB245" s="3"/>
+      <c r="HC245" s="3"/>
     </row>
-    <row r="246" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="246" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C246" s="3"/>
       <c r="D246" s="3"/>
       <c r="E246" s="3"/>
@@ -51152,8 +52310,12 @@
       <c r="GW246" s="3"/>
       <c r="GX246" s="3"/>
       <c r="GY246" s="3"/>
+      <c r="GZ246" s="3"/>
+      <c r="HA246" s="3"/>
+      <c r="HB246" s="3"/>
+      <c r="HC246" s="3"/>
     </row>
-    <row r="247" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="247" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C247" s="3"/>
       <c r="D247" s="3"/>
       <c r="E247" s="3"/>
@@ -51359,8 +52521,12 @@
       <c r="GW247" s="3"/>
       <c r="GX247" s="3"/>
       <c r="GY247" s="3"/>
+      <c r="GZ247" s="3"/>
+      <c r="HA247" s="3"/>
+      <c r="HB247" s="3"/>
+      <c r="HC247" s="3"/>
     </row>
-    <row r="248" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="248" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C248" s="3"/>
       <c r="D248" s="3"/>
       <c r="E248" s="3"/>
@@ -51566,8 +52732,12 @@
       <c r="GW248" s="3"/>
       <c r="GX248" s="3"/>
       <c r="GY248" s="3"/>
+      <c r="GZ248" s="3"/>
+      <c r="HA248" s="3"/>
+      <c r="HB248" s="3"/>
+      <c r="HC248" s="3"/>
     </row>
-    <row r="249" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="249" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C249" s="3"/>
       <c r="D249" s="3"/>
       <c r="E249" s="3"/>
@@ -51773,8 +52943,12 @@
       <c r="GW249" s="3"/>
       <c r="GX249" s="3"/>
       <c r="GY249" s="3"/>
+      <c r="GZ249" s="3"/>
+      <c r="HA249" s="3"/>
+      <c r="HB249" s="3"/>
+      <c r="HC249" s="3"/>
     </row>
-    <row r="250" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="250" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C250" s="3"/>
       <c r="D250" s="3"/>
       <c r="E250" s="3"/>
@@ -51980,8 +53154,12 @@
       <c r="GW250" s="3"/>
       <c r="GX250" s="3"/>
       <c r="GY250" s="3"/>
+      <c r="GZ250" s="3"/>
+      <c r="HA250" s="3"/>
+      <c r="HB250" s="3"/>
+      <c r="HC250" s="3"/>
     </row>
-    <row r="251" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="251" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C251" s="3"/>
       <c r="D251" s="3"/>
       <c r="E251" s="3"/>
@@ -52187,8 +53365,12 @@
       <c r="GW251" s="3"/>
       <c r="GX251" s="3"/>
       <c r="GY251" s="3"/>
+      <c r="GZ251" s="3"/>
+      <c r="HA251" s="3"/>
+      <c r="HB251" s="3"/>
+      <c r="HC251" s="3"/>
     </row>
-    <row r="252" spans="3:207" x14ac:dyDescent="0.2">
+    <row r="252" spans="3:211" x14ac:dyDescent="0.2">
       <c r="C252" s="3"/>
       <c r="D252" s="3"/>
       <c r="E252" s="3"/>
@@ -52394,6 +53576,10 @@
       <c r="GW252" s="3"/>
       <c r="GX252" s="3"/>
       <c r="GY252" s="3"/>
+      <c r="GZ252" s="3"/>
+      <c r="HA252" s="3"/>
+      <c r="HB252" s="3"/>
+      <c r="HC252" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
